--- a/workspaces/nasdaq_hourly_24hrs/day_of_week/day_of_week.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/day_of_week/day_of_week.xlsx
@@ -622,79 +622,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.3780600130776293</v>
+        <v>0.301047655152999</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.283196556604089</v>
+        <v>3.09300010958836</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.34793589434868</v>
+        <v>4.228090199949207</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.720105566192501</v>
+        <v>5.675701194354225</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4.801447467738903</v>
+        <v>4.725941112916267</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.431458473422211</v>
+        <v>4.436096540422902</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.63346837735515</v>
+        <v>4.718692256466753</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4.077403948349968</v>
+        <v>4.162900140680733</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.009820726231446</v>
+        <v>3.094592622683351</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>2.796088705780626</v>
+        <v>2.880710172989801</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.9867028496217429</v>
+        <v>1.070450856046691</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.01388006235818295</v>
+        <v>0.09845375397583211</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.005141538907118104</v>
+        <v>0.09159819240692713</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.6331493139652977</v>
+        <v>-0.5451477116295464</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.7346959727669073</v>
+        <v>-0.6455119799471305</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-1.394331281343895</v>
+        <v>-1.305096339457762</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-1.806805292970452</v>
+        <v>-1.715648995172501</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-1.494788025140203</v>
+        <v>-1.403732543480515</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-1.00088978475511</v>
+        <v>-0.910480887259979</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-1.23317547640147</v>
+        <v>-1.142400849380465</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-1.498810597591849</v>
+        <v>-1.406825421136425</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.8782212913963789</v>
+        <v>-0.786971265089818</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.7435439880765458</v>
+        <v>-0.6529906543413233</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.8017143762837264</v>
+        <v>0.8045187632789847</v>
       </c>
     </row>
     <row r="7">
@@ -704,79 +704,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.8485089791080185</v>
+        <v>0.8650955185896052</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.05337213444837374</v>
+        <v>0.1014279554114239</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.39855913176585</v>
+        <v>-2.336142117608766</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.390530047233575</v>
+        <v>-1.333317277627671</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-3.483902565819584</v>
+        <v>-3.383807609047281</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.876153315406299</v>
+        <v>-4.769469667335336</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-6.515151289962098</v>
+        <v>-6.398423000485387</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-6.075463296564706</v>
+        <v>-5.961874050553881</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-6.036561129265188</v>
+        <v>-5.919912108396503</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-5.237464376776742</v>
+        <v>-5.119767939826986</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-5.687178025864114</v>
+        <v>-5.560339212283452</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-5.541830618662253</v>
+        <v>-5.409895730748637</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-4.374291647369773</v>
+        <v>-4.244978598181781</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-4.602601021738991</v>
+        <v>-4.465755354473956</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-4.549916891254774</v>
+        <v>-4.412406068930046</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-2.940439522751817</v>
+        <v>-2.81938094051511</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-2.561883933075443</v>
+        <v>-2.527305818109561</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-1.712754653478562</v>
+        <v>-1.775273355542559</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-1.696852193293104</v>
+        <v>-1.848668305649923</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-1.854600882059977</v>
+        <v>-2.095081626398887</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-1.299333595121887</v>
+        <v>-1.637039326450207</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.4189815644505046</v>
+        <v>-0.7623073331608694</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.4882871919683609</v>
+        <v>-0.8296385247179856</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.7087645206065787</v>
+        <v>-0.9610994736276695</v>
       </c>
     </row>
     <row r="8">
@@ -789,76 +789,76 @@
         <v>661</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.8249736856047249</v>
+        <v>-0.8051583934585409</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.097802303365476</v>
+        <v>-2.048433480477108</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.048547730218282</v>
+        <v>-1.997074411961286</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.519765647152354</v>
+        <v>-3.467240789664338</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.332070559496159</v>
+        <v>-1.249955394497896</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.9959184627888149</v>
+        <v>-0.9140513966458101</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.5743809786680103</v>
+        <v>-0.4913667616269848</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.153245298463673</v>
+        <v>-1.069801948543223</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.5438134568736075</v>
+        <v>0.6272206994674363</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.7632659506848896</v>
+        <v>0.756541662356284</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.730901199636733</v>
+        <v>1.63104878884451</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.902826883198081</v>
+        <v>2.709176521765201</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>3.834385190587646</v>
+        <v>3.544904488039883</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>5.369820244117967</v>
+        <v>4.982491902560966</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>5.410149404401906</v>
+        <v>5.018631019423601</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>4.740057044551868</v>
+        <v>4.358744113335618</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>5.816206582571823</v>
+        <v>5.521729088260287</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>4.803471846461356</v>
+        <v>4.605336208570449</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>4.565795240855671</v>
+        <v>4.462104661667134</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>4.450316736961817</v>
+        <v>4.441366447977842</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>3.453094730103601</v>
+        <v>3.540541053580469</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>2.469396771122213</v>
+        <v>2.556979509720541</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>2.744247153435786</v>
+        <v>2.831454222202595</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>1.609276982458532</v>
+        <v>1.696620456120016</v>
       </c>
     </row>
     <row r="9">
@@ -1086,79 +1086,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2754</v>
+        <v>2759</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.3104567279958559</v>
+        <v>0.3050988325139841</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.7240141270127651</v>
+        <v>0.7107495561345871</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.7645695280808269</v>
+        <v>0.7709946158190277</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.061759346799626</v>
+        <v>1.088410234751706</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.985291531711411</v>
+        <v>1.025883929369712</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.7391363692100867</v>
+        <v>0.8003910076628244</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.7244370674661411</v>
+        <v>0.8074512845071666</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.44579648983364</v>
+        <v>0.5292398397540907</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.5956621409384582</v>
+        <v>0.679069383532287</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.6373345916630484</v>
+        <v>0.7006643611613796</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.4270485567919593</v>
+        <v>0.4691263146270188</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3135568198845391</v>
+        <v>0.3348333936636791</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.4395320515186256</v>
+        <v>0.4395514279270927</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.3844264401826862</v>
+        <v>0.3629290339651519</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.3622421809112026</v>
+        <v>0.3405403858166807</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.1466503066862472</v>
+        <v>0.1255325207258693</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.6136363107777001</v>
+        <v>0.5916136590522356</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.7478578229133532</v>
+        <v>0.7255415728678543</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>1.02222801841382</v>
+        <v>0.9994770914127855</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>1.086261791316133</v>
+        <v>1.063446332622576</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>1.000089671325973</v>
+        <v>0.9772249886797937</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>1.127639878170726</v>
+        <v>1.104503072463103</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>1.061705989110706</v>
+        <v>1.038770760605104</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>1.007813782733635</v>
+        <v>0.9849350299614201</v>
       </c>
     </row>
     <row r="7">
@@ -1168,79 +1168,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2754</v>
+        <v>2759</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.3104567279958559</v>
+        <v>0.3050988325139841</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.7240141270127651</v>
+        <v>0.7107495561345871</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.7645695280808269</v>
+        <v>0.7709946158190277</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.061759346799626</v>
+        <v>1.088410234751706</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.985291531711411</v>
+        <v>1.025883929369712</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.7391363692100867</v>
+        <v>0.8003910076628244</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.7244370674661411</v>
+        <v>0.8074512845071666</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.44579648983364</v>
+        <v>0.5292398397540907</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.5956621409384582</v>
+        <v>0.679069383532287</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.6373345916630484</v>
+        <v>0.7006643611613796</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.4270485567919593</v>
+        <v>0.4691263146270188</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.3135568198845391</v>
+        <v>0.3348333936636791</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.4395320515186256</v>
+        <v>0.4395514279270927</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.3844264401826862</v>
+        <v>0.3629290339651519</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.3622421809112026</v>
+        <v>0.3405403858166807</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.1466503066862472</v>
+        <v>0.1255325207258693</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.6136363107777001</v>
+        <v>0.5916136590522356</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.7478578229133532</v>
+        <v>0.7255415728678543</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>1.02222801841382</v>
+        <v>0.9994770914127855</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>1.086261791316133</v>
+        <v>1.063446332622576</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>1.000089671325973</v>
+        <v>0.9772249886797937</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>1.127639878170726</v>
+        <v>1.104503072463103</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>1.061705989110706</v>
+        <v>1.038770760605104</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>1.007813782733635</v>
+        <v>0.9849350299614201</v>
       </c>
     </row>
     <row r="8">
@@ -1250,79 +1250,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2754</v>
+        <v>2759</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.3104567279958559</v>
+        <v>0.3050988325139841</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.7240141270127651</v>
+        <v>0.7107495561345871</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.7645695280808269</v>
+        <v>0.7709946158190277</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.061759346799626</v>
+        <v>1.088410234751706</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.985291531711411</v>
+        <v>1.025883929369712</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.7391363692100867</v>
+        <v>0.8003910076628244</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.7244370674661411</v>
+        <v>0.8074512845071666</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.44579648983364</v>
+        <v>0.5292398397540907</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.5956621409384582</v>
+        <v>0.679069383532287</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.6373345916630484</v>
+        <v>0.7006643611613796</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.4270485567919593</v>
+        <v>0.4691263146270188</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.3135568198845391</v>
+        <v>0.3348333936636791</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.4395320515186256</v>
+        <v>0.4395514279270927</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.3844264401826862</v>
+        <v>0.3629290339651519</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.3622421809112026</v>
+        <v>0.3405403858166807</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.1466503066862472</v>
+        <v>0.1255325207258693</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.6136363107777001</v>
+        <v>0.5916136590522356</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.7478578229133532</v>
+        <v>0.7255415728678543</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>1.02222801841382</v>
+        <v>0.9994770914127855</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.086261791316133</v>
+        <v>1.063446332622576</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>1.000089671325973</v>
+        <v>0.9772249886797937</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>1.127639878170726</v>
+        <v>1.104503072463103</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>1.061705989110706</v>
+        <v>1.038770760605104</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>1.007813782733635</v>
+        <v>0.9849350299614201</v>
       </c>
     </row>
     <row r="9">
@@ -1332,79 +1332,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2754</v>
+        <v>2759</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.3104567279958559</v>
+        <v>0.3050988325139841</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.7240141270127651</v>
+        <v>0.7107495561345871</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.7645695280808269</v>
+        <v>0.7709946158190277</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.061759346799626</v>
+        <v>1.088410234751706</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.985291531711411</v>
+        <v>1.025883929369712</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.7391363692100867</v>
+        <v>0.8003910076628244</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.7244370674661411</v>
+        <v>0.8074512845071666</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.44579648983364</v>
+        <v>0.5292398397540907</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.5956621409384582</v>
+        <v>0.679069383532287</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.6373345916630484</v>
+        <v>0.7006643611613796</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.4270485567919593</v>
+        <v>0.4691263146270188</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.3135568198845391</v>
+        <v>0.3348333936636791</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.4395320515186256</v>
+        <v>0.4395514279270927</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.3844264401826862</v>
+        <v>0.3629290339651519</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.3622421809112026</v>
+        <v>0.3405403858166807</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.1466503066862472</v>
+        <v>0.1255325207258693</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.6136363107777001</v>
+        <v>0.5916136590522356</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.7478578229133532</v>
+        <v>0.7255415728678543</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.02222801841382</v>
+        <v>0.9994770914127855</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.086261791316133</v>
+        <v>1.063446332622576</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>1.000089671325973</v>
+        <v>0.9772249886797937</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>1.127639878170726</v>
+        <v>1.104503072463103</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>1.061705989110706</v>
+        <v>1.038770760605104</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>1.007813782733635</v>
+        <v>0.9849350299614201</v>
       </c>
     </row>
     <row r="10">
@@ -1414,79 +1414,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2754</v>
+        <v>2759</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.3104567279958559</v>
+        <v>0.3050988325139841</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.7240141270127651</v>
+        <v>0.7107495561345871</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.7645695280808269</v>
+        <v>0.7709946158190277</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.061759346799626</v>
+        <v>1.088410234751706</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.985291531711411</v>
+        <v>1.025883929369712</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.7391363692100867</v>
+        <v>0.8003910076628244</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.7244370674661411</v>
+        <v>0.8074512845071666</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.44579648983364</v>
+        <v>0.5292398397540907</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.5956621409384582</v>
+        <v>0.679069383532287</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.6373345916630484</v>
+        <v>0.7006643611613796</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4270485567919593</v>
+        <v>0.4691263146270188</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.3135568198845391</v>
+        <v>0.3348333936636791</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.4395320515186256</v>
+        <v>0.4395514279270927</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.3844264401826862</v>
+        <v>0.3629290339651519</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.3622421809112026</v>
+        <v>0.3405403858166807</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.1466503066862472</v>
+        <v>0.1255325207258693</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.6136363107777001</v>
+        <v>0.5916136590522356</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.7478578229133532</v>
+        <v>0.7255415728678543</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1.02222801841382</v>
+        <v>0.9994770914127855</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.086261791316133</v>
+        <v>1.063446332622576</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>1.000089671325973</v>
+        <v>0.9772249886797937</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>1.127639878170726</v>
+        <v>1.104503072463103</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>1.061705989110706</v>
+        <v>1.038770760605104</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>1.007813782733635</v>
+        <v>0.9849350299614201</v>
       </c>
     </row>
     <row r="11">
@@ -1496,79 +1496,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2754</v>
+        <v>2759</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.3104567279958559</v>
+        <v>0.3050988325139841</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.7240141270127651</v>
+        <v>0.7107495561345871</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.7645695280808269</v>
+        <v>0.7709946158190277</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.061759346799626</v>
+        <v>1.088410234751706</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.985291531711411</v>
+        <v>1.025883929369712</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.7391363692100867</v>
+        <v>0.8003910076628244</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.7244370674661411</v>
+        <v>0.8074512845071666</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.44579648983364</v>
+        <v>0.5292398397540907</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.5956621409384582</v>
+        <v>0.679069383532287</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.6373345916630484</v>
+        <v>0.7006643611613796</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4270485567919593</v>
+        <v>0.4691263146270188</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.3135568198845391</v>
+        <v>0.3348333936636791</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.4395320515186256</v>
+        <v>0.4395514279270927</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.3844264401826862</v>
+        <v>0.3629290339651519</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.3622421809112026</v>
+        <v>0.3405403858166807</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.1466503066862472</v>
+        <v>0.1255325207258693</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.6136363107777001</v>
+        <v>0.5916136590522356</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.7478578229133532</v>
+        <v>0.7255415728678543</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1.02222801841382</v>
+        <v>0.9994770914127855</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.086261791316133</v>
+        <v>1.063446332622576</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>1.000089671325973</v>
+        <v>0.9772249886797937</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>1.127639878170726</v>
+        <v>1.104503072463103</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>1.061705989110706</v>
+        <v>1.038770760605104</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>1.007813782733635</v>
+        <v>0.9849350299614201</v>
       </c>
     </row>
     <row r="12">
@@ -1578,79 +1578,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2754</v>
+        <v>2759</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.3104567279958559</v>
+        <v>0.3050988325139841</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.7240141270127651</v>
+        <v>0.7107495561345871</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.7645695280808269</v>
+        <v>0.7709946158190277</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.061759346799626</v>
+        <v>1.088410234751706</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.985291531711411</v>
+        <v>1.025883929369712</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.7391363692100867</v>
+        <v>0.8003910076628244</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.7244370674661411</v>
+        <v>0.8074512845071666</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.44579648983364</v>
+        <v>0.5292398397540907</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.5956621409384582</v>
+        <v>0.679069383532287</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.6373345916630484</v>
+        <v>0.7006643611613796</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4270485567919593</v>
+        <v>0.4691263146270188</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3135568198845391</v>
+        <v>0.3348333936636791</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.4395320515186256</v>
+        <v>0.4395514279270927</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.3844264401826862</v>
+        <v>0.3629290339651519</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.3622421809112026</v>
+        <v>0.3405403858166807</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.1466503066862472</v>
+        <v>0.1255325207258693</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.6136363107777001</v>
+        <v>0.5916136590522356</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.7478578229133532</v>
+        <v>0.7255415728678543</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>1.02222801841382</v>
+        <v>0.9994770914127855</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1.086261791316133</v>
+        <v>1.063446332622576</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>1.000089671325973</v>
+        <v>0.9772249886797937</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>1.127639878170726</v>
+        <v>1.104503072463103</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>1.061705989110706</v>
+        <v>1.038770760605104</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>1.007813782733635</v>
+        <v>0.9849350299614201</v>
       </c>
     </row>
     <row r="13">
@@ -1660,79 +1660,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2754</v>
+        <v>2759</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.3104567279958559</v>
+        <v>0.3050988325139841</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.7240141270127651</v>
+        <v>0.7107495561345871</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.7645695280808269</v>
+        <v>0.7709946158190277</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.061759346799626</v>
+        <v>1.088410234751706</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.985291531711411</v>
+        <v>1.025883929369712</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.7391363692100867</v>
+        <v>0.8003910076628244</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.7244370674661411</v>
+        <v>0.8074512845071666</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.44579648983364</v>
+        <v>0.5292398397540907</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.5956621409384582</v>
+        <v>0.679069383532287</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.6373345916630484</v>
+        <v>0.7006643611613796</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.4270485567919593</v>
+        <v>0.4691263146270188</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3135568198845391</v>
+        <v>0.3348333936636791</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.4395320515186256</v>
+        <v>0.4395514279270927</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3844264401826862</v>
+        <v>0.3629290339651519</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.3622421809112026</v>
+        <v>0.3405403858166807</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.1466503066862472</v>
+        <v>0.1255325207258693</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.6136363107777001</v>
+        <v>0.5916136590522356</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.7478578229133532</v>
+        <v>0.7255415728678543</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.02222801841382</v>
+        <v>0.9994770914127855</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>1.086261791316133</v>
+        <v>1.063446332622576</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>1.000089671325973</v>
+        <v>0.9772249886797937</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1.127639878170726</v>
+        <v>1.104503072463103</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>1.061705989110706</v>
+        <v>1.038770760605104</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>1.007813782733635</v>
+        <v>0.9849350299614201</v>
       </c>
     </row>
     <row r="14">
@@ -1742,79 +1742,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2038</v>
+        <v>2042</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.2867060154744792</v>
+        <v>0.3065213076206632</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1750902005570936</v>
+        <v>-0.1257213776687252</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.4943560451516404</v>
+        <v>-0.4428827268946449</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.5748333387181859</v>
+        <v>-0.5223084812301693</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3554187971382845</v>
+        <v>-0.2733036321400206</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.5580680599439276</v>
+        <v>-0.4762009938009228</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.64890268615531</v>
+        <v>-0.5658884691142845</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.8300773768482372</v>
+        <v>-0.7466340269277865</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.252491709439262</v>
+        <v>-0.1690844668454332</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.1210893267413482</v>
+        <v>-0.06480716042577939</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.230428108476886</v>
+        <v>0.2579854252059164</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.4188407052569048</v>
+        <v>0.4178325129859957</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.5921442237609398</v>
+        <v>0.5617269763443034</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.741926067253317</v>
+        <v>0.6817787041862076</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.747623789367303</v>
+        <v>0.6867693506808621</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.6880353984573873</v>
+        <v>0.6278640059127838</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>1.463997541535157</v>
+        <v>1.401754365751131</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>1.535754990335512</v>
+        <v>1.473185814504376</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1.732999533167963</v>
+        <v>1.670113658850781</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.901137691063838</v>
+        <v>1.83797739505949</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>1.878015379149907</v>
+        <v>1.814327899472268</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>1.832348709088301</v>
+        <v>1.768649546520621</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>1.695935127317803</v>
+        <v>1.632792765755241</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>1.080221621309761</v>
+        <v>1.048283934570286</v>
       </c>
     </row>
     <row r="15">
@@ -1824,79 +1824,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2038</v>
+        <v>2042</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2867060154744792</v>
+        <v>0.3065213076206632</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1750902005570936</v>
+        <v>-0.1257213776687252</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.4943560451516404</v>
+        <v>-0.4428827268946449</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5748333387181859</v>
+        <v>-0.5223084812301693</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.3554187971382845</v>
+        <v>-0.2733036321400206</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.5580680599439276</v>
+        <v>-0.4762009938009228</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.64890268615531</v>
+        <v>-0.5658884691142845</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.8300773768482372</v>
+        <v>-0.7466340269277865</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.252491709439262</v>
+        <v>-0.1690844668454332</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.1210893267413482</v>
+        <v>-0.06480716042577939</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.230428108476886</v>
+        <v>0.2579854252059164</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.4188407052569048</v>
+        <v>0.4178325129859957</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.5921442237609398</v>
+        <v>0.5617269763443034</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.741926067253317</v>
+        <v>0.6817787041862076</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.747623789367303</v>
+        <v>0.6867693506808621</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.6880353984573873</v>
+        <v>0.6278640059127838</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>1.463997541535157</v>
+        <v>1.401754365751131</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>1.535754990335512</v>
+        <v>1.473185814504376</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>1.732999533167963</v>
+        <v>1.670113658850781</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.901137691063838</v>
+        <v>1.83797739505949</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>1.878015379149907</v>
+        <v>1.814327899472268</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>1.832348709088301</v>
+        <v>1.768649546520621</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>1.695935127317803</v>
+        <v>1.632792765755241</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.080221621309761</v>
+        <v>1.048283934570286</v>
       </c>
     </row>
     <row r="16">
@@ -1906,79 +1906,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2038</v>
+        <v>2042</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2867060154744792</v>
+        <v>0.3065213076206632</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1750902005570936</v>
+        <v>-0.1257213776687252</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.4943560451516404</v>
+        <v>-0.4428827268946449</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5748333387181859</v>
+        <v>-0.5223084812301693</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3554187971382845</v>
+        <v>-0.2733036321400206</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.5580680599439276</v>
+        <v>-0.4762009938009228</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.64890268615531</v>
+        <v>-0.5658884691142845</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.8300773768482372</v>
+        <v>-0.7466340269277865</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.252491709439262</v>
+        <v>-0.1690844668454332</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.1210893267413482</v>
+        <v>-0.06480716042577939</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.230428108476886</v>
+        <v>0.2579854252059164</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.4188407052569048</v>
+        <v>0.4178325129859957</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.5921442237609398</v>
+        <v>0.5617269763443034</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.741926067253317</v>
+        <v>0.6817787041862076</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.747623789367303</v>
+        <v>0.6867693506808621</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.6880353984573873</v>
+        <v>0.6278640059127838</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>1.463997541535157</v>
+        <v>1.401754365751131</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>1.535754990335512</v>
+        <v>1.473185814504376</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>1.732999533167963</v>
+        <v>1.670113658850781</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1.901137691063838</v>
+        <v>1.83797739505949</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>1.878015379149907</v>
+        <v>1.814327899472268</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>1.832348709088301</v>
+        <v>1.768649546520621</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>1.695935127317803</v>
+        <v>1.632792765755241</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>1.080221621309761</v>
+        <v>1.048283934570286</v>
       </c>
     </row>
     <row r="17">
@@ -1988,79 +1988,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2038</v>
+        <v>2042</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2867060154744792</v>
+        <v>0.3065213076206632</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.1750902005570936</v>
+        <v>-0.1257213776687252</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.4943560451516404</v>
+        <v>-0.4428827268946449</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5748333387181859</v>
+        <v>-0.5223084812301693</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3554187971382845</v>
+        <v>-0.2733036321400206</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5580680599439276</v>
+        <v>-0.4762009938009228</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.64890268615531</v>
+        <v>-0.5658884691142845</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.8300773768482372</v>
+        <v>-0.7466340269277865</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.252491709439262</v>
+        <v>-0.1690844668454332</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.1210893267413482</v>
+        <v>-0.06480716042577939</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.230428108476886</v>
+        <v>0.2579854252059164</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.4188407052569048</v>
+        <v>0.4178325129859957</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.5921442237609398</v>
+        <v>0.5617269763443034</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.741926067253317</v>
+        <v>0.6817787041862076</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.747623789367303</v>
+        <v>0.6867693506808621</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.6880353984573873</v>
+        <v>0.6278640059127838</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.463997541535157</v>
+        <v>1.401754365751131</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>1.535754990335512</v>
+        <v>1.473185814504376</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>1.732999533167963</v>
+        <v>1.670113658850781</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.901137691063838</v>
+        <v>1.83797739505949</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.878015379149907</v>
+        <v>1.814327899472268</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>1.832348709088301</v>
+        <v>1.768649546520621</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>1.695935127317803</v>
+        <v>1.632792765755241</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>1.080221621309761</v>
+        <v>1.048283934570286</v>
       </c>
     </row>
     <row r="18">
@@ -2070,79 +2070,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2038</v>
+        <v>2042</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2867060154744792</v>
+        <v>0.3065213076206632</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.1750902005570936</v>
+        <v>-0.1257213776687252</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.4943560451516404</v>
+        <v>-0.4428827268946449</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.5748333387181859</v>
+        <v>-0.5223084812301693</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.3554187971382845</v>
+        <v>-0.2733036321400206</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.5580680599439276</v>
+        <v>-0.4762009938009228</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.64890268615531</v>
+        <v>-0.5658884691142845</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.8300773768482372</v>
+        <v>-0.7466340269277865</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.252491709439262</v>
+        <v>-0.1690844668454332</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.1210893267413482</v>
+        <v>-0.06480716042577939</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.230428108476886</v>
+        <v>0.2579854252059164</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.4188407052569048</v>
+        <v>0.4178325129859957</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.5921442237609398</v>
+        <v>0.5617269763443034</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.741926067253317</v>
+        <v>0.6817787041862076</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.747623789367303</v>
+        <v>0.6867693506808621</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.6880353984573873</v>
+        <v>0.6278640059127838</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.463997541535157</v>
+        <v>1.401754365751131</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1.535754990335512</v>
+        <v>1.473185814504376</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>1.732999533167963</v>
+        <v>1.670113658850781</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.901137691063838</v>
+        <v>1.83797739505949</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>1.878015379149907</v>
+        <v>1.814327899472268</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>1.832348709088301</v>
+        <v>1.768649546520621</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>1.695935127317803</v>
+        <v>1.632792765755241</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.080221621309761</v>
+        <v>1.048283934570286</v>
       </c>
     </row>
     <row r="19">
@@ -2152,79 +2152,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2038</v>
+        <v>2042</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.2867060154744792</v>
+        <v>0.3065213076206632</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.1750902005570936</v>
+        <v>-0.1257213776687252</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.4943560451516404</v>
+        <v>-0.4428827268946449</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.5748333387181859</v>
+        <v>-0.5223084812301693</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.3554187971382845</v>
+        <v>-0.2733036321400206</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.5580680599439276</v>
+        <v>-0.4762009938009228</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.64890268615531</v>
+        <v>-0.5658884691142845</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.8300773768482372</v>
+        <v>-0.7466340269277865</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.252491709439262</v>
+        <v>-0.1690844668454332</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.1210893267413482</v>
+        <v>-0.06480716042577939</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.230428108476886</v>
+        <v>0.2579854252059164</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.4188407052569048</v>
+        <v>0.4178325129859957</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.5921442237609398</v>
+        <v>0.5617269763443034</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.741926067253317</v>
+        <v>0.6817787041862076</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.747623789367303</v>
+        <v>0.6867693506808621</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.6880353984573873</v>
+        <v>0.6278640059127838</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>1.463997541535157</v>
+        <v>1.401754365751131</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.535754990335512</v>
+        <v>1.473185814504376</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.732999533167963</v>
+        <v>1.670113658850781</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.901137691063838</v>
+        <v>1.83797739505949</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.878015379149907</v>
+        <v>1.814327899472268</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.832348709088301</v>
+        <v>1.768649546520621</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.695935127317803</v>
+        <v>1.632792765755241</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.080221621309761</v>
+        <v>1.048283934570286</v>
       </c>
     </row>
     <row r="20">
@@ -2234,79 +2234,79 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2038</v>
+        <v>2042</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.2867060154744792</v>
+        <v>0.3065213076206632</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.1750902005570936</v>
+        <v>-0.1257213776687252</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.4943560451516404</v>
+        <v>-0.4428827268946449</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.5748333387181859</v>
+        <v>-0.5223084812301693</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3554187971382845</v>
+        <v>-0.2733036321400206</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.5580680599439276</v>
+        <v>-0.4762009938009228</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.64890268615531</v>
+        <v>-0.5658884691142845</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.8300773768482372</v>
+        <v>-0.7466340269277865</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.252491709439262</v>
+        <v>-0.1690844668454332</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.1210893267413482</v>
+        <v>-0.06480716042577939</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.230428108476886</v>
+        <v>0.2579854252059164</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.4188407052569048</v>
+        <v>0.4178325129859957</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.5921442237609398</v>
+        <v>0.5617269763443034</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.741926067253317</v>
+        <v>0.6817787041862076</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.747623789367303</v>
+        <v>0.6867693506808621</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.6880353984573873</v>
+        <v>0.6278640059127838</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.463997541535157</v>
+        <v>1.401754365751131</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.535754990335512</v>
+        <v>1.473185814504376</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.732999533167963</v>
+        <v>1.670113658850781</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.901137691063838</v>
+        <v>1.83797739505949</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.878015379149907</v>
+        <v>1.814327899472268</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.832348709088301</v>
+        <v>1.768649546520621</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.695935127317803</v>
+        <v>1.632792765755241</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>1.080221621309761</v>
+        <v>1.048283934570286</v>
       </c>
     </row>
     <row r="21">
@@ -2319,76 +2319,76 @@
         <v>1346</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.00212582021229224</v>
+        <v>0.01768947193389181</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.2925463192969033</v>
+        <v>-0.2431774964085349</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4846250365252018</v>
+        <v>0.5360983547821974</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.1554706921411722</v>
+        <v>-0.1029458346531555</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.252984447978697</v>
+        <v>1.335099612976961</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.661928222953513</v>
+        <v>1.743795289096518</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.36702898831296</v>
+        <v>2.450043205353985</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.866658920658288</v>
+        <v>1.950102270578739</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.721190339980907</v>
+        <v>2.804597582574736</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.509320431523491</v>
+        <v>2.549050716589988</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.272763505924125</v>
+        <v>3.266569338796252</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.483316601357984</v>
+        <v>3.43127891539261</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.145467866273911</v>
+        <v>3.047215148610398</v>
       </c>
       <c r="P21" s="4" t="n">
+        <v>3.343505082215536</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>3.323490072857084</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>2.410391853397037</v>
+      </c>
+      <c r="S21" s="4" t="n">
+        <v>3.433422930362596</v>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>3.15292398861483</v>
+      </c>
+      <c r="U21" s="4" t="n">
         <v>3.489632416126035</v>
       </c>
-      <c r="Q21" s="4" t="n">
-        <v>3.471173678661856</v>
-      </c>
-      <c r="R21" s="4" t="n">
-        <v>2.553492044428239</v>
-      </c>
-      <c r="S21" s="4" t="n">
-        <v>3.533767214960505</v>
-      </c>
-      <c r="T21" s="4" t="n">
-        <v>3.205865446144827</v>
-      </c>
-      <c r="U21" s="4" t="n">
-        <v>3.496340836816593</v>
-      </c>
       <c r="V21" s="4" t="n">
-        <v>3.832022603843676</v>
+        <v>3.871713709275717</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>3.511541003366901</v>
+        <v>3.598987326843769</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>2.989793396524306</v>
+        <v>3.077376135122634</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>2.818878548525845</v>
+        <v>2.906085617292653</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1.999967839887837</v>
+        <v>2.087311313549321</v>
       </c>
     </row>
     <row r="22">
@@ -2401,76 +2401,76 @@
         <v>1346</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.00212582021229224</v>
+        <v>0.01768947193389181</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2925463192969033</v>
+        <v>-0.2431774964085349</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4846250365252018</v>
+        <v>0.5360983547821974</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1554706921411722</v>
+        <v>-0.1029458346531555</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.252984447978697</v>
+        <v>1.335099612976961</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.661928222953513</v>
+        <v>1.743795289096518</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.36702898831296</v>
+        <v>2.450043205353985</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.866658920658288</v>
+        <v>1.950102270578739</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.721190339980907</v>
+        <v>2.804597582574736</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.509320431523491</v>
+        <v>2.549050716589988</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.272763505924125</v>
+        <v>3.266569338796252</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.483316601357984</v>
+        <v>3.43127891539261</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.145467866273911</v>
+        <v>3.047215148610398</v>
       </c>
       <c r="P22" s="4" t="n">
+        <v>3.343505082215536</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>3.323490072857084</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>2.410391853397037</v>
+      </c>
+      <c r="S22" s="4" t="n">
+        <v>3.433422930362596</v>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>3.15292398861483</v>
+      </c>
+      <c r="U22" s="4" t="n">
         <v>3.489632416126035</v>
       </c>
-      <c r="Q22" s="4" t="n">
-        <v>3.471173678661856</v>
-      </c>
-      <c r="R22" s="4" t="n">
-        <v>2.553492044428239</v>
-      </c>
-      <c r="S22" s="4" t="n">
-        <v>3.533767214960505</v>
-      </c>
-      <c r="T22" s="4" t="n">
-        <v>3.205865446144827</v>
-      </c>
-      <c r="U22" s="4" t="n">
-        <v>3.496340836816593</v>
-      </c>
       <c r="V22" s="4" t="n">
-        <v>3.832022603843676</v>
+        <v>3.871713709275717</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>3.511541003366901</v>
+        <v>3.598987326843769</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>2.989793396524306</v>
+        <v>3.077376135122634</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>2.818878548525845</v>
+        <v>2.906085617292653</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>1.999967839887837</v>
+        <v>2.087311313549321</v>
       </c>
     </row>
     <row r="23">
@@ -2483,76 +2483,76 @@
         <v>1346</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.00212582021229224</v>
+        <v>0.01768947193389181</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.2925463192969033</v>
+        <v>-0.2431774964085349</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4846250365252018</v>
+        <v>0.5360983547821974</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.1554706921411722</v>
+        <v>-0.1029458346531555</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.252984447978697</v>
+        <v>1.335099612976961</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.661928222953513</v>
+        <v>1.743795289096518</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.36702898831296</v>
+        <v>2.450043205353985</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.866658920658288</v>
+        <v>1.950102270578739</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.721190339980907</v>
+        <v>2.804597582574736</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.509320431523491</v>
+        <v>2.549050716589988</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.272763505924125</v>
+        <v>3.266569338796252</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.483316601357984</v>
+        <v>3.43127891539261</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.145467866273911</v>
+        <v>3.047215148610398</v>
       </c>
       <c r="P23" s="4" t="n">
+        <v>3.343505082215536</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>3.323490072857084</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>2.410391853397037</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>3.433422930362596</v>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>3.15292398861483</v>
+      </c>
+      <c r="U23" s="4" t="n">
         <v>3.489632416126035</v>
       </c>
-      <c r="Q23" s="4" t="n">
-        <v>3.471173678661856</v>
-      </c>
-      <c r="R23" s="4" t="n">
-        <v>2.553492044428239</v>
-      </c>
-      <c r="S23" s="4" t="n">
-        <v>3.533767214960505</v>
-      </c>
-      <c r="T23" s="4" t="n">
-        <v>3.205865446144827</v>
-      </c>
-      <c r="U23" s="4" t="n">
-        <v>3.496340836816593</v>
-      </c>
       <c r="V23" s="4" t="n">
-        <v>3.832022603843676</v>
+        <v>3.871713709275717</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>3.511541003366901</v>
+        <v>3.598987326843769</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>2.989793396524306</v>
+        <v>3.077376135122634</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>2.818878548525845</v>
+        <v>2.906085617292653</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.999967839887837</v>
+        <v>2.087311313549321</v>
       </c>
     </row>
     <row r="24">
@@ -2565,76 +2565,76 @@
         <v>1346</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.00212582021229224</v>
+        <v>0.01768947193389181</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.2925463192969033</v>
+        <v>-0.2431774964085349</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4846250365252018</v>
+        <v>0.5360983547821974</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1554706921411722</v>
+        <v>-0.1029458346531555</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.252984447978697</v>
+        <v>1.335099612976961</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.661928222953513</v>
+        <v>1.743795289096518</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.36702898831296</v>
+        <v>2.450043205353985</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.866658920658288</v>
+        <v>1.950102270578739</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.721190339980907</v>
+        <v>2.804597582574736</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.509320431523491</v>
+        <v>2.549050716589988</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.272763505924125</v>
+        <v>3.266569338796252</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.483316601357984</v>
+        <v>3.43127891539261</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.145467866273911</v>
+        <v>3.047215148610398</v>
       </c>
       <c r="P24" s="4" t="n">
+        <v>3.343505082215536</v>
+      </c>
+      <c r="Q24" s="4" t="n">
+        <v>3.323490072857084</v>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>2.410391853397037</v>
+      </c>
+      <c r="S24" s="4" t="n">
+        <v>3.433422930362596</v>
+      </c>
+      <c r="T24" s="4" t="n">
+        <v>3.15292398861483</v>
+      </c>
+      <c r="U24" s="4" t="n">
         <v>3.489632416126035</v>
       </c>
-      <c r="Q24" s="4" t="n">
-        <v>3.471173678661856</v>
-      </c>
-      <c r="R24" s="4" t="n">
-        <v>2.553492044428239</v>
-      </c>
-      <c r="S24" s="4" t="n">
-        <v>3.533767214960505</v>
-      </c>
-      <c r="T24" s="4" t="n">
-        <v>3.205865446144827</v>
-      </c>
-      <c r="U24" s="4" t="n">
-        <v>3.496340836816593</v>
-      </c>
       <c r="V24" s="4" t="n">
-        <v>3.832022603843676</v>
+        <v>3.871713709275717</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.511541003366901</v>
+        <v>3.598987326843769</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.989793396524306</v>
+        <v>3.077376135122634</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.818878548525845</v>
+        <v>2.906085617292653</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>1.999967839887837</v>
+        <v>2.087311313549321</v>
       </c>
     </row>
     <row r="25">
@@ -2647,76 +2647,76 @@
         <v>1346</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.00212582021229224</v>
+        <v>0.01768947193389181</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.2925463192969033</v>
+        <v>-0.2431774964085349</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.4846250365252018</v>
+        <v>0.5360983547821974</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.1554706921411722</v>
+        <v>-0.1029458346531555</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.252984447978697</v>
+        <v>1.335099612976961</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.661928222953513</v>
+        <v>1.743795289096518</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.36702898831296</v>
+        <v>2.450043205353985</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.866658920658288</v>
+        <v>1.950102270578739</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.721190339980907</v>
+        <v>2.804597582574736</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.509320431523491</v>
+        <v>2.549050716589988</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.272763505924125</v>
+        <v>3.266569338796252</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.483316601357984</v>
+        <v>3.43127891539261</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.145467866273911</v>
+        <v>3.047215148610398</v>
       </c>
       <c r="P25" s="4" t="n">
+        <v>3.343505082215536</v>
+      </c>
+      <c r="Q25" s="4" t="n">
+        <v>3.323490072857084</v>
+      </c>
+      <c r="R25" s="4" t="n">
+        <v>2.410391853397037</v>
+      </c>
+      <c r="S25" s="4" t="n">
+        <v>3.433422930362596</v>
+      </c>
+      <c r="T25" s="4" t="n">
+        <v>3.15292398861483</v>
+      </c>
+      <c r="U25" s="4" t="n">
         <v>3.489632416126035</v>
       </c>
-      <c r="Q25" s="4" t="n">
-        <v>3.471173678661856</v>
-      </c>
-      <c r="R25" s="4" t="n">
-        <v>2.553492044428239</v>
-      </c>
-      <c r="S25" s="4" t="n">
-        <v>3.533767214960505</v>
-      </c>
-      <c r="T25" s="4" t="n">
-        <v>3.205865446144827</v>
-      </c>
-      <c r="U25" s="4" t="n">
-        <v>3.496340836816593</v>
-      </c>
       <c r="V25" s="4" t="n">
-        <v>3.832022603843676</v>
+        <v>3.871713709275717</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.511541003366901</v>
+        <v>3.598987326843769</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>2.989793396524306</v>
+        <v>3.077376135122634</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>2.818878548525845</v>
+        <v>2.906085617292653</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.999967839887837</v>
+        <v>2.087311313549321</v>
       </c>
     </row>
     <row r="26">
@@ -2729,76 +2729,76 @@
         <v>1346</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.00212582021229224</v>
+        <v>0.01768947193389181</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.2925463192969033</v>
+        <v>-0.2431774964085349</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.4846250365252018</v>
+        <v>0.5360983547821974</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.1554706921411722</v>
+        <v>-0.1029458346531555</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.252984447978697</v>
+        <v>1.335099612976961</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.661928222953513</v>
+        <v>1.743795289096518</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.36702898831296</v>
+        <v>2.450043205353985</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.866658920658288</v>
+        <v>1.950102270578739</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.721190339980907</v>
+        <v>2.804597582574736</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.509320431523491</v>
+        <v>2.549050716589988</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.272763505924125</v>
+        <v>3.266569338796252</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.483316601357984</v>
+        <v>3.43127891539261</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.145467866273911</v>
+        <v>3.047215148610398</v>
       </c>
       <c r="P26" s="4" t="n">
+        <v>3.343505082215536</v>
+      </c>
+      <c r="Q26" s="4" t="n">
+        <v>3.323490072857084</v>
+      </c>
+      <c r="R26" s="4" t="n">
+        <v>2.410391853397037</v>
+      </c>
+      <c r="S26" s="4" t="n">
+        <v>3.433422930362596</v>
+      </c>
+      <c r="T26" s="4" t="n">
+        <v>3.15292398861483</v>
+      </c>
+      <c r="U26" s="4" t="n">
         <v>3.489632416126035</v>
       </c>
-      <c r="Q26" s="4" t="n">
-        <v>3.471173678661856</v>
-      </c>
-      <c r="R26" s="4" t="n">
-        <v>2.553492044428239</v>
-      </c>
-      <c r="S26" s="4" t="n">
-        <v>3.533767214960505</v>
-      </c>
-      <c r="T26" s="4" t="n">
-        <v>3.205865446144827</v>
-      </c>
-      <c r="U26" s="4" t="n">
-        <v>3.496340836816593</v>
-      </c>
       <c r="V26" s="4" t="n">
-        <v>3.832022603843676</v>
+        <v>3.871713709275717</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>3.511541003366901</v>
+        <v>3.598987326843769</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>2.989793396524306</v>
+        <v>3.077376135122634</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>2.818878548525845</v>
+        <v>2.906085617292653</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>1.999967839887837</v>
+        <v>2.087311313549321</v>
       </c>
     </row>
     <row r="27">
@@ -2811,76 +2811,76 @@
         <v>1346</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.00212582021229224</v>
+        <v>0.01768947193389181</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2925463192969033</v>
+        <v>-0.2431774964085349</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.4846250365252018</v>
+        <v>0.5360983547821974</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.1554706921411722</v>
+        <v>-0.1029458346531555</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.252984447978697</v>
+        <v>1.335099612976961</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.661928222953513</v>
+        <v>1.743795289096518</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.36702898831296</v>
+        <v>2.450043205353985</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.866658920658288</v>
+        <v>1.950102270578739</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.721190339980907</v>
+        <v>2.804597582574736</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.509320431523491</v>
+        <v>2.549050716589988</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.272763505924125</v>
+        <v>3.266569338796252</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.483316601357984</v>
+        <v>3.43127891539261</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.145467866273911</v>
+        <v>3.047215148610398</v>
       </c>
       <c r="P27" s="4" t="n">
+        <v>3.343505082215536</v>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>3.323490072857084</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>2.410391853397037</v>
+      </c>
+      <c r="S27" s="4" t="n">
+        <v>3.433422930362596</v>
+      </c>
+      <c r="T27" s="4" t="n">
+        <v>3.15292398861483</v>
+      </c>
+      <c r="U27" s="4" t="n">
         <v>3.489632416126035</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>3.471173678661856</v>
-      </c>
-      <c r="R27" s="4" t="n">
-        <v>2.553492044428239</v>
-      </c>
-      <c r="S27" s="4" t="n">
-        <v>3.533767214960505</v>
-      </c>
-      <c r="T27" s="4" t="n">
-        <v>3.205865446144827</v>
-      </c>
-      <c r="U27" s="4" t="n">
-        <v>3.496340836816593</v>
-      </c>
       <c r="V27" s="4" t="n">
-        <v>3.832022603843676</v>
+        <v>3.871713709275717</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>3.511541003366901</v>
+        <v>3.598987326843769</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>2.989793396524306</v>
+        <v>3.077376135122634</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>2.818878548525845</v>
+        <v>2.906085617292653</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>1.999967839887837</v>
+        <v>2.087311313549321</v>
       </c>
     </row>
     <row r="28">
@@ -2893,76 +2893,76 @@
         <v>685</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.7918923389473989</v>
+        <v>0.8117076310935829</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.449459820074374</v>
+        <v>1.498828642962742</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.92904430487183</v>
+        <v>2.980517623128826</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.090951154957196</v>
+        <v>3.143476012445213</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.747468185118656</v>
+        <v>3.82958335011692</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.226653272991008</v>
+        <v>4.308520339134013</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>5.205382255720878</v>
+        <v>5.288396472761903</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.780756276628523</v>
+        <v>4.864199626548974</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.822279565869849</v>
+        <v>4.905686808463678</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.194199280916656</v>
+        <v>4.278756533887041</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.760604359144502</v>
+        <v>4.844786978968671</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.043467993626159</v>
+        <v>4.128081371141114</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.480687791279195</v>
+        <v>2.566963099905443</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.675319782107529</v>
+        <v>1.761942617619425</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.600132868860143</v>
+        <v>1.687740925878295</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.4435366209512708</v>
+        <v>0.5303030303030312</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>1.331296525922433</v>
+        <v>1.418283703544539</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>1.664233576642324</v>
+        <v>1.75139920410291</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>2.464356368101512</v>
+        <v>2.551232190866664</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>3.23539133086399</v>
+        <v>3.322019606674097</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>3.567939523990326</v>
+        <v>3.655385847467194</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>3.491957147459765</v>
+        <v>3.579539886058093</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>2.890895121014211</v>
+        <v>2.978102189781019</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>2.3769702585167</v>
+        <v>2.464313732178184</v>
       </c>
     </row>
     <row r="29">
@@ -2975,76 +2975,76 @@
         <v>685</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.7918923389473989</v>
+        <v>0.8117076310935829</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.449459820074374</v>
+        <v>1.498828642962742</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.92904430487183</v>
+        <v>2.980517623128826</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.090951154957196</v>
+        <v>3.143476012445213</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.747468185118656</v>
+        <v>3.82958335011692</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.226653272991008</v>
+        <v>4.308520339134013</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.205382255720878</v>
+        <v>5.288396472761903</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.780756276628523</v>
+        <v>4.864199626548974</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.822279565869849</v>
+        <v>4.905686808463678</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>4.194199280916656</v>
+        <v>4.278756533887041</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.760604359144502</v>
+        <v>4.844786978968671</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.043467993626159</v>
+        <v>4.128081371141114</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2.480687791279195</v>
+        <v>2.566963099905443</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.675319782107529</v>
+        <v>1.761942617619425</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>1.600132868860143</v>
+        <v>1.687740925878295</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.4435366209512708</v>
+        <v>0.5303030303030312</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>1.331296525922433</v>
+        <v>1.418283703544539</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>1.664233576642324</v>
+        <v>1.75139920410291</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.464356368101512</v>
+        <v>2.551232190866664</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>3.23539133086399</v>
+        <v>3.322019606674097</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>3.567939523990326</v>
+        <v>3.655385847467194</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>3.491957147459765</v>
+        <v>3.579539886058093</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>2.890895121014211</v>
+        <v>2.978102189781019</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>2.3769702585167</v>
+        <v>2.464313732178184</v>
       </c>
     </row>
     <row r="30">
@@ -3057,76 +3057,76 @@
         <v>685</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.7918923389473989</v>
+        <v>0.8117076310935829</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.449459820074374</v>
+        <v>1.498828642962742</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.92904430487183</v>
+        <v>2.980517623128826</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.090951154957196</v>
+        <v>3.143476012445213</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.747468185118656</v>
+        <v>3.82958335011692</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.226653272991008</v>
+        <v>4.308520339134013</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.205382255720878</v>
+        <v>5.288396472761903</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.780756276628523</v>
+        <v>4.864199626548974</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.822279565869849</v>
+        <v>4.905686808463678</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>4.194199280916656</v>
+        <v>4.278756533887041</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>4.760604359144502</v>
+        <v>4.844786978968671</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.043467993626159</v>
+        <v>4.128081371141114</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>2.480687791279195</v>
+        <v>2.566963099905443</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>1.675319782107529</v>
+        <v>1.761942617619425</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1.600132868860143</v>
+        <v>1.687740925878295</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.4435366209512708</v>
+        <v>0.5303030303030312</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>1.331296525922433</v>
+        <v>1.418283703544539</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>1.664233576642324</v>
+        <v>1.75139920410291</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>2.464356368101512</v>
+        <v>2.551232190866664</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>3.23539133086399</v>
+        <v>3.322019606674097</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>3.567939523990326</v>
+        <v>3.655385847467194</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>3.491957147459765</v>
+        <v>3.579539886058093</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>2.890895121014211</v>
+        <v>2.978102189781019</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>2.3769702585167</v>
+        <v>2.464313732178184</v>
       </c>
     </row>
     <row r="31">
@@ -3139,76 +3139,76 @@
         <v>685</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.7918923389473989</v>
+        <v>0.8117076310935829</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.449459820074374</v>
+        <v>1.498828642962742</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.92904430487183</v>
+        <v>2.980517623128826</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.090951154957196</v>
+        <v>3.143476012445213</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.747468185118656</v>
+        <v>3.82958335011692</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.226653272991008</v>
+        <v>4.308520339134013</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.205382255720878</v>
+        <v>5.288396472761903</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.780756276628523</v>
+        <v>4.864199626548974</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.822279565869849</v>
+        <v>4.905686808463678</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.194199280916656</v>
+        <v>4.278756533887041</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.760604359144502</v>
+        <v>4.844786978968671</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.043467993626159</v>
+        <v>4.128081371141114</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>2.480687791279195</v>
+        <v>2.566963099905443</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.675319782107529</v>
+        <v>1.761942617619425</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>1.600132868860143</v>
+        <v>1.687740925878295</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.4435366209512708</v>
+        <v>0.5303030303030312</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>1.331296525922433</v>
+        <v>1.418283703544539</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>1.664233576642324</v>
+        <v>1.75139920410291</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.464356368101512</v>
+        <v>2.551232190866664</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>3.23539133086399</v>
+        <v>3.322019606674097</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>3.567939523990326</v>
+        <v>3.655385847467194</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>3.491957147459765</v>
+        <v>3.579539886058093</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>2.890895121014211</v>
+        <v>2.978102189781019</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>2.3769702585167</v>
+        <v>2.464313732178184</v>
       </c>
     </row>
     <row r="32">
@@ -3221,76 +3221,76 @@
         <v>685</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.7918923389473989</v>
+        <v>0.8117076310935829</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.449459820074374</v>
+        <v>1.498828642962742</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.92904430487183</v>
+        <v>2.980517623128826</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.090951154957196</v>
+        <v>3.143476012445213</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.747468185118656</v>
+        <v>3.82958335011692</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.226653272991008</v>
+        <v>4.308520339134013</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.205382255720878</v>
+        <v>5.288396472761903</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.780756276628523</v>
+        <v>4.864199626548974</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.822279565869849</v>
+        <v>4.905686808463678</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>4.194199280916656</v>
+        <v>4.278756533887041</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.760604359144502</v>
+        <v>4.844786978968671</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4.043467993626159</v>
+        <v>4.128081371141114</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.480687791279195</v>
+        <v>2.566963099905443</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>1.675319782107529</v>
+        <v>1.761942617619425</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>1.600132868860143</v>
+        <v>1.687740925878295</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>0.4435366209512708</v>
+        <v>0.5303030303030312</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>1.331296525922433</v>
+        <v>1.418283703544539</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>1.664233576642324</v>
+        <v>1.75139920410291</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2.464356368101512</v>
+        <v>2.551232190866664</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>3.23539133086399</v>
+        <v>3.322019606674097</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>3.567939523990326</v>
+        <v>3.655385847467194</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>3.491957147459765</v>
+        <v>3.579539886058093</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>2.890895121014211</v>
+        <v>2.978102189781019</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>2.3769702585167</v>
+        <v>2.464313732178184</v>
       </c>
     </row>
     <row r="33">
@@ -3303,76 +3303,76 @@
         <v>685</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.7918923389473989</v>
+        <v>0.8117076310935829</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.449459820074374</v>
+        <v>1.498828642962742</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.92904430487183</v>
+        <v>2.980517623128826</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.090951154957196</v>
+        <v>3.143476012445213</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.747468185118656</v>
+        <v>3.82958335011692</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4.226653272991008</v>
+        <v>4.308520339134013</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.205382255720878</v>
+        <v>5.288396472761903</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>4.780756276628523</v>
+        <v>4.864199626548974</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4.822279565869849</v>
+        <v>4.905686808463678</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>4.194199280916656</v>
+        <v>4.278756533887041</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>4.760604359144502</v>
+        <v>4.844786978968671</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4.043467993626159</v>
+        <v>4.128081371141114</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.480687791279195</v>
+        <v>2.566963099905443</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.675319782107529</v>
+        <v>1.761942617619425</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>1.600132868860143</v>
+        <v>1.687740925878295</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>0.4435366209512708</v>
+        <v>0.5303030303030312</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>1.331296525922433</v>
+        <v>1.418283703544539</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>1.664233576642324</v>
+        <v>1.75139920410291</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>2.464356368101512</v>
+        <v>2.551232190866664</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>3.23539133086399</v>
+        <v>3.322019606674097</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>3.567939523990326</v>
+        <v>3.655385847467194</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>3.491957147459765</v>
+        <v>3.579539886058093</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>2.890895121014211</v>
+        <v>2.978102189781019</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>2.3769702585167</v>
+        <v>2.464313732178184</v>
       </c>
     </row>
     <row r="34">
@@ -3385,76 +3385,76 @@
         <v>685</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.7918923389473989</v>
+        <v>0.8117076310935829</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.449459820074374</v>
+        <v>1.498828642962742</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.92904430487183</v>
+        <v>2.980517623128826</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.090951154957196</v>
+        <v>3.143476012445213</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>3.747468185118656</v>
+        <v>3.82958335011692</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.226653272991008</v>
+        <v>4.308520339134013</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.205382255720878</v>
+        <v>5.288396472761903</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.780756276628523</v>
+        <v>4.864199626548974</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.822279565869849</v>
+        <v>4.905686808463678</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.194199280916656</v>
+        <v>4.278756533887041</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>4.760604359144502</v>
+        <v>4.844786978968671</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.043467993626159</v>
+        <v>4.128081371141114</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>2.480687791279195</v>
+        <v>2.566963099905443</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.675319782107529</v>
+        <v>1.761942617619425</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>1.600132868860143</v>
+        <v>1.687740925878295</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0.4435366209512708</v>
+        <v>0.5303030303030312</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>1.331296525922433</v>
+        <v>1.418283703544539</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>1.664233576642324</v>
+        <v>1.75139920410291</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>2.464356368101512</v>
+        <v>2.551232190866664</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>3.23539133086399</v>
+        <v>3.322019606674097</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>3.567939523990326</v>
+        <v>3.655385847467194</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>3.491957147459765</v>
+        <v>3.579539886058093</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>2.890895121014211</v>
+        <v>2.978102189781019</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>2.3769702585167</v>
+        <v>2.464313732178184</v>
       </c>
     </row>
     <row r="35">
@@ -3719,76 +3719,76 @@
         <v>665</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.279710024625764</v>
+        <v>-1.25989473247958</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.983326068003485</v>
+        <v>-2.933957245115117</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-3.155131182199433</v>
+        <v>-3.181500103669912</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.388077061624131</v>
+        <v>-4.489692218350747</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.07813490479657</v>
+        <v>-4.230244595659926</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-3.063875159195717</v>
+        <v>-3.299230790514933</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-3.007445636902155</v>
+        <v>-3.327131855357663</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.853469189713728</v>
+        <v>-2.184001663605173</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.480283410915177</v>
+        <v>-2.806482273135622</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.652845337929726</v>
+        <v>-2.900059216824879</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-1.776907303223091</v>
+        <v>-1.944626894015279</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-1.304207765113759</v>
+        <v>-1.390035482840645</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.827528003682673</v>
+        <v>-1.82750436025546</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.597826587466031</v>
+        <v>-1.511203751954135</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-1.50507540730473</v>
+        <v>-1.417467350286579</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.6090949579961062</v>
+        <v>-0.5223285486443459</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-2.547744141439409</v>
+        <v>-2.460756963817303</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-3.103891114647936</v>
+        <v>-3.016725487187351</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-4.241093387674795</v>
+        <v>-4.154217564909644</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-4.505127850300596</v>
+        <v>-4.41849957449049</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-4.14623642683565</v>
+        <v>-4.058790103358781</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-4.673346622915076</v>
+        <v>-4.585763884316748</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-4.398496240601503</v>
+        <v>-4.311289171834694</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-4.173713019020212</v>
+        <v>-4.086369545358728</v>
       </c>
     </row>
     <row r="8">
@@ -3801,76 +3801,76 @@
         <v>665</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.279710024625764</v>
+        <v>-1.25989473247958</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.983326068003485</v>
+        <v>-2.933957245115117</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.155131182199433</v>
+        <v>-3.181500103669912</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-4.388077061624131</v>
+        <v>-4.489692218350747</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-4.07813490479657</v>
+        <v>-4.230244595659926</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.063875159195717</v>
+        <v>-3.299230790514933</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.007445636902155</v>
+        <v>-3.327131855357663</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.853469189713728</v>
+        <v>-2.184001663605173</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-2.480283410915177</v>
+        <v>-2.806482273135622</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.652845337929726</v>
+        <v>-2.900059216824879</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.776907303223091</v>
+        <v>-1.944626894015279</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.304207765113759</v>
+        <v>-1.390035482840645</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.827528003682673</v>
+        <v>-1.82750436025546</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.597826587466031</v>
+        <v>-1.511203751954135</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-1.50507540730473</v>
+        <v>-1.417467350286579</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.6090949579961062</v>
+        <v>-0.5223285486443459</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-2.547744141439409</v>
+        <v>-2.460756963817303</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-3.103891114647936</v>
+        <v>-3.016725487187351</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-4.241093387674795</v>
+        <v>-4.154217564909644</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-4.505127850300596</v>
+        <v>-4.41849957449049</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-4.14623642683565</v>
+        <v>-4.058790103358781</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-4.673346622915076</v>
+        <v>-4.585763884316748</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-4.398496240601503</v>
+        <v>-4.311289171834694</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-4.173713019020212</v>
+        <v>-4.086369545358728</v>
       </c>
     </row>
     <row r="9">
@@ -3883,76 +3883,76 @@
         <v>665</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.279710024625764</v>
+        <v>-1.25989473247958</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.983326068003485</v>
+        <v>-2.933957245115117</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.155131182199433</v>
+        <v>-3.181500103669912</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.388077061624131</v>
+        <v>-4.489692218350747</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-4.07813490479657</v>
+        <v>-4.230244595659926</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-3.063875159195717</v>
+        <v>-3.299230790514933</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.007445636902155</v>
+        <v>-3.327131855357663</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.853469189713728</v>
+        <v>-2.184001663605173</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.480283410915177</v>
+        <v>-2.806482273135622</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.652845337929726</v>
+        <v>-2.900059216824879</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.776907303223091</v>
+        <v>-1.944626894015279</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.304207765113759</v>
+        <v>-1.390035482840645</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.827528003682673</v>
+        <v>-1.82750436025546</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.597826587466031</v>
+        <v>-1.511203751954135</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-1.50507540730473</v>
+        <v>-1.417467350286579</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.6090949579961062</v>
+        <v>-0.5223285486443459</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-2.547744141439409</v>
+        <v>-2.460756963817303</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-3.103891114647936</v>
+        <v>-3.016725487187351</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-4.241093387674795</v>
+        <v>-4.154217564909644</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-4.505127850300596</v>
+        <v>-4.41849957449049</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-4.14623642683565</v>
+        <v>-4.058790103358781</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-4.673346622915076</v>
+        <v>-4.585763884316748</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-4.398496240601503</v>
+        <v>-4.311289171834694</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-4.173713019020212</v>
+        <v>-4.086369545358728</v>
       </c>
     </row>
     <row r="10">
@@ -3965,76 +3965,76 @@
         <v>665</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.279710024625764</v>
+        <v>-1.25989473247958</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.983326068003485</v>
+        <v>-2.933957245115117</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.155131182199433</v>
+        <v>-3.181500103669912</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-4.388077061624131</v>
+        <v>-4.489692218350747</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.07813490479657</v>
+        <v>-4.230244595659926</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-3.063875159195717</v>
+        <v>-3.299230790514933</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.007445636902155</v>
+        <v>-3.327131855357663</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.853469189713728</v>
+        <v>-2.184001663605173</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.480283410915177</v>
+        <v>-2.806482273135622</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.652845337929726</v>
+        <v>-2.900059216824879</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.776907303223091</v>
+        <v>-1.944626894015279</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.304207765113759</v>
+        <v>-1.390035482840645</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.827528003682673</v>
+        <v>-1.82750436025546</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.597826587466031</v>
+        <v>-1.511203751954135</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-1.50507540730473</v>
+        <v>-1.417467350286579</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.6090949579961062</v>
+        <v>-0.5223285486443459</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-2.547744141439409</v>
+        <v>-2.460756963817303</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-3.103891114647936</v>
+        <v>-3.016725487187351</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-4.241093387674795</v>
+        <v>-4.154217564909644</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-4.505127850300596</v>
+        <v>-4.41849957449049</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-4.14623642683565</v>
+        <v>-4.058790103358781</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-4.673346622915076</v>
+        <v>-4.585763884316748</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-4.398496240601503</v>
+        <v>-4.311289171834694</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-4.173713019020212</v>
+        <v>-4.086369545358728</v>
       </c>
     </row>
     <row r="11">
@@ -4047,76 +4047,76 @@
         <v>665</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.279710024625764</v>
+        <v>-1.25989473247958</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.983326068003485</v>
+        <v>-2.933957245115117</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-3.155131182199433</v>
+        <v>-3.181500103669912</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-4.388077061624131</v>
+        <v>-4.489692218350747</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-4.07813490479657</v>
+        <v>-4.230244595659926</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.063875159195717</v>
+        <v>-3.299230790514933</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.007445636902155</v>
+        <v>-3.327131855357663</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.853469189713728</v>
+        <v>-2.184001663605173</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.480283410915177</v>
+        <v>-2.806482273135622</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.652845337929726</v>
+        <v>-2.900059216824879</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.776907303223091</v>
+        <v>-1.944626894015279</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.304207765113759</v>
+        <v>-1.390035482840645</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.827528003682673</v>
+        <v>-1.82750436025546</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.597826587466031</v>
+        <v>-1.511203751954135</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-1.50507540730473</v>
+        <v>-1.417467350286579</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.6090949579961062</v>
+        <v>-0.5223285486443459</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-2.547744141439409</v>
+        <v>-2.460756963817303</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-3.103891114647936</v>
+        <v>-3.016725487187351</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-4.241093387674795</v>
+        <v>-4.154217564909644</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-4.505127850300596</v>
+        <v>-4.41849957449049</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-4.14623642683565</v>
+        <v>-4.058790103358781</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-4.673346622915076</v>
+        <v>-4.585763884316748</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-4.398496240601503</v>
+        <v>-4.311289171834694</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-4.173713019020212</v>
+        <v>-4.086369545358728</v>
       </c>
     </row>
     <row r="12">
@@ -4129,76 +4129,76 @@
         <v>665</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.279710024625764</v>
+        <v>-1.25989473247958</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.983326068003485</v>
+        <v>-2.933957245115117</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.155131182199433</v>
+        <v>-3.181500103669912</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.388077061624131</v>
+        <v>-4.489692218350747</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-4.07813490479657</v>
+        <v>-4.230244595659926</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.063875159195717</v>
+        <v>-3.299230790514933</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.007445636902155</v>
+        <v>-3.327131855357663</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.853469189713728</v>
+        <v>-2.184001663605173</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.480283410915177</v>
+        <v>-2.806482273135622</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.652845337929726</v>
+        <v>-2.900059216824879</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.776907303223091</v>
+        <v>-1.944626894015279</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.304207765113759</v>
+        <v>-1.390035482840645</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.827528003682673</v>
+        <v>-1.82750436025546</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.597826587466031</v>
+        <v>-1.511203751954135</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1.50507540730473</v>
+        <v>-1.417467350286579</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.6090949579961062</v>
+        <v>-0.5223285486443459</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.547744141439409</v>
+        <v>-2.460756963817303</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-3.103891114647936</v>
+        <v>-3.016725487187351</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-4.241093387674795</v>
+        <v>-4.154217564909644</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-4.505127850300596</v>
+        <v>-4.41849957449049</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-4.14623642683565</v>
+        <v>-4.058790103358781</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-4.673346622915076</v>
+        <v>-4.585763884316748</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-4.398496240601503</v>
+        <v>-4.311289171834694</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-4.173713019020212</v>
+        <v>-4.086369545358728</v>
       </c>
     </row>
     <row r="13">
@@ -4211,76 +4211,76 @@
         <v>665</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.279710024625764</v>
+        <v>-1.25989473247958</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.983326068003485</v>
+        <v>-2.933957245115117</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.155131182199433</v>
+        <v>-3.181500103669912</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-4.388077061624131</v>
+        <v>-4.489692218350747</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.07813490479657</v>
+        <v>-4.230244595659926</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-3.063875159195717</v>
+        <v>-3.299230790514933</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-3.007445636902155</v>
+        <v>-3.327131855357663</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.853469189713728</v>
+        <v>-2.184001663605173</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.480283410915177</v>
+        <v>-2.806482273135622</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.652845337929726</v>
+        <v>-2.900059216824879</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.776907303223091</v>
+        <v>-1.944626894015279</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.304207765113759</v>
+        <v>-1.390035482840645</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.827528003682673</v>
+        <v>-1.82750436025546</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.597826587466031</v>
+        <v>-1.511203751954135</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-1.50507540730473</v>
+        <v>-1.417467350286579</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.6090949579961062</v>
+        <v>-0.5223285486443459</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-2.547744141439409</v>
+        <v>-2.460756963817303</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-3.103891114647936</v>
+        <v>-3.016725487187351</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-4.241093387674795</v>
+        <v>-4.154217564909644</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-4.505127850300596</v>
+        <v>-4.41849957449049</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-4.14623642683565</v>
+        <v>-4.058790103358781</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-4.673346622915076</v>
+        <v>-4.585763884316748</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-4.398496240601503</v>
+        <v>-4.311289171834694</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-4.173713019020212</v>
+        <v>-4.086369545358728</v>
       </c>
     </row>
     <row r="14">
@@ -4290,79 +4290,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.4232523336357019</v>
+        <v>-0.4508829557258736</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2586645727452606</v>
+        <v>0.1850647539284083</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.7308491387976659</v>
+        <v>0.6524015474427927</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.8504383641310227</v>
+        <v>0.7699547438824226</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.5262044529060219</v>
+        <v>0.4031768893970735</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.8268271906172941</v>
+        <v>0.7029959994816437</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.9621013814961614</v>
+        <v>0.8359993798578031</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.231611552633815</v>
+        <v>1.103813417331281</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.3749008594568508</v>
+        <v>0.2501523619083343</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1797063742015439</v>
+        <v>0.09594826348753571</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.3418072520822193</v>
+        <v>-0.382228225648042</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.6209874132210018</v>
+        <v>-0.6195031189647793</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.8775046094517904</v>
+        <v>-0.8334517393047918</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.098931012784028</v>
+        <v>-1.012308177272132</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.106829430568389</v>
+        <v>-1.019221373550238</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.018113161972032</v>
+        <v>-0.9313467526202714</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-2.165275669245901</v>
+        <v>-2.078288491623795</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-2.270294822905562</v>
+        <v>-2.183129195444977</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-2.56062593829882</v>
+        <v>-2.473750115533669</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-2.80768598224406</v>
+        <v>-2.721057706433953</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-2.772178996719113</v>
+        <v>-2.684732673242245</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-2.703443572960232</v>
+        <v>-2.615860834361904</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-2.50095209079138</v>
+        <v>-2.413745022024571</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.594128648971264</v>
+        <v>-1.548911573366517</v>
       </c>
     </row>
     <row r="15">
@@ -4372,79 +4372,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.4232523336357019</v>
+        <v>-0.4508829557258736</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2586645727452606</v>
+        <v>0.1850647539284083</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.7308491387976659</v>
+        <v>0.6524015474427927</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.8504383641310227</v>
+        <v>0.7699547438824226</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.5262044529060219</v>
+        <v>0.4031768893970735</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.8268271906172941</v>
+        <v>0.7029959994816437</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.9621013814961614</v>
+        <v>0.8359993798578031</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.231611552633815</v>
+        <v>1.103813417331281</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.3749008594568508</v>
+        <v>0.2501523619083343</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.1797063742015439</v>
+        <v>0.09594826348753571</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.3418072520822193</v>
+        <v>-0.382228225648042</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.6209874132210018</v>
+        <v>-0.6195031189647793</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.8775046094517904</v>
+        <v>-0.8334517393047918</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.098931012784028</v>
+        <v>-1.012308177272132</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.106829430568389</v>
+        <v>-1.019221373550238</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-1.018113161972032</v>
+        <v>-0.9313467526202714</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-2.165275669245901</v>
+        <v>-2.078288491623795</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.270294822905562</v>
+        <v>-2.183129195444977</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-2.56062593829882</v>
+        <v>-2.473750115533669</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-2.80768598224406</v>
+        <v>-2.721057706433953</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-2.772178996719113</v>
+        <v>-2.684732673242245</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-2.703443572960232</v>
+        <v>-2.615860834361904</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-2.50095209079138</v>
+        <v>-2.413745022024571</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-1.594128648971264</v>
+        <v>-1.548911573366517</v>
       </c>
     </row>
     <row r="16">
@@ -4454,79 +4454,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.4232523336357019</v>
+        <v>-0.4508829557258736</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2586645727452606</v>
+        <v>0.1850647539284083</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.7308491387976659</v>
+        <v>0.6524015474427927</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.8504383641310227</v>
+        <v>0.7699547438824226</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.5262044529060219</v>
+        <v>0.4031768893970735</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.8268271906172941</v>
+        <v>0.7029959994816437</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.9621013814961614</v>
+        <v>0.8359993798578031</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.231611552633815</v>
+        <v>1.103813417331281</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.3749008594568508</v>
+        <v>0.2501523619083343</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1797063742015439</v>
+        <v>0.09594826348753571</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.3418072520822193</v>
+        <v>-0.382228225648042</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.6209874132210018</v>
+        <v>-0.6195031189647793</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.8775046094517904</v>
+        <v>-0.8334517393047918</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.098931012784028</v>
+        <v>-1.012308177272132</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-1.106829430568389</v>
+        <v>-1.019221373550238</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-1.018113161972032</v>
+        <v>-0.9313467526202714</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-2.165275669245901</v>
+        <v>-2.078288491623795</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.270294822905562</v>
+        <v>-2.183129195444977</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-2.56062593829882</v>
+        <v>-2.473750115533669</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-2.80768598224406</v>
+        <v>-2.721057706433953</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-2.772178996719113</v>
+        <v>-2.684732673242245</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-2.703443572960232</v>
+        <v>-2.615860834361904</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-2.50095209079138</v>
+        <v>-2.413745022024571</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.594128648971264</v>
+        <v>-1.548911573366517</v>
       </c>
     </row>
     <row r="17">
@@ -4536,79 +4536,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4232523336357019</v>
+        <v>-0.4508829557258736</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2586645727452606</v>
+        <v>0.1850647539284083</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.7308491387976659</v>
+        <v>0.6524015474427927</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.8504383641310227</v>
+        <v>0.7699547438824226</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.5262044529060219</v>
+        <v>0.4031768893970735</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.8268271906172941</v>
+        <v>0.7029959994816437</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.9621013814961614</v>
+        <v>0.8359993798578031</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.231611552633815</v>
+        <v>1.103813417331281</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.3749008594568508</v>
+        <v>0.2501523619083343</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.1797063742015439</v>
+        <v>0.09594826348753571</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.3418072520822193</v>
+        <v>-0.382228225648042</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.6209874132210018</v>
+        <v>-0.6195031189647793</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.8775046094517904</v>
+        <v>-0.8334517393047918</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.098931012784028</v>
+        <v>-1.012308177272132</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.106829430568389</v>
+        <v>-1.019221373550238</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.018113161972032</v>
+        <v>-0.9313467526202714</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-2.165275669245901</v>
+        <v>-2.078288491623795</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-2.270294822905562</v>
+        <v>-2.183129195444977</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-2.56062593829882</v>
+        <v>-2.473750115533669</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-2.80768598224406</v>
+        <v>-2.721057706433953</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-2.772178996719113</v>
+        <v>-2.684732673242245</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-2.703443572960232</v>
+        <v>-2.615860834361904</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-2.50095209079138</v>
+        <v>-2.413745022024571</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.594128648971264</v>
+        <v>-1.548911573366517</v>
       </c>
     </row>
     <row r="18">
@@ -4618,79 +4618,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.4232523336357019</v>
+        <v>-0.4508829557258736</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2586645727452606</v>
+        <v>0.1850647539284083</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7308491387976659</v>
+        <v>0.6524015474427927</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.8504383641310227</v>
+        <v>0.7699547438824226</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.5262044529060219</v>
+        <v>0.4031768893970735</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.8268271906172941</v>
+        <v>0.7029959994816437</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.9621013814961614</v>
+        <v>0.8359993798578031</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.231611552633815</v>
+        <v>1.103813417331281</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.3749008594568508</v>
+        <v>0.2501523619083343</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.1797063742015439</v>
+        <v>0.09594826348753571</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.3418072520822193</v>
+        <v>-0.382228225648042</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.6209874132210018</v>
+        <v>-0.6195031189647793</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.8775046094517904</v>
+        <v>-0.8334517393047918</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.098931012784028</v>
+        <v>-1.012308177272132</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.106829430568389</v>
+        <v>-1.019221373550238</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.018113161972032</v>
+        <v>-0.9313467526202714</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-2.165275669245901</v>
+        <v>-2.078288491623795</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-2.270294822905562</v>
+        <v>-2.183129195444977</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-2.56062593829882</v>
+        <v>-2.473750115533669</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-2.80768598224406</v>
+        <v>-2.721057706433953</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-2.772178996719113</v>
+        <v>-2.684732673242245</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-2.703443572960232</v>
+        <v>-2.615860834361904</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-2.50095209079138</v>
+        <v>-2.413745022024571</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.594128648971264</v>
+        <v>-1.548911573366517</v>
       </c>
     </row>
     <row r="19">
@@ -4700,79 +4700,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.4232523336357019</v>
+        <v>-0.4508829557258736</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2586645727452606</v>
+        <v>0.1850647539284083</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.7308491387976659</v>
+        <v>0.6524015474427927</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.8504383641310227</v>
+        <v>0.7699547438824226</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.5262044529060219</v>
+        <v>0.4031768893970735</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.8268271906172941</v>
+        <v>0.7029959994816437</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.9621013814961614</v>
+        <v>0.8359993798578031</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.231611552633815</v>
+        <v>1.103813417331281</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.3749008594568508</v>
+        <v>0.2501523619083343</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.1797063742015439</v>
+        <v>0.09594826348753571</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.3418072520822193</v>
+        <v>-0.382228225648042</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.6209874132210018</v>
+        <v>-0.6195031189647793</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.8775046094517904</v>
+        <v>-0.8334517393047918</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.098931012784028</v>
+        <v>-1.012308177272132</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-1.106829430568389</v>
+        <v>-1.019221373550238</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-1.018113161972032</v>
+        <v>-0.9313467526202714</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-2.165275669245901</v>
+        <v>-2.078288491623795</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.270294822905562</v>
+        <v>-2.183129195444977</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-2.56062593829882</v>
+        <v>-2.473750115533669</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-2.80768598224406</v>
+        <v>-2.721057706433953</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-2.772178996719113</v>
+        <v>-2.684732673242245</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-2.703443572960232</v>
+        <v>-2.615860834361904</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-2.50095209079138</v>
+        <v>-2.413745022024571</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.594128648971264</v>
+        <v>-1.548911573366517</v>
       </c>
     </row>
     <row r="20">
@@ -4782,79 +4782,79 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.4232523336357019</v>
+        <v>-0.4508829557258736</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2586645727452606</v>
+        <v>0.1850647539284083</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.7308491387976659</v>
+        <v>0.6524015474427927</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.8504383641310227</v>
+        <v>0.7699547438824226</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.5262044529060219</v>
+        <v>0.4031768893970735</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.8268271906172941</v>
+        <v>0.7029959994816437</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.9621013814961614</v>
+        <v>0.8359993798578031</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.231611552633815</v>
+        <v>1.103813417331281</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.3749008594568508</v>
+        <v>0.2501523619083343</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1797063742015439</v>
+        <v>0.09594826348753571</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.3418072520822193</v>
+        <v>-0.382228225648042</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.6209874132210018</v>
+        <v>-0.6195031189647793</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.8775046094517904</v>
+        <v>-0.8334517393047918</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.098931012784028</v>
+        <v>-1.012308177272132</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.106829430568389</v>
+        <v>-1.019221373550238</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-1.018113161972032</v>
+        <v>-0.9313467526202714</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-2.165275669245901</v>
+        <v>-2.078288491623795</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-2.270294822905562</v>
+        <v>-2.183129195444977</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-2.56062593829882</v>
+        <v>-2.473750115533669</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-2.80768598224406</v>
+        <v>-2.721057706433953</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-2.772178996719113</v>
+        <v>-2.684732673242245</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-2.703443572960232</v>
+        <v>-2.615860834361904</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-2.50095209079138</v>
+        <v>-2.413745022024571</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.594128648971264</v>
+        <v>-1.548911573366517</v>
       </c>
     </row>
     <row r="21">
@@ -4864,79 +4864,79 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2073</v>
+        <v>2078</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.00137684765305579</v>
+        <v>-0.01142973043292272</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.1895666523030357</v>
+        <v>0.1571997862593051</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.3141819235355072</v>
+        <v>-0.3467213546942247</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.1008398113456295</v>
+        <v>0.06661201065792</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.8130877496955407</v>
+        <v>-0.8643013284008703</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.078977392349373</v>
+        <v>-1.129418394517756</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.537489304458674</v>
+        <v>-1.587599835653229</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.213059327401851</v>
+        <v>-1.264249339766657</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.769231393557995</v>
+        <v>-1.819089419570268</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.630274494675504</v>
+        <v>-1.654132191628896</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.124701343826764</v>
+        <v>-2.120762147500635</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.259720044129416</v>
+        <v>-2.228766381433601</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.039037074292878</v>
+        <v>-1.980250766604165</v>
       </c>
       <c r="P21" s="4" t="n">
+        <v>-2.17384064211322</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>-2.159230455791814</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>-1.564843533848823</v>
+      </c>
+      <c r="S21" s="4" t="n">
+        <v>-2.227352693892129</v>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>-2.043870476041029</v>
+      </c>
+      <c r="U21" s="4" t="n">
         <v>-2.260463477625116</v>
       </c>
-      <c r="Q21" s="4" t="n">
-        <v>-2.246838512809965</v>
-      </c>
-      <c r="R21" s="4" t="n">
-        <v>-1.651609943200583</v>
-      </c>
-      <c r="S21" s="4" t="n">
-        <v>-2.286755130450402</v>
-      </c>
-      <c r="T21" s="4" t="n">
-        <v>-2.075562717898492</v>
-      </c>
-      <c r="U21" s="4" t="n">
-        <v>-2.26471355455012</v>
-      </c>
       <c r="V21" s="4" t="n">
-        <v>-2.483342525167828</v>
+        <v>-2.506102050165502</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-2.276750573473919</v>
+        <v>-2.327840913950851</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-1.939403330950221</v>
+        <v>-1.991417441286089</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.829416840075119</v>
+        <v>-1.881477268338578</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.298580179685985</v>
+        <v>-1.352031293569475</v>
       </c>
     </row>
     <row r="22">
@@ -4946,79 +4946,79 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2073</v>
+        <v>2078</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.00137684765305579</v>
+        <v>-0.01142973043292272</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.1895666523030357</v>
+        <v>0.1571997862593051</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.3141819235355072</v>
+        <v>-0.3467213546942247</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.1008398113456295</v>
+        <v>0.06661201065792</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.8130877496955407</v>
+        <v>-0.8643013284008703</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.078977392349373</v>
+        <v>-1.129418394517756</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.537489304458674</v>
+        <v>-1.587599835653229</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.213059327401851</v>
+        <v>-1.264249339766657</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.769231393557995</v>
+        <v>-1.819089419570268</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.630274494675504</v>
+        <v>-1.654132191628896</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.124701343826764</v>
+        <v>-2.120762147500635</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.259720044129416</v>
+        <v>-2.228766381433601</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.039037074292878</v>
+        <v>-1.980250766604165</v>
       </c>
       <c r="P22" s="4" t="n">
+        <v>-2.17384064211322</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>-2.159230455791814</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>-1.564843533848823</v>
+      </c>
+      <c r="S22" s="4" t="n">
+        <v>-2.227352693892129</v>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>-2.043870476041029</v>
+      </c>
+      <c r="U22" s="4" t="n">
         <v>-2.260463477625116</v>
       </c>
-      <c r="Q22" s="4" t="n">
-        <v>-2.246838512809965</v>
-      </c>
-      <c r="R22" s="4" t="n">
-        <v>-1.651609943200583</v>
-      </c>
-      <c r="S22" s="4" t="n">
-        <v>-2.286755130450402</v>
-      </c>
-      <c r="T22" s="4" t="n">
-        <v>-2.075562717898492</v>
-      </c>
-      <c r="U22" s="4" t="n">
-        <v>-2.26471355455012</v>
-      </c>
       <c r="V22" s="4" t="n">
-        <v>-2.483342525167828</v>
+        <v>-2.506102050165502</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-2.276750573473919</v>
+        <v>-2.327840913950851</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.939403330950221</v>
+        <v>-1.991417441286089</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.829416840075119</v>
+        <v>-1.881477268338578</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.298580179685985</v>
+        <v>-1.352031293569475</v>
       </c>
     </row>
     <row r="23">
@@ -5028,79 +5028,79 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2073</v>
+        <v>2078</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.00137684765305579</v>
+        <v>-0.01142973043292272</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1895666523030357</v>
+        <v>0.1571997862593051</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3141819235355072</v>
+        <v>-0.3467213546942247</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.1008398113456295</v>
+        <v>0.06661201065792</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.8130877496955407</v>
+        <v>-0.8643013284008703</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.078977392349373</v>
+        <v>-1.129418394517756</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.537489304458674</v>
+        <v>-1.587599835653229</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.213059327401851</v>
+        <v>-1.264249339766657</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.769231393557995</v>
+        <v>-1.819089419570268</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.630274494675504</v>
+        <v>-1.654132191628896</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.124701343826764</v>
+        <v>-2.120762147500635</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.259720044129416</v>
+        <v>-2.228766381433601</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.039037074292878</v>
+        <v>-1.980250766604165</v>
       </c>
       <c r="P23" s="4" t="n">
+        <v>-2.17384064211322</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>-2.159230455791814</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>-1.564843533848823</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>-2.227352693892129</v>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>-2.043870476041029</v>
+      </c>
+      <c r="U23" s="4" t="n">
         <v>-2.260463477625116</v>
       </c>
-      <c r="Q23" s="4" t="n">
-        <v>-2.246838512809965</v>
-      </c>
-      <c r="R23" s="4" t="n">
-        <v>-1.651609943200583</v>
-      </c>
-      <c r="S23" s="4" t="n">
-        <v>-2.286755130450402</v>
-      </c>
-      <c r="T23" s="4" t="n">
-        <v>-2.075562717898492</v>
-      </c>
-      <c r="U23" s="4" t="n">
-        <v>-2.26471355455012</v>
-      </c>
       <c r="V23" s="4" t="n">
-        <v>-2.483342525167828</v>
+        <v>-2.506102050165502</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.276750573473919</v>
+        <v>-2.327840913950851</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.939403330950221</v>
+        <v>-1.991417441286089</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.829416840075119</v>
+        <v>-1.881477268338578</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.298580179685985</v>
+        <v>-1.352031293569475</v>
       </c>
     </row>
     <row r="24">
@@ -5110,79 +5110,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2073</v>
+        <v>2078</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.00137684765305579</v>
+        <v>-0.01142973043292272</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.1895666523030357</v>
+        <v>0.1571997862593051</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.3141819235355072</v>
+        <v>-0.3467213546942247</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.1008398113456295</v>
+        <v>0.06661201065792</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.8130877496955407</v>
+        <v>-0.8643013284008703</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.078977392349373</v>
+        <v>-1.129418394517756</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.537489304458674</v>
+        <v>-1.587599835653229</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.213059327401851</v>
+        <v>-1.264249339766657</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.769231393557995</v>
+        <v>-1.819089419570268</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.630274494675504</v>
+        <v>-1.654132191628896</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.124701343826764</v>
+        <v>-2.120762147500635</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.259720044129416</v>
+        <v>-2.228766381433601</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.039037074292878</v>
+        <v>-1.980250766604165</v>
       </c>
       <c r="P24" s="4" t="n">
+        <v>-2.17384064211322</v>
+      </c>
+      <c r="Q24" s="4" t="n">
+        <v>-2.159230455791814</v>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>-1.564843533848823</v>
+      </c>
+      <c r="S24" s="4" t="n">
+        <v>-2.227352693892129</v>
+      </c>
+      <c r="T24" s="4" t="n">
+        <v>-2.043870476041029</v>
+      </c>
+      <c r="U24" s="4" t="n">
         <v>-2.260463477625116</v>
       </c>
-      <c r="Q24" s="4" t="n">
-        <v>-2.246838512809965</v>
-      </c>
-      <c r="R24" s="4" t="n">
-        <v>-1.651609943200583</v>
-      </c>
-      <c r="S24" s="4" t="n">
-        <v>-2.286755130450402</v>
-      </c>
-      <c r="T24" s="4" t="n">
-        <v>-2.075562717898492</v>
-      </c>
-      <c r="U24" s="4" t="n">
-        <v>-2.26471355455012</v>
-      </c>
       <c r="V24" s="4" t="n">
-        <v>-2.483342525167828</v>
+        <v>-2.506102050165502</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-2.276750573473919</v>
+        <v>-2.327840913950851</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.939403330950221</v>
+        <v>-1.991417441286089</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.829416840075119</v>
+        <v>-1.881477268338578</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.298580179685985</v>
+        <v>-1.352031293569475</v>
       </c>
     </row>
     <row r="25">
@@ -5192,79 +5192,79 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2073</v>
+        <v>2078</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.00137684765305579</v>
+        <v>-0.01142973043292272</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.1895666523030357</v>
+        <v>0.1571997862593051</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.3141819235355072</v>
+        <v>-0.3467213546942247</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.1008398113456295</v>
+        <v>0.06661201065792</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.8130877496955407</v>
+        <v>-0.8643013284008703</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.078977392349373</v>
+        <v>-1.129418394517756</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.537489304458674</v>
+        <v>-1.587599835653229</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.213059327401851</v>
+        <v>-1.264249339766657</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.769231393557995</v>
+        <v>-1.819089419570268</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.630274494675504</v>
+        <v>-1.654132191628896</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.124701343826764</v>
+        <v>-2.120762147500635</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.259720044129416</v>
+        <v>-2.228766381433601</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.039037074292878</v>
+        <v>-1.980250766604165</v>
       </c>
       <c r="P25" s="4" t="n">
+        <v>-2.17384064211322</v>
+      </c>
+      <c r="Q25" s="4" t="n">
+        <v>-2.159230455791814</v>
+      </c>
+      <c r="R25" s="4" t="n">
+        <v>-1.564843533848823</v>
+      </c>
+      <c r="S25" s="4" t="n">
+        <v>-2.227352693892129</v>
+      </c>
+      <c r="T25" s="4" t="n">
+        <v>-2.043870476041029</v>
+      </c>
+      <c r="U25" s="4" t="n">
         <v>-2.260463477625116</v>
       </c>
-      <c r="Q25" s="4" t="n">
-        <v>-2.246838512809965</v>
-      </c>
-      <c r="R25" s="4" t="n">
-        <v>-1.651609943200583</v>
-      </c>
-      <c r="S25" s="4" t="n">
-        <v>-2.286755130450402</v>
-      </c>
-      <c r="T25" s="4" t="n">
-        <v>-2.075562717898492</v>
-      </c>
-      <c r="U25" s="4" t="n">
-        <v>-2.26471355455012</v>
-      </c>
       <c r="V25" s="4" t="n">
-        <v>-2.483342525167828</v>
+        <v>-2.506102050165502</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-2.276750573473919</v>
+        <v>-2.327840913950851</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.939403330950221</v>
+        <v>-1.991417441286089</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.829416840075119</v>
+        <v>-1.881477268338578</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.298580179685985</v>
+        <v>-1.352031293569475</v>
       </c>
     </row>
     <row r="26">
@@ -5274,79 +5274,79 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2073</v>
+        <v>2078</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.00137684765305579</v>
+        <v>-0.01142973043292272</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.1895666523030357</v>
+        <v>0.1571997862593051</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.3141819235355072</v>
+        <v>-0.3467213546942247</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.1008398113456295</v>
+        <v>0.06661201065792</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.8130877496955407</v>
+        <v>-0.8643013284008703</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.078977392349373</v>
+        <v>-1.129418394517756</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.537489304458674</v>
+        <v>-1.587599835653229</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.213059327401851</v>
+        <v>-1.264249339766657</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.769231393557995</v>
+        <v>-1.819089419570268</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.630274494675504</v>
+        <v>-1.654132191628896</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.124701343826764</v>
+        <v>-2.120762147500635</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.259720044129416</v>
+        <v>-2.228766381433601</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.039037074292878</v>
+        <v>-1.980250766604165</v>
       </c>
       <c r="P26" s="4" t="n">
+        <v>-2.17384064211322</v>
+      </c>
+      <c r="Q26" s="4" t="n">
+        <v>-2.159230455791814</v>
+      </c>
+      <c r="R26" s="4" t="n">
+        <v>-1.564843533848823</v>
+      </c>
+      <c r="S26" s="4" t="n">
+        <v>-2.227352693892129</v>
+      </c>
+      <c r="T26" s="4" t="n">
+        <v>-2.043870476041029</v>
+      </c>
+      <c r="U26" s="4" t="n">
         <v>-2.260463477625116</v>
       </c>
-      <c r="Q26" s="4" t="n">
-        <v>-2.246838512809965</v>
-      </c>
-      <c r="R26" s="4" t="n">
-        <v>-1.651609943200583</v>
-      </c>
-      <c r="S26" s="4" t="n">
-        <v>-2.286755130450402</v>
-      </c>
-      <c r="T26" s="4" t="n">
-        <v>-2.075562717898492</v>
-      </c>
-      <c r="U26" s="4" t="n">
-        <v>-2.26471355455012</v>
-      </c>
       <c r="V26" s="4" t="n">
-        <v>-2.483342525167828</v>
+        <v>-2.506102050165502</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-2.276750573473919</v>
+        <v>-2.327840913950851</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.939403330950221</v>
+        <v>-1.991417441286089</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.829416840075119</v>
+        <v>-1.881477268338578</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.298580179685985</v>
+        <v>-1.352031293569475</v>
       </c>
     </row>
     <row r="27">
@@ -5356,79 +5356,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2073</v>
+        <v>2078</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.00137684765305579</v>
+        <v>-0.01142973043292272</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1895666523030357</v>
+        <v>0.1571997862593051</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.3141819235355072</v>
+        <v>-0.3467213546942247</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.1008398113456295</v>
+        <v>0.06661201065792</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.8130877496955407</v>
+        <v>-0.8643013284008703</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.078977392349373</v>
+        <v>-1.129418394517756</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.537489304458674</v>
+        <v>-1.587599835653229</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.213059327401851</v>
+        <v>-1.264249339766657</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.769231393557995</v>
+        <v>-1.819089419570268</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.630274494675504</v>
+        <v>-1.654132191628896</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.124701343826764</v>
+        <v>-2.120762147500635</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.259720044129416</v>
+        <v>-2.228766381433601</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.039037074292878</v>
+        <v>-1.980250766604165</v>
       </c>
       <c r="P27" s="4" t="n">
+        <v>-2.17384064211322</v>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>-2.159230455791814</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>-1.564843533848823</v>
+      </c>
+      <c r="S27" s="4" t="n">
+        <v>-2.227352693892129</v>
+      </c>
+      <c r="T27" s="4" t="n">
+        <v>-2.043870476041029</v>
+      </c>
+      <c r="U27" s="4" t="n">
         <v>-2.260463477625116</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>-2.246838512809965</v>
-      </c>
-      <c r="R27" s="4" t="n">
-        <v>-1.651609943200583</v>
-      </c>
-      <c r="S27" s="4" t="n">
-        <v>-2.286755130450402</v>
-      </c>
-      <c r="T27" s="4" t="n">
-        <v>-2.075562717898492</v>
-      </c>
-      <c r="U27" s="4" t="n">
-        <v>-2.26471355455012</v>
-      </c>
       <c r="V27" s="4" t="n">
-        <v>-2.483342525167828</v>
+        <v>-2.506102050165502</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-2.276750573473919</v>
+        <v>-2.327840913950851</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.939403330950221</v>
+        <v>-1.991417441286089</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.829416840075119</v>
+        <v>-1.881477268338578</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.298580179685985</v>
+        <v>-1.352031293569475</v>
       </c>
     </row>
     <row r="28">
@@ -5438,79 +5438,79 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2734</v>
+        <v>2739</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1967523584254423</v>
+        <v>-0.2013105457274094</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.3602612397499811</v>
+        <v>-0.3718571606046766</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.7282741738066036</v>
+        <v>-0.7397299173345075</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.7688095646861584</v>
+        <v>-0.7804570744925527</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.9324430464243676</v>
+        <v>-0.9511474237962645</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.052055774708876</v>
+        <v>-1.070488368627792</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.2961420738527</v>
+        <v>-1.314423651611726</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.190842927087459</v>
+        <v>-1.209428945258097</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.201622954754768</v>
+        <v>-1.220187169134931</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.04549727344537</v>
+        <v>-1.06463793160647</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.187118305793227</v>
+        <v>-1.205915363587764</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.008658257696261</v>
+        <v>-1.027893761988977</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.6190423085705703</v>
+        <v>-0.6394071721582648</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.4182194062476867</v>
+        <v>-0.4390435405854163</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.3995957036708688</v>
+        <v>-0.4207068901843627</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.1108032769334812</v>
+        <v>-0.1322379234647144</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.3327027071349349</v>
+        <v>-0.3537961897043047</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.4160583941605935</v>
+        <v>-0.4370522604045419</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.6163140241509879</v>
+        <v>-0.6368782983759615</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.8094386638574989</v>
+        <v>-0.8295965842405337</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.8929625772500458</v>
+        <v>-0.9131799071900204</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.8742655869919318</v>
+        <v>-0.8945584903136776</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.724045030308865</v>
+        <v>-0.7445255474452495</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.5955466814498749</v>
+        <v>-0.6163033612785895</v>
       </c>
     </row>
     <row r="29">
@@ -5520,79 +5520,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2734</v>
+        <v>2739</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1967523584254423</v>
+        <v>-0.2013105457274094</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.3602612397499811</v>
+        <v>-0.3718571606046766</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.7282741738066036</v>
+        <v>-0.7397299173345075</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.7688095646861584</v>
+        <v>-0.7804570744925527</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.9324430464243676</v>
+        <v>-0.9511474237962645</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.052055774708876</v>
+        <v>-1.070488368627792</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.2961420738527</v>
+        <v>-1.314423651611726</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.190842927087459</v>
+        <v>-1.209428945258097</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.201622954754768</v>
+        <v>-1.220187169134931</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.04549727344537</v>
+        <v>-1.06463793160647</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.187118305793227</v>
+        <v>-1.205915363587764</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.008658257696261</v>
+        <v>-1.027893761988977</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.6190423085705703</v>
+        <v>-0.6394071721582648</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.4182194062476867</v>
+        <v>-0.4390435405854163</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.3995957036708688</v>
+        <v>-0.4207068901843627</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.1108032769334812</v>
+        <v>-0.1322379234647144</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.3327027071349349</v>
+        <v>-0.3537961897043047</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.4160583941605935</v>
+        <v>-0.4370522604045419</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.6163140241509879</v>
+        <v>-0.6368782983759615</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.8094386638574989</v>
+        <v>-0.8295965842405337</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.8929625772500458</v>
+        <v>-0.9131799071900204</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.8742655869919318</v>
+        <v>-0.8945584903136776</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.724045030308865</v>
+        <v>-0.7445255474452495</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.5955466814498749</v>
+        <v>-0.6163033612785895</v>
       </c>
     </row>
     <row r="30">
@@ -5602,79 +5602,79 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2734</v>
+        <v>2739</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1967523584254423</v>
+        <v>-0.2013105457274094</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3602612397499811</v>
+        <v>-0.3718571606046766</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7282741738066036</v>
+        <v>-0.7397299173345075</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.7688095646861584</v>
+        <v>-0.7804570744925527</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.9324430464243676</v>
+        <v>-0.9511474237962645</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.052055774708876</v>
+        <v>-1.070488368627792</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.2961420738527</v>
+        <v>-1.314423651611726</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.190842927087459</v>
+        <v>-1.209428945258097</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.201622954754768</v>
+        <v>-1.220187169134931</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.04549727344537</v>
+        <v>-1.06463793160647</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.187118305793227</v>
+        <v>-1.205915363587764</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.008658257696261</v>
+        <v>-1.027893761988977</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.6190423085705703</v>
+        <v>-0.6394071721582648</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.4182194062476867</v>
+        <v>-0.4390435405854163</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.3995957036708688</v>
+        <v>-0.4207068901843627</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.1108032769334812</v>
+        <v>-0.1322379234647144</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.3327027071349349</v>
+        <v>-0.3537961897043047</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.4160583941605935</v>
+        <v>-0.4370522604045419</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.6163140241509879</v>
+        <v>-0.6368782983759615</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.8094386638574989</v>
+        <v>-0.8295965842405337</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.8929625772500458</v>
+        <v>-0.9131799071900204</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.8742655869919318</v>
+        <v>-0.8945584903136776</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.724045030308865</v>
+        <v>-0.7445255474452495</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.5955466814498749</v>
+        <v>-0.6163033612785895</v>
       </c>
     </row>
     <row r="31">
@@ -5684,79 +5684,79 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2734</v>
+        <v>2739</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1967523584254423</v>
+        <v>-0.2013105457274094</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3602612397499811</v>
+        <v>-0.3718571606046766</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.7282741738066036</v>
+        <v>-0.7397299173345075</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.7688095646861584</v>
+        <v>-0.7804570744925527</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.9324430464243676</v>
+        <v>-0.9511474237962645</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.052055774708876</v>
+        <v>-1.070488368627792</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.2961420738527</v>
+        <v>-1.314423651611726</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.190842927087459</v>
+        <v>-1.209428945258097</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.201622954754768</v>
+        <v>-1.220187169134931</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.04549727344537</v>
+        <v>-1.06463793160647</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.187118305793227</v>
+        <v>-1.205915363587764</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.008658257696261</v>
+        <v>-1.027893761988977</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.6190423085705703</v>
+        <v>-0.6394071721582648</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.4182194062476867</v>
+        <v>-0.4390435405854163</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.3995957036708688</v>
+        <v>-0.4207068901843627</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.1108032769334812</v>
+        <v>-0.1322379234647144</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.3327027071349349</v>
+        <v>-0.3537961897043047</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.4160583941605935</v>
+        <v>-0.4370522604045419</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.6163140241509879</v>
+        <v>-0.6368782983759615</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.8094386638574989</v>
+        <v>-0.8295965842405337</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.8929625772500458</v>
+        <v>-0.9131799071900204</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.8742655869919318</v>
+        <v>-0.8945584903136776</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.724045030308865</v>
+        <v>-0.7445255474452495</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.5955466814498749</v>
+        <v>-0.6163033612785895</v>
       </c>
     </row>
     <row r="32">
@@ -5766,79 +5766,79 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2734</v>
+        <v>2739</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1967523584254423</v>
+        <v>-0.2013105457274094</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.3602612397499811</v>
+        <v>-0.3718571606046766</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.7282741738066036</v>
+        <v>-0.7397299173345075</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.7688095646861584</v>
+        <v>-0.7804570744925527</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.9324430464243676</v>
+        <v>-0.9511474237962645</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.052055774708876</v>
+        <v>-1.070488368627792</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.2961420738527</v>
+        <v>-1.314423651611726</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.190842927087459</v>
+        <v>-1.209428945258097</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.201622954754768</v>
+        <v>-1.220187169134931</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.04549727344537</v>
+        <v>-1.06463793160647</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.187118305793227</v>
+        <v>-1.205915363587764</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.008658257696261</v>
+        <v>-1.027893761988977</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.6190423085705703</v>
+        <v>-0.6394071721582648</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.4182194062476867</v>
+        <v>-0.4390435405854163</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.3995957036708688</v>
+        <v>-0.4207068901843627</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.1108032769334812</v>
+        <v>-0.1322379234647144</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.3327027071349349</v>
+        <v>-0.3537961897043047</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.4160583941605935</v>
+        <v>-0.4370522604045419</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.6163140241509879</v>
+        <v>-0.6368782983759615</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.8094386638574989</v>
+        <v>-0.8295965842405337</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.8929625772500458</v>
+        <v>-0.9131799071900204</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.8742655869919318</v>
+        <v>-0.8945584903136776</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.724045030308865</v>
+        <v>-0.7445255474452495</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.5955466814498749</v>
+        <v>-0.6163033612785895</v>
       </c>
     </row>
     <row r="33">
@@ -5848,79 +5848,79 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2734</v>
+        <v>2739</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1967523584254423</v>
+        <v>-0.2013105457274094</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.3602612397499811</v>
+        <v>-0.3718571606046766</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.7282741738066036</v>
+        <v>-0.7397299173345075</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.7688095646861584</v>
+        <v>-0.7804570744925527</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.9324430464243676</v>
+        <v>-0.9511474237962645</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.052055774708876</v>
+        <v>-1.070488368627792</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.2961420738527</v>
+        <v>-1.314423651611726</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.190842927087459</v>
+        <v>-1.209428945258097</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-1.201622954754768</v>
+        <v>-1.220187169134931</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-1.04549727344537</v>
+        <v>-1.06463793160647</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.187118305793227</v>
+        <v>-1.205915363587764</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.008658257696261</v>
+        <v>-1.027893761988977</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.6190423085705703</v>
+        <v>-0.6394071721582648</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.4182194062476867</v>
+        <v>-0.4390435405854163</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.3995957036708688</v>
+        <v>-0.4207068901843627</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.1108032769334812</v>
+        <v>-0.1322379234647144</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.3327027071349349</v>
+        <v>-0.3537961897043047</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.4160583941605935</v>
+        <v>-0.4370522604045419</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.6163140241509879</v>
+        <v>-0.6368782983759615</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.8094386638574989</v>
+        <v>-0.8295965842405337</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.8929625772500458</v>
+        <v>-0.9131799071900204</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.8742655869919318</v>
+        <v>-0.8945584903136776</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.724045030308865</v>
+        <v>-0.7445255474452495</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.5955466814498749</v>
+        <v>-0.6163033612785895</v>
       </c>
     </row>
     <row r="34">
@@ -5930,79 +5930,79 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2734</v>
+        <v>2739</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1967523584254423</v>
+        <v>-0.2013105457274094</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.3602612397499811</v>
+        <v>-0.3718571606046766</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.7282741738066036</v>
+        <v>-0.7397299173345075</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.7688095646861584</v>
+        <v>-0.7804570744925527</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.9324430464243676</v>
+        <v>-0.9511474237962645</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.052055774708876</v>
+        <v>-1.070488368627792</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.2961420738527</v>
+        <v>-1.314423651611726</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.190842927087459</v>
+        <v>-1.209428945258097</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-1.201622954754768</v>
+        <v>-1.220187169134931</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.04549727344537</v>
+        <v>-1.06463793160647</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-1.187118305793227</v>
+        <v>-1.205915363587764</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-1.008658257696261</v>
+        <v>-1.027893761988977</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.6190423085705703</v>
+        <v>-0.6394071721582648</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.4182194062476867</v>
+        <v>-0.4390435405854163</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.3995957036708688</v>
+        <v>-0.4207068901843627</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.1108032769334812</v>
+        <v>-0.1322379234647144</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.3327027071349349</v>
+        <v>-0.3537961897043047</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.4160583941605935</v>
+        <v>-0.4370522604045419</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.6163140241509879</v>
+        <v>-0.6368782983759615</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.8094386638574989</v>
+        <v>-0.8295965842405337</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.8929625772500458</v>
+        <v>-0.9131799071900204</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.8742655869919318</v>
+        <v>-0.8945584903136776</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.724045030308865</v>
+        <v>-0.7445255474452495</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.5955466814498749</v>
+        <v>-0.6163033612785895</v>
       </c>
     </row>
     <row r="35">
@@ -6012,79 +6012,79 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2734</v>
+        <v>2739</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1967523584254423</v>
+        <v>-0.2013105457274094</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.3602612397499811</v>
+        <v>-0.3718571606046766</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.7282741738066036</v>
+        <v>-0.7397299173345075</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.7688095646861584</v>
+        <v>-0.7804570744925527</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.9324430464243676</v>
+        <v>-0.9511474237962645</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-1.052055774708876</v>
+        <v>-1.070488368627792</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-1.2961420738527</v>
+        <v>-1.314423651611726</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-1.190842927087459</v>
+        <v>-1.209428945258097</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-1.201622954754768</v>
+        <v>-1.220187169134931</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-1.04549727344537</v>
+        <v>-1.06463793160647</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-1.187118305793227</v>
+        <v>-1.205915363587764</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-1.008658257696261</v>
+        <v>-1.027893761988977</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.6190423085705703</v>
+        <v>-0.6394071721582648</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.4182194062476867</v>
+        <v>-0.4390435405854163</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.3995957036708688</v>
+        <v>-0.4207068901843627</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.1108032769334812</v>
+        <v>-0.1322379234647144</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.3327027071349349</v>
+        <v>-0.3537961897043047</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.4160583941605935</v>
+        <v>-0.4370522604045419</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.6163140241509879</v>
+        <v>-0.6368782983759615</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.8094386638574989</v>
+        <v>-0.8295965842405337</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.8929625772500458</v>
+        <v>-0.9131799071900204</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.8742655869919318</v>
+        <v>-0.8945584903136776</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.724045030308865</v>
+        <v>-0.7445255474452495</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.5955466814498749</v>
+        <v>-0.6163033612785895</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/day_of_week/day_of_week.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/day_of_week/day_of_week.xlsx
@@ -625,76 +625,76 @@
         <v>717</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.301047655152999</v>
+        <v>0.4636542212375119</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.09300010958836</v>
+        <v>3.266131289022212</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.228090199949207</v>
+        <v>4.365387223577734</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.675701194354225</v>
+        <v>5.713473682803524</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4.725941112916267</v>
+        <v>4.467089519721327</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.436096540422902</v>
+        <v>4.21114740877713</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.718692256466753</v>
+        <v>4.385638916286624</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4.162900140680733</v>
+        <v>3.664927864784438</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.094592622683351</v>
+        <v>2.402941912477566</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>2.880710172989801</v>
+        <v>2.157977257354773</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.070450856046691</v>
+        <v>0.3459303083863645</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.09845375397583211</v>
+        <v>-0.7681387620453464</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.09159819240692713</v>
+        <v>-0.91923672580171</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.5451477116295464</v>
+        <v>-1.588494740140192</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.6455119799471305</v>
+        <v>-1.63568256100951</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-1.305096339457762</v>
+        <v>-2.240648160222278</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-1.715648995172501</v>
+        <v>-2.544263193542704</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-1.403732543480515</v>
+        <v>-2.17666849030833</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.910480887259979</v>
+        <v>-1.599634478795728</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-1.142400849380465</v>
+        <v>-1.719415116799759</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-1.406825421136425</v>
+        <v>-1.924217521506343</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.786971265089818</v>
+        <v>-1.302029973726611</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.6529906543413233</v>
+        <v>-1.058395488448269</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.8045187632789847</v>
+        <v>0.3136356706793109</v>
       </c>
     </row>
     <row r="7">
@@ -704,79 +704,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.8650955185896052</v>
+        <v>0.6855759607857905</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1014279554114239</v>
+        <v>-0.6921146867995205</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.336142117608766</v>
+        <v>-3.08829676749972</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.333317277627671</v>
+        <v>-2.125512208825398</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-3.383807609047281</v>
+        <v>-4.111719674433594</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.769469667335336</v>
+        <v>-5.375659313438433</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-6.398423000485387</v>
+        <v>-7.177493171728138</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-5.961874050553881</v>
+        <v>-6.693480728738045</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.919912108396503</v>
+        <v>-6.489294616833966</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-5.119767939826986</v>
+        <v>-5.645393600542114</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-5.560339212283452</v>
+        <v>-6.002759066629004</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-5.409895730748637</v>
+        <v>-5.771984508949323</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-4.244978598181781</v>
+        <v>-4.530017606133171</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-4.465755354473956</v>
+        <v>-4.693550993820317</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-4.412406068930046</v>
+        <v>-4.52222031169395</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-2.81938094051511</v>
+        <v>-2.822936207525792</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-2.527305818109561</v>
+        <v>-2.500074087245139</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-1.775273355542559</v>
+        <v>-1.494978107058238</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-1.848668305649923</v>
+        <v>-1.565010901249593</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-2.095081626398887</v>
+        <v>-1.777166988196264</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-1.637039326450207</v>
+        <v>-1.348878914897092</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.7623073331608694</v>
+        <v>-0.428308862172436</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.8296385247179856</v>
+        <v>-0.7536644195683024</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.9610994736276695</v>
+        <v>-0.7735559031892052</v>
       </c>
     </row>
     <row r="8">
@@ -786,79 +786,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>661</v>
+        <v>675</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.8051583934585409</v>
+        <v>-0.9806181602455197</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.048433480477108</v>
+        <v>-1.741321516602412</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.997074411961286</v>
+        <v>-1.74334714001909</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.467240789664338</v>
+        <v>-3.142382398412792</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.249955394497896</v>
+        <v>-0.9704146321221714</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.9140513966458101</v>
+        <v>-0.8767405879643064</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.4913667616269848</v>
+        <v>-0.2530401145519434</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.069801948543223</v>
+        <v>-0.5579605579605627</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.6272206994674363</v>
+        <v>1.05144983320502</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.756541662356284</v>
+        <v>1.292435375022727</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.63104878884451</v>
+        <v>2.157262982219656</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.709176521765201</v>
+        <v>3.36216250922984</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>3.544904488039883</v>
+        <v>4.32134446585313</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>4.982491902560966</v>
+        <v>5.850888182197814</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>5.018631019423601</v>
+        <v>5.761326392905325</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>4.358744113335618</v>
+        <v>4.989297078391672</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>5.521729088260287</v>
+        <v>6.070601851851855</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>4.605336208570449</v>
+        <v>5.048828857801368</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>4.462104661667134</v>
+        <v>4.818846640502684</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>4.441366447977842</v>
+        <v>4.737136789265378</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>3.540541053580469</v>
+        <v>3.725247843440194</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>2.556979509720541</v>
+        <v>2.761196432596023</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>2.831454222202595</v>
+        <v>3.004830917874401</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>1.696620456120016</v>
+        <v>1.805654886547906</v>
       </c>
     </row>
     <row r="9">
@@ -1086,79 +1086,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2759</v>
+        <v>2780</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.3050988325139841</v>
+        <v>0.2430875576036797</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.7107495561345871</v>
+        <v>0.588029494420617</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.7709946158190277</v>
+        <v>0.6394027846156121</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.088410234751706</v>
+        <v>0.9607233710953125</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.025883929369712</v>
+        <v>0.8842340268599216</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.8003910076628244</v>
+        <v>0.6679280700785739</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.8074512845071666</v>
+        <v>0.6804416850715853</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.5292398397540907</v>
+        <v>0.4318154694094432</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.679069383532287</v>
+        <v>0.5802623133069034</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.7006643611613796</v>
+        <v>0.6288208468435315</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.4691263146270188</v>
+        <v>0.4201064708695981</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3348333936636791</v>
+        <v>0.3076228494553277</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.4395514279270927</v>
+        <v>0.4329869548270437</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.3629290339651519</v>
+        <v>0.3853537564911562</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.3405403858166807</v>
+        <v>0.3705630523932584</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.1255325207258693</v>
+        <v>0.16344429562686</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.5916136590522356</v>
+        <v>0.6555316091954069</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.7255415728678543</v>
+        <v>0.831583944904267</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.9994770914127855</v>
+        <v>1.103587168233865</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>1.063446332622576</v>
+        <v>1.195964549064016</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.9772249886797937</v>
+        <v>1.081762631609664</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>1.104503072463103</v>
+        <v>1.222427447783872</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>1.038770760605104</v>
+        <v>1.142320925867999</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.9849350299614201</v>
+        <v>1.088095600643292</v>
       </c>
     </row>
     <row r="7">
@@ -1168,79 +1168,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2759</v>
+        <v>2780</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.3050988325139841</v>
+        <v>0.2430875576036797</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.7107495561345871</v>
+        <v>0.588029494420617</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.7709946158190277</v>
+        <v>0.6394027846156121</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.088410234751706</v>
+        <v>0.9607233710953125</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.025883929369712</v>
+        <v>0.8842340268599216</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.8003910076628244</v>
+        <v>0.6679280700785739</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.8074512845071666</v>
+        <v>0.6804416850715853</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.5292398397540907</v>
+        <v>0.4318154694094432</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.679069383532287</v>
+        <v>0.5802623133069034</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.7006643611613796</v>
+        <v>0.6288208468435315</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.4691263146270188</v>
+        <v>0.4201064708695981</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.3348333936636791</v>
+        <v>0.3076228494553277</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.4395514279270927</v>
+        <v>0.4329869548270437</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.3629290339651519</v>
+        <v>0.3853537564911562</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.3405403858166807</v>
+        <v>0.3705630523932584</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.1255325207258693</v>
+        <v>0.16344429562686</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.5916136590522356</v>
+        <v>0.6555316091954069</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.7255415728678543</v>
+        <v>0.831583944904267</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.9994770914127855</v>
+        <v>1.103587168233865</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>1.063446332622576</v>
+        <v>1.195964549064016</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.9772249886797937</v>
+        <v>1.081762631609664</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>1.104503072463103</v>
+        <v>1.222427447783872</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>1.038770760605104</v>
+        <v>1.142320925867999</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.9849350299614201</v>
+        <v>1.088095600643292</v>
       </c>
     </row>
     <row r="8">
@@ -1250,79 +1250,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2759</v>
+        <v>2780</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.3050988325139841</v>
+        <v>0.2430875576036797</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.7107495561345871</v>
+        <v>0.588029494420617</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.7709946158190277</v>
+        <v>0.6394027846156121</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.088410234751706</v>
+        <v>0.9607233710953125</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.025883929369712</v>
+        <v>0.8842340268599216</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.8003910076628244</v>
+        <v>0.6679280700785739</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.8074512845071666</v>
+        <v>0.6804416850715853</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.5292398397540907</v>
+        <v>0.4318154694094432</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.679069383532287</v>
+        <v>0.5802623133069034</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.7006643611613796</v>
+        <v>0.6288208468435315</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.4691263146270188</v>
+        <v>0.4201064708695981</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.3348333936636791</v>
+        <v>0.3076228494553277</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.4395514279270927</v>
+        <v>0.4329869548270437</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.3629290339651519</v>
+        <v>0.3853537564911562</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.3405403858166807</v>
+        <v>0.3705630523932584</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.1255325207258693</v>
+        <v>0.16344429562686</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.5916136590522356</v>
+        <v>0.6555316091954069</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.7255415728678543</v>
+        <v>0.831583944904267</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.9994770914127855</v>
+        <v>1.103587168233865</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.063446332622576</v>
+        <v>1.195964549064016</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.9772249886797937</v>
+        <v>1.081762631609664</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>1.104503072463103</v>
+        <v>1.222427447783872</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>1.038770760605104</v>
+        <v>1.142320925867999</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.9849350299614201</v>
+        <v>1.088095600643292</v>
       </c>
     </row>
     <row r="9">
@@ -1332,79 +1332,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2759</v>
+        <v>2780</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.3050988325139841</v>
+        <v>0.2430875576036797</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.7107495561345871</v>
+        <v>0.588029494420617</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.7709946158190277</v>
+        <v>0.6394027846156121</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.088410234751706</v>
+        <v>0.9607233710953125</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.025883929369712</v>
+        <v>0.8842340268599216</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.8003910076628244</v>
+        <v>0.6679280700785739</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.8074512845071666</v>
+        <v>0.6804416850715853</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.5292398397540907</v>
+        <v>0.4318154694094432</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.679069383532287</v>
+        <v>0.5802623133069034</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.7006643611613796</v>
+        <v>0.6288208468435315</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.4691263146270188</v>
+        <v>0.4201064708695981</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.3348333936636791</v>
+        <v>0.3076228494553277</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.4395514279270927</v>
+        <v>0.4329869548270437</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.3629290339651519</v>
+        <v>0.3853537564911562</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.3405403858166807</v>
+        <v>0.3705630523932584</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.1255325207258693</v>
+        <v>0.16344429562686</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.5916136590522356</v>
+        <v>0.6555316091954069</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.7255415728678543</v>
+        <v>0.831583944904267</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.9994770914127855</v>
+        <v>1.103587168233865</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.063446332622576</v>
+        <v>1.195964549064016</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.9772249886797937</v>
+        <v>1.081762631609664</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>1.104503072463103</v>
+        <v>1.222427447783872</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>1.038770760605104</v>
+        <v>1.142320925867999</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.9849350299614201</v>
+        <v>1.088095600643292</v>
       </c>
     </row>
     <row r="10">
@@ -1414,79 +1414,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2759</v>
+        <v>2780</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.3050988325139841</v>
+        <v>0.2430875576036797</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.7107495561345871</v>
+        <v>0.588029494420617</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.7709946158190277</v>
+        <v>0.6394027846156121</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.088410234751706</v>
+        <v>0.9607233710953125</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.025883929369712</v>
+        <v>0.8842340268599216</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.8003910076628244</v>
+        <v>0.6679280700785739</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.8074512845071666</v>
+        <v>0.6804416850715853</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.5292398397540907</v>
+        <v>0.4318154694094432</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.679069383532287</v>
+        <v>0.5802623133069034</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.7006643611613796</v>
+        <v>0.6288208468435315</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4691263146270188</v>
+        <v>0.4201064708695981</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.3348333936636791</v>
+        <v>0.3076228494553277</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.4395514279270927</v>
+        <v>0.4329869548270437</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.3629290339651519</v>
+        <v>0.3853537564911562</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.3405403858166807</v>
+        <v>0.3705630523932584</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.1255325207258693</v>
+        <v>0.16344429562686</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.5916136590522356</v>
+        <v>0.6555316091954069</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.7255415728678543</v>
+        <v>0.831583944904267</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.9994770914127855</v>
+        <v>1.103587168233865</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.063446332622576</v>
+        <v>1.195964549064016</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.9772249886797937</v>
+        <v>1.081762631609664</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>1.104503072463103</v>
+        <v>1.222427447783872</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>1.038770760605104</v>
+        <v>1.142320925867999</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.9849350299614201</v>
+        <v>1.088095600643292</v>
       </c>
     </row>
     <row r="11">
@@ -1496,79 +1496,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2759</v>
+        <v>2780</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.3050988325139841</v>
+        <v>0.2430875576036797</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.7107495561345871</v>
+        <v>0.588029494420617</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.7709946158190277</v>
+        <v>0.6394027846156121</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.088410234751706</v>
+        <v>0.9607233710953125</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.025883929369712</v>
+        <v>0.8842340268599216</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.8003910076628244</v>
+        <v>0.6679280700785739</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.8074512845071666</v>
+        <v>0.6804416850715853</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.5292398397540907</v>
+        <v>0.4318154694094432</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.679069383532287</v>
+        <v>0.5802623133069034</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.7006643611613796</v>
+        <v>0.6288208468435315</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4691263146270188</v>
+        <v>0.4201064708695981</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.3348333936636791</v>
+        <v>0.3076228494553277</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.4395514279270927</v>
+        <v>0.4329869548270437</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.3629290339651519</v>
+        <v>0.3853537564911562</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.3405403858166807</v>
+        <v>0.3705630523932584</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.1255325207258693</v>
+        <v>0.16344429562686</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.5916136590522356</v>
+        <v>0.6555316091954069</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.7255415728678543</v>
+        <v>0.831583944904267</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.9994770914127855</v>
+        <v>1.103587168233865</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.063446332622576</v>
+        <v>1.195964549064016</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.9772249886797937</v>
+        <v>1.081762631609664</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>1.104503072463103</v>
+        <v>1.222427447783872</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>1.038770760605104</v>
+        <v>1.142320925867999</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.9849350299614201</v>
+        <v>1.088095600643292</v>
       </c>
     </row>
     <row r="12">
@@ -1578,79 +1578,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2759</v>
+        <v>2780</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.3050988325139841</v>
+        <v>0.2430875576036797</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.7107495561345871</v>
+        <v>0.588029494420617</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.7709946158190277</v>
+        <v>0.6394027846156121</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.088410234751706</v>
+        <v>0.9607233710953125</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.025883929369712</v>
+        <v>0.8842340268599216</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.8003910076628244</v>
+        <v>0.6679280700785739</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.8074512845071666</v>
+        <v>0.6804416850715853</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.5292398397540907</v>
+        <v>0.4318154694094432</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.679069383532287</v>
+        <v>0.5802623133069034</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.7006643611613796</v>
+        <v>0.6288208468435315</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4691263146270188</v>
+        <v>0.4201064708695981</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3348333936636791</v>
+        <v>0.3076228494553277</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.4395514279270927</v>
+        <v>0.4329869548270437</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.3629290339651519</v>
+        <v>0.3853537564911562</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.3405403858166807</v>
+        <v>0.3705630523932584</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.1255325207258693</v>
+        <v>0.16344429562686</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.5916136590522356</v>
+        <v>0.6555316091954069</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.7255415728678543</v>
+        <v>0.831583944904267</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.9994770914127855</v>
+        <v>1.103587168233865</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1.063446332622576</v>
+        <v>1.195964549064016</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.9772249886797937</v>
+        <v>1.081762631609664</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>1.104503072463103</v>
+        <v>1.222427447783872</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>1.038770760605104</v>
+        <v>1.142320925867999</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.9849350299614201</v>
+        <v>1.088095600643292</v>
       </c>
     </row>
     <row r="13">
@@ -1660,79 +1660,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2759</v>
+        <v>2780</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.3050988325139841</v>
+        <v>0.2430875576036797</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.7107495561345871</v>
+        <v>0.588029494420617</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.7709946158190277</v>
+        <v>0.6394027846156121</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.088410234751706</v>
+        <v>0.9607233710953125</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.025883929369712</v>
+        <v>0.8842340268599216</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.8003910076628244</v>
+        <v>0.6679280700785739</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.8074512845071666</v>
+        <v>0.6804416850715853</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.5292398397540907</v>
+        <v>0.4318154694094432</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.679069383532287</v>
+        <v>0.5802623133069034</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.7006643611613796</v>
+        <v>0.6288208468435315</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.4691263146270188</v>
+        <v>0.4201064708695981</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3348333936636791</v>
+        <v>0.3076228494553277</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.4395514279270927</v>
+        <v>0.4329869548270437</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3629290339651519</v>
+        <v>0.3853537564911562</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.3405403858166807</v>
+        <v>0.3705630523932584</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.1255325207258693</v>
+        <v>0.16344429562686</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.5916136590522356</v>
+        <v>0.6555316091954069</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.7255415728678543</v>
+        <v>0.831583944904267</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.9994770914127855</v>
+        <v>1.103587168233865</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>1.063446332622576</v>
+        <v>1.195964549064016</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.9772249886797937</v>
+        <v>1.081762631609664</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1.104503072463103</v>
+        <v>1.222427447783872</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>1.038770760605104</v>
+        <v>1.142320925867999</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.9849350299614201</v>
+        <v>1.088095600643292</v>
       </c>
     </row>
     <row r="14">
@@ -1742,79 +1742,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2042</v>
+        <v>2063</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.3065213076206632</v>
+        <v>0.1664291485753324</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1257213776687252</v>
+        <v>-0.3427504312843439</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.4428827268946449</v>
+        <v>-0.6555709636809723</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.5223084812301693</v>
+        <v>-0.6911050212918823</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2733036321400206</v>
+        <v>-0.3609949544205548</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4762009938009228</v>
+        <v>-0.5635252822466157</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.5658884691142845</v>
+        <v>-0.6073074253409985</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.7466340269277865</v>
+        <v>-0.6918595608784202</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.1690844668454332</v>
+        <v>-0.05321382465012192</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.06480716042577939</v>
+        <v>0.09735931202212811</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2579854252059164</v>
+        <v>0.4458865525470017</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.4178325129859957</v>
+        <v>0.6815060658615266</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.5617269763443034</v>
+        <v>0.902955146301025</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.6817787041862076</v>
+        <v>1.071368963512327</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.6867693506808621</v>
+        <v>1.067837945660237</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.6278640059127838</v>
+        <v>0.9989916978778624</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>1.401754365751131</v>
+        <v>1.767627039909513</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>1.473185814504376</v>
+        <v>1.877108421902541</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1.670113658850781</v>
+        <v>2.043097551617393</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.83797739505949</v>
+        <v>2.209210899245456</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>1.814327899472268</v>
+        <v>2.126497372173972</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>1.768649546520621</v>
+        <v>2.099807947649616</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>1.632792765755241</v>
+        <v>1.907184556049657</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>1.048283934570286</v>
+        <v>1.357260782312785</v>
       </c>
     </row>
     <row r="15">
@@ -1824,79 +1824,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2042</v>
+        <v>2063</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.3065213076206632</v>
+        <v>0.1664291485753324</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1257213776687252</v>
+        <v>-0.3427504312843439</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.4428827268946449</v>
+        <v>-0.6555709636809723</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5223084812301693</v>
+        <v>-0.6911050212918823</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.2733036321400206</v>
+        <v>-0.3609949544205548</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4762009938009228</v>
+        <v>-0.5635252822466157</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.5658884691142845</v>
+        <v>-0.6073074253409985</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.7466340269277865</v>
+        <v>-0.6918595608784202</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.1690844668454332</v>
+        <v>-0.05321382465012192</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.06480716042577939</v>
+        <v>0.09735931202212811</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.2579854252059164</v>
+        <v>0.4458865525470017</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.4178325129859957</v>
+        <v>0.6815060658615266</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.5617269763443034</v>
+        <v>0.902955146301025</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.6817787041862076</v>
+        <v>1.071368963512327</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.6867693506808621</v>
+        <v>1.067837945660237</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.6278640059127838</v>
+        <v>0.9989916978778624</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>1.401754365751131</v>
+        <v>1.767627039909513</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>1.473185814504376</v>
+        <v>1.877108421902541</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>1.670113658850781</v>
+        <v>2.043097551617393</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.83797739505949</v>
+        <v>2.209210899245456</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>1.814327899472268</v>
+        <v>2.126497372173972</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>1.768649546520621</v>
+        <v>2.099807947649616</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>1.632792765755241</v>
+        <v>1.907184556049657</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.048283934570286</v>
+        <v>1.357260782312785</v>
       </c>
     </row>
     <row r="16">
@@ -1906,79 +1906,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2042</v>
+        <v>2063</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.3065213076206632</v>
+        <v>0.1664291485753324</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1257213776687252</v>
+        <v>-0.3427504312843439</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.4428827268946449</v>
+        <v>-0.6555709636809723</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5223084812301693</v>
+        <v>-0.6911050212918823</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.2733036321400206</v>
+        <v>-0.3609949544205548</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4762009938009228</v>
+        <v>-0.5635252822466157</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.5658884691142845</v>
+        <v>-0.6073074253409985</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.7466340269277865</v>
+        <v>-0.6918595608784202</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.1690844668454332</v>
+        <v>-0.05321382465012192</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.06480716042577939</v>
+        <v>0.09735931202212811</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2579854252059164</v>
+        <v>0.4458865525470017</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.4178325129859957</v>
+        <v>0.6815060658615266</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.5617269763443034</v>
+        <v>0.902955146301025</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.6817787041862076</v>
+        <v>1.071368963512327</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.6867693506808621</v>
+        <v>1.067837945660237</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.6278640059127838</v>
+        <v>0.9989916978778624</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>1.401754365751131</v>
+        <v>1.767627039909513</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>1.473185814504376</v>
+        <v>1.877108421902541</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>1.670113658850781</v>
+        <v>2.043097551617393</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1.83797739505949</v>
+        <v>2.209210899245456</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>1.814327899472268</v>
+        <v>2.126497372173972</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>1.768649546520621</v>
+        <v>2.099807947649616</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>1.632792765755241</v>
+        <v>1.907184556049657</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>1.048283934570286</v>
+        <v>1.357260782312785</v>
       </c>
     </row>
     <row r="17">
@@ -1988,79 +1988,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2042</v>
+        <v>2063</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3065213076206632</v>
+        <v>0.1664291485753324</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.1257213776687252</v>
+        <v>-0.3427504312843439</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.4428827268946449</v>
+        <v>-0.6555709636809723</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5223084812301693</v>
+        <v>-0.6911050212918823</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.2733036321400206</v>
+        <v>-0.3609949544205548</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.4762009938009228</v>
+        <v>-0.5635252822466157</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.5658884691142845</v>
+        <v>-0.6073074253409985</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.7466340269277865</v>
+        <v>-0.6918595608784202</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.1690844668454332</v>
+        <v>-0.05321382465012192</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.06480716042577939</v>
+        <v>0.09735931202212811</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.2579854252059164</v>
+        <v>0.4458865525470017</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.4178325129859957</v>
+        <v>0.6815060658615266</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.5617269763443034</v>
+        <v>0.902955146301025</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.6817787041862076</v>
+        <v>1.071368963512327</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.6867693506808621</v>
+        <v>1.067837945660237</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.6278640059127838</v>
+        <v>0.9989916978778624</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.401754365751131</v>
+        <v>1.767627039909513</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>1.473185814504376</v>
+        <v>1.877108421902541</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>1.670113658850781</v>
+        <v>2.043097551617393</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.83797739505949</v>
+        <v>2.209210899245456</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.814327899472268</v>
+        <v>2.126497372173972</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>1.768649546520621</v>
+        <v>2.099807947649616</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>1.632792765755241</v>
+        <v>1.907184556049657</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>1.048283934570286</v>
+        <v>1.357260782312785</v>
       </c>
     </row>
     <row r="18">
@@ -2070,79 +2070,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2042</v>
+        <v>2063</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.3065213076206632</v>
+        <v>0.1664291485753324</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.1257213776687252</v>
+        <v>-0.3427504312843439</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.4428827268946449</v>
+        <v>-0.6555709636809723</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.5223084812301693</v>
+        <v>-0.6911050212918823</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2733036321400206</v>
+        <v>-0.3609949544205548</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.4762009938009228</v>
+        <v>-0.5635252822466157</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.5658884691142845</v>
+        <v>-0.6073074253409985</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.7466340269277865</v>
+        <v>-0.6918595608784202</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.1690844668454332</v>
+        <v>-0.05321382465012192</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.06480716042577939</v>
+        <v>0.09735931202212811</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.2579854252059164</v>
+        <v>0.4458865525470017</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.4178325129859957</v>
+        <v>0.6815060658615266</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.5617269763443034</v>
+        <v>0.902955146301025</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.6817787041862076</v>
+        <v>1.071368963512327</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.6867693506808621</v>
+        <v>1.067837945660237</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.6278640059127838</v>
+        <v>0.9989916978778624</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.401754365751131</v>
+        <v>1.767627039909513</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>1.473185814504376</v>
+        <v>1.877108421902541</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>1.670113658850781</v>
+        <v>2.043097551617393</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.83797739505949</v>
+        <v>2.209210899245456</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>1.814327899472268</v>
+        <v>2.126497372173972</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>1.768649546520621</v>
+        <v>2.099807947649616</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>1.632792765755241</v>
+        <v>1.907184556049657</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.048283934570286</v>
+        <v>1.357260782312785</v>
       </c>
     </row>
     <row r="19">
@@ -2152,79 +2152,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2042</v>
+        <v>2063</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3065213076206632</v>
+        <v>0.1664291485753324</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.1257213776687252</v>
+        <v>-0.3427504312843439</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.4428827268946449</v>
+        <v>-0.6555709636809723</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.5223084812301693</v>
+        <v>-0.6911050212918823</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.2733036321400206</v>
+        <v>-0.3609949544205548</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.4762009938009228</v>
+        <v>-0.5635252822466157</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.5658884691142845</v>
+        <v>-0.6073074253409985</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.7466340269277865</v>
+        <v>-0.6918595608784202</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.1690844668454332</v>
+        <v>-0.05321382465012192</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.06480716042577939</v>
+        <v>0.09735931202212811</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.2579854252059164</v>
+        <v>0.4458865525470017</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.4178325129859957</v>
+        <v>0.6815060658615266</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.5617269763443034</v>
+        <v>0.902955146301025</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.6817787041862076</v>
+        <v>1.071368963512327</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.6867693506808621</v>
+        <v>1.067837945660237</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.6278640059127838</v>
+        <v>0.9989916978778624</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>1.401754365751131</v>
+        <v>1.767627039909513</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.473185814504376</v>
+        <v>1.877108421902541</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.670113658850781</v>
+        <v>2.043097551617393</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.83797739505949</v>
+        <v>2.209210899245456</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.814327899472268</v>
+        <v>2.126497372173972</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.768649546520621</v>
+        <v>2.099807947649616</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.632792765755241</v>
+        <v>1.907184556049657</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.048283934570286</v>
+        <v>1.357260782312785</v>
       </c>
     </row>
     <row r="20">
@@ -2234,79 +2234,79 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2042</v>
+        <v>2063</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.3065213076206632</v>
+        <v>0.1664291485753324</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.1257213776687252</v>
+        <v>-0.3427504312843439</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.4428827268946449</v>
+        <v>-0.6555709636809723</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.5223084812301693</v>
+        <v>-0.6911050212918823</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.2733036321400206</v>
+        <v>-0.3609949544205548</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4762009938009228</v>
+        <v>-0.5635252822466157</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.5658884691142845</v>
+        <v>-0.6073074253409985</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.7466340269277865</v>
+        <v>-0.6918595608784202</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.1690844668454332</v>
+        <v>-0.05321382465012192</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.06480716042577939</v>
+        <v>0.09735931202212811</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.2579854252059164</v>
+        <v>0.4458865525470017</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.4178325129859957</v>
+        <v>0.6815060658615266</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.5617269763443034</v>
+        <v>0.902955146301025</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.6817787041862076</v>
+        <v>1.071368963512327</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.6867693506808621</v>
+        <v>1.067837945660237</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.6278640059127838</v>
+        <v>0.9989916978778624</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.401754365751131</v>
+        <v>1.767627039909513</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.473185814504376</v>
+        <v>1.877108421902541</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.670113658850781</v>
+        <v>2.043097551617393</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.83797739505949</v>
+        <v>2.209210899245456</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.814327899472268</v>
+        <v>2.126497372173972</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.768649546520621</v>
+        <v>2.099807947649616</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.632792765755241</v>
+        <v>1.907184556049657</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>1.048283934570286</v>
+        <v>1.357260782312785</v>
       </c>
     </row>
     <row r="21">
@@ -2316,79 +2316,79 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1346</v>
+        <v>1360</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.01768947193389181</v>
+        <v>-0.1019239462657922</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.2431774964085349</v>
+        <v>-0.1621599374408405</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.5360983547821974</v>
+        <v>0.6019336246165281</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.1029458346531555</v>
+        <v>0.0503569293228594</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.335099612976961</v>
+        <v>1.577798779527363</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.743795289096518</v>
+        <v>1.923923411817981</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.450043205353985</v>
+        <v>2.788898883269404</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.950102270578739</v>
+        <v>2.410449028096082</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.804597582574736</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.549050716589988</v>
+        <v>3.065855854325555</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.266569338796252</v>
+        <v>3.779267339518128</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.43127891539261</v>
+        <v>4.017391267399773</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.047215148610398</v>
+        <v>3.711322679360762</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.343505082215536</v>
+        <v>4.051323912045298</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>3.323490072857084</v>
+        <v>3.957404824277887</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>2.410391853397037</v>
+        <v>2.97459119603873</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>3.433422930362596</v>
+        <v>3.973651960784309</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>3.15292398861483</v>
+        <v>3.620179620328592</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>3.489632416126035</v>
+        <v>3.908171259239069</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>3.871713709275717</v>
+        <v>4.269816527827466</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>3.598987326843769</v>
+        <v>3.922960261740847</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>3.077376135122634</v>
+        <v>3.406621269197331</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>2.906085617292653</v>
+        <v>3.282608695652179</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>2.087311313549321</v>
+        <v>2.458704995480367</v>
       </c>
     </row>
     <row r="22">
@@ -2398,79 +2398,79 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1346</v>
+        <v>1360</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.01768947193389181</v>
+        <v>-0.1019239462657922</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2431774964085349</v>
+        <v>-0.1621599374408405</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.5360983547821974</v>
+        <v>0.6019336246165281</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1029458346531555</v>
+        <v>0.0503569293228594</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.335099612976961</v>
+        <v>1.577798779527363</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.743795289096518</v>
+        <v>1.923923411817981</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.450043205353985</v>
+        <v>2.788898883269404</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.950102270578739</v>
+        <v>2.410449028096082</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.804597582574736</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.549050716589988</v>
+        <v>3.065855854325555</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.266569338796252</v>
+        <v>3.779267339518128</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.43127891539261</v>
+        <v>4.017391267399773</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.047215148610398</v>
+        <v>3.711322679360762</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.343505082215536</v>
+        <v>4.051323912045298</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>3.323490072857084</v>
+        <v>3.957404824277887</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>2.410391853397037</v>
+        <v>2.97459119603873</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>3.433422930362596</v>
+        <v>3.973651960784309</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>3.15292398861483</v>
+        <v>3.620179620328592</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>3.489632416126035</v>
+        <v>3.908171259239069</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>3.871713709275717</v>
+        <v>4.269816527827466</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>3.598987326843769</v>
+        <v>3.922960261740847</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>3.077376135122634</v>
+        <v>3.406621269197331</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>2.906085617292653</v>
+        <v>3.282608695652179</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>2.087311313549321</v>
+        <v>2.458704995480367</v>
       </c>
     </row>
     <row r="23">
@@ -2480,79 +2480,79 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1346</v>
+        <v>1360</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.01768947193389181</v>
+        <v>-0.1019239462657922</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.2431774964085349</v>
+        <v>-0.1621599374408405</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.5360983547821974</v>
+        <v>0.6019336246165281</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.1029458346531555</v>
+        <v>0.0503569293228594</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.335099612976961</v>
+        <v>1.577798779527363</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.743795289096518</v>
+        <v>1.923923411817981</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.450043205353985</v>
+        <v>2.788898883269404</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.950102270578739</v>
+        <v>2.410449028096082</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.804597582574736</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.549050716589988</v>
+        <v>3.065855854325555</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.266569338796252</v>
+        <v>3.779267339518128</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.43127891539261</v>
+        <v>4.017391267399773</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.047215148610398</v>
+        <v>3.711322679360762</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.343505082215536</v>
+        <v>4.051323912045298</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>3.323490072857084</v>
+        <v>3.957404824277887</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>2.410391853397037</v>
+        <v>2.97459119603873</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>3.433422930362596</v>
+        <v>3.973651960784309</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>3.15292398861483</v>
+        <v>3.620179620328592</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>3.489632416126035</v>
+        <v>3.908171259239069</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>3.871713709275717</v>
+        <v>4.269816527827466</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>3.598987326843769</v>
+        <v>3.922960261740847</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>3.077376135122634</v>
+        <v>3.406621269197331</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>2.906085617292653</v>
+        <v>3.282608695652179</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>2.087311313549321</v>
+        <v>2.458704995480367</v>
       </c>
     </row>
     <row r="24">
@@ -2562,79 +2562,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1346</v>
+        <v>1360</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.01768947193389181</v>
+        <v>-0.1019239462657922</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.2431774964085349</v>
+        <v>-0.1621599374408405</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.5360983547821974</v>
+        <v>0.6019336246165281</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1029458346531555</v>
+        <v>0.0503569293228594</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.335099612976961</v>
+        <v>1.577798779527363</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.743795289096518</v>
+        <v>1.923923411817981</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.450043205353985</v>
+        <v>2.788898883269404</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.950102270578739</v>
+        <v>2.410449028096082</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.804597582574736</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.549050716589988</v>
+        <v>3.065855854325555</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.266569338796252</v>
+        <v>3.779267339518128</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.43127891539261</v>
+        <v>4.017391267399773</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.047215148610398</v>
+        <v>3.711322679360762</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.343505082215536</v>
+        <v>4.051323912045298</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>3.323490072857084</v>
+        <v>3.957404824277887</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.410391853397037</v>
+        <v>2.97459119603873</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.433422930362596</v>
+        <v>3.973651960784309</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>3.15292398861483</v>
+        <v>3.620179620328592</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>3.489632416126035</v>
+        <v>3.908171259239069</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>3.871713709275717</v>
+        <v>4.269816527827466</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.598987326843769</v>
+        <v>3.922960261740847</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.077376135122634</v>
+        <v>3.406621269197331</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.906085617292653</v>
+        <v>3.282608695652179</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.087311313549321</v>
+        <v>2.458704995480367</v>
       </c>
     </row>
     <row r="25">
@@ -2644,79 +2644,79 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1346</v>
+        <v>1360</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.01768947193389181</v>
+        <v>-0.1019239462657922</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.2431774964085349</v>
+        <v>-0.1621599374408405</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.5360983547821974</v>
+        <v>0.6019336246165281</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.1029458346531555</v>
+        <v>0.0503569293228594</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.335099612976961</v>
+        <v>1.577798779527363</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.743795289096518</v>
+        <v>1.923923411817981</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.450043205353985</v>
+        <v>2.788898883269404</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.950102270578739</v>
+        <v>2.410449028096082</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.804597582574736</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.549050716589988</v>
+        <v>3.065855854325555</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.266569338796252</v>
+        <v>3.779267339518128</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.43127891539261</v>
+        <v>4.017391267399773</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.047215148610398</v>
+        <v>3.711322679360762</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.343505082215536</v>
+        <v>4.051323912045298</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>3.323490072857084</v>
+        <v>3.957404824277887</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>2.410391853397037</v>
+        <v>2.97459119603873</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.433422930362596</v>
+        <v>3.973651960784309</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>3.15292398861483</v>
+        <v>3.620179620328592</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.489632416126035</v>
+        <v>3.908171259239069</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.871713709275717</v>
+        <v>4.269816527827466</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.598987326843769</v>
+        <v>3.922960261740847</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.077376135122634</v>
+        <v>3.406621269197331</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>2.906085617292653</v>
+        <v>3.282608695652179</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>2.087311313549321</v>
+        <v>2.458704995480367</v>
       </c>
     </row>
     <row r="26">
@@ -2726,79 +2726,79 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1346</v>
+        <v>1360</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.01768947193389181</v>
+        <v>-0.1019239462657922</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.2431774964085349</v>
+        <v>-0.1621599374408405</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.5360983547821974</v>
+        <v>0.6019336246165281</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.1029458346531555</v>
+        <v>0.0503569293228594</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.335099612976961</v>
+        <v>1.577798779527363</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.743795289096518</v>
+        <v>1.923923411817981</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.450043205353985</v>
+        <v>2.788898883269404</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.950102270578739</v>
+        <v>2.410449028096082</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.804597582574736</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.549050716589988</v>
+        <v>3.065855854325555</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.266569338796252</v>
+        <v>3.779267339518128</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.43127891539261</v>
+        <v>4.017391267399773</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.047215148610398</v>
+        <v>3.711322679360762</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.343505082215536</v>
+        <v>4.051323912045298</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>3.323490072857084</v>
+        <v>3.957404824277887</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>2.410391853397037</v>
+        <v>2.97459119603873</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>3.433422930362596</v>
+        <v>3.973651960784309</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>3.15292398861483</v>
+        <v>3.620179620328592</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.489632416126035</v>
+        <v>3.908171259239069</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.871713709275717</v>
+        <v>4.269816527827466</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>3.598987326843769</v>
+        <v>3.922960261740847</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>3.077376135122634</v>
+        <v>3.406621269197331</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>2.906085617292653</v>
+        <v>3.282608695652179</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>2.087311313549321</v>
+        <v>2.458704995480367</v>
       </c>
     </row>
     <row r="27">
@@ -2808,79 +2808,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1346</v>
+        <v>1360</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.01768947193389181</v>
+        <v>-0.1019239462657922</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2431774964085349</v>
+        <v>-0.1621599374408405</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.5360983547821974</v>
+        <v>0.6019336246165281</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.1029458346531555</v>
+        <v>0.0503569293228594</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.335099612976961</v>
+        <v>1.577798779527363</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.743795289096518</v>
+        <v>1.923923411817981</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.450043205353985</v>
+        <v>2.788898883269404</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.950102270578739</v>
+        <v>2.410449028096082</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.804597582574736</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.549050716589988</v>
+        <v>3.065855854325555</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.266569338796252</v>
+        <v>3.779267339518128</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.43127891539261</v>
+        <v>4.017391267399773</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.047215148610398</v>
+        <v>3.711322679360762</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.343505082215536</v>
+        <v>4.051323912045298</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>3.323490072857084</v>
+        <v>3.957404824277887</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>2.410391853397037</v>
+        <v>2.97459119603873</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>3.433422930362596</v>
+        <v>3.973651960784309</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>3.15292398861483</v>
+        <v>3.620179620328592</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>3.489632416126035</v>
+        <v>3.908171259239069</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>3.871713709275717</v>
+        <v>4.269816527827466</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>3.598987326843769</v>
+        <v>3.922960261740847</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>3.077376135122634</v>
+        <v>3.406621269197331</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>2.906085617292653</v>
+        <v>3.282608695652179</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>2.087311313549321</v>
+        <v>2.458704995480367</v>
       </c>
     </row>
     <row r="28">
@@ -2893,76 +2893,76 @@
         <v>685</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.8117076310935829</v>
+        <v>0.7639426149550914</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.498828642962742</v>
+        <v>1.393948188010349</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.980517623128826</v>
+        <v>2.912976713855997</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.143476012445213</v>
+        <v>3.196486923806894</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.82958335011692</v>
+        <v>4.088811995386394</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.308520339134013</v>
+        <v>4.683701805764038</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>5.288396472761903</v>
+        <v>5.78643001250942</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.864199626548974</v>
+        <v>5.335524167640948</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.905686808463678</v>
+        <v>5.463453077325056</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.278756533887041</v>
+        <v>4.813386983565572</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.844786978968671</v>
+        <v>5.377592801089612</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.128081371141114</v>
+        <v>4.663054642238755</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.566963099905443</v>
+        <v>3.11020632040843</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.761942617619425</v>
+        <v>2.278030653135893</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.687740925878295</v>
+        <v>2.179817877090265</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.5303030303030312</v>
+        <v>0.9892970783916724</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>1.418283703544539</v>
+        <v>1.907314476885645</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>1.75139920410291</v>
+        <v>2.212386576103597</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>2.551232190866664</v>
+        <v>3.010790409088798</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>3.322019606674097</v>
+        <v>3.809318459987189</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>3.655385847467194</v>
+        <v>4.117786367365582</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>3.579539886058093</v>
+        <v>4.042623845410297</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>2.978102189781019</v>
+        <v>3.556331323389408</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>2.464313732178184</v>
+        <v>3.102221526180237</v>
       </c>
     </row>
     <row r="29">
@@ -2975,76 +2975,76 @@
         <v>685</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.8117076310935829</v>
+        <v>0.7639426149550914</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.498828642962742</v>
+        <v>1.393948188010349</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.980517623128826</v>
+        <v>2.912976713855997</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.143476012445213</v>
+        <v>3.196486923806894</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.82958335011692</v>
+        <v>4.088811995386394</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.308520339134013</v>
+        <v>4.683701805764038</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.288396472761903</v>
+        <v>5.78643001250942</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.864199626548974</v>
+        <v>5.335524167640948</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.905686808463678</v>
+        <v>5.463453077325056</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>4.278756533887041</v>
+        <v>4.813386983565572</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.844786978968671</v>
+        <v>5.377592801089612</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.128081371141114</v>
+        <v>4.663054642238755</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2.566963099905443</v>
+        <v>3.11020632040843</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.761942617619425</v>
+        <v>2.278030653135893</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>1.687740925878295</v>
+        <v>2.179817877090265</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.5303030303030312</v>
+        <v>0.9892970783916724</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>1.418283703544539</v>
+        <v>1.907314476885645</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>1.75139920410291</v>
+        <v>2.212386576103597</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.551232190866664</v>
+        <v>3.010790409088798</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>3.322019606674097</v>
+        <v>3.809318459987189</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>3.655385847467194</v>
+        <v>4.117786367365582</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>3.579539886058093</v>
+        <v>4.042623845410297</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>2.978102189781019</v>
+        <v>3.556331323389408</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>2.464313732178184</v>
+        <v>3.102221526180237</v>
       </c>
     </row>
     <row r="30">
@@ -3057,76 +3057,76 @@
         <v>685</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.8117076310935829</v>
+        <v>0.7639426149550914</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.498828642962742</v>
+        <v>1.393948188010349</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.980517623128826</v>
+        <v>2.912976713855997</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.143476012445213</v>
+        <v>3.196486923806894</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.82958335011692</v>
+        <v>4.088811995386394</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.308520339134013</v>
+        <v>4.683701805764038</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.288396472761903</v>
+        <v>5.78643001250942</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.864199626548974</v>
+        <v>5.335524167640948</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.905686808463678</v>
+        <v>5.463453077325056</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>4.278756533887041</v>
+        <v>4.813386983565572</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>4.844786978968671</v>
+        <v>5.377592801089612</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.128081371141114</v>
+        <v>4.663054642238755</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>2.566963099905443</v>
+        <v>3.11020632040843</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>1.761942617619425</v>
+        <v>2.278030653135893</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1.687740925878295</v>
+        <v>2.179817877090265</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.5303030303030312</v>
+        <v>0.9892970783916724</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>1.418283703544539</v>
+        <v>1.907314476885645</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>1.75139920410291</v>
+        <v>2.212386576103597</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>2.551232190866664</v>
+        <v>3.010790409088798</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>3.322019606674097</v>
+        <v>3.809318459987189</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>3.655385847467194</v>
+        <v>4.117786367365582</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>3.579539886058093</v>
+        <v>4.042623845410297</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>2.978102189781019</v>
+        <v>3.556331323389408</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>2.464313732178184</v>
+        <v>3.102221526180237</v>
       </c>
     </row>
     <row r="31">
@@ -3139,76 +3139,76 @@
         <v>685</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.8117076310935829</v>
+        <v>0.7639426149550914</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.498828642962742</v>
+        <v>1.393948188010349</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.980517623128826</v>
+        <v>2.912976713855997</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.143476012445213</v>
+        <v>3.196486923806894</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.82958335011692</v>
+        <v>4.088811995386394</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.308520339134013</v>
+        <v>4.683701805764038</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.288396472761903</v>
+        <v>5.78643001250942</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.864199626548974</v>
+        <v>5.335524167640948</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.905686808463678</v>
+        <v>5.463453077325056</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.278756533887041</v>
+        <v>4.813386983565572</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.844786978968671</v>
+        <v>5.377592801089612</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.128081371141114</v>
+        <v>4.663054642238755</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>2.566963099905443</v>
+        <v>3.11020632040843</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.761942617619425</v>
+        <v>2.278030653135893</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>1.687740925878295</v>
+        <v>2.179817877090265</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.5303030303030312</v>
+        <v>0.9892970783916724</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>1.418283703544539</v>
+        <v>1.907314476885645</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>1.75139920410291</v>
+        <v>2.212386576103597</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.551232190866664</v>
+        <v>3.010790409088798</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>3.322019606674097</v>
+        <v>3.809318459987189</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>3.655385847467194</v>
+        <v>4.117786367365582</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>3.579539886058093</v>
+        <v>4.042623845410297</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>2.978102189781019</v>
+        <v>3.556331323389408</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>2.464313732178184</v>
+        <v>3.102221526180237</v>
       </c>
     </row>
     <row r="32">
@@ -3221,76 +3221,76 @@
         <v>685</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.8117076310935829</v>
+        <v>0.7639426149550914</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.498828642962742</v>
+        <v>1.393948188010349</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.980517623128826</v>
+        <v>2.912976713855997</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.143476012445213</v>
+        <v>3.196486923806894</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.82958335011692</v>
+        <v>4.088811995386394</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.308520339134013</v>
+        <v>4.683701805764038</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.288396472761903</v>
+        <v>5.78643001250942</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.864199626548974</v>
+        <v>5.335524167640948</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.905686808463678</v>
+        <v>5.463453077325056</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>4.278756533887041</v>
+        <v>4.813386983565572</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.844786978968671</v>
+        <v>5.377592801089612</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4.128081371141114</v>
+        <v>4.663054642238755</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.566963099905443</v>
+        <v>3.11020632040843</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>1.761942617619425</v>
+        <v>2.278030653135893</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>1.687740925878295</v>
+        <v>2.179817877090265</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>0.5303030303030312</v>
+        <v>0.9892970783916724</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>1.418283703544539</v>
+        <v>1.907314476885645</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>1.75139920410291</v>
+        <v>2.212386576103597</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2.551232190866664</v>
+        <v>3.010790409088798</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>3.322019606674097</v>
+        <v>3.809318459987189</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>3.655385847467194</v>
+        <v>4.117786367365582</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>3.579539886058093</v>
+        <v>4.042623845410297</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>2.978102189781019</v>
+        <v>3.556331323389408</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>2.464313732178184</v>
+        <v>3.102221526180237</v>
       </c>
     </row>
     <row r="33">
@@ -3303,76 +3303,76 @@
         <v>685</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.8117076310935829</v>
+        <v>0.7639426149550914</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.498828642962742</v>
+        <v>1.393948188010349</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.980517623128826</v>
+        <v>2.912976713855997</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.143476012445213</v>
+        <v>3.196486923806894</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.82958335011692</v>
+        <v>4.088811995386394</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4.308520339134013</v>
+        <v>4.683701805764038</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.288396472761903</v>
+        <v>5.78643001250942</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>4.864199626548974</v>
+        <v>5.335524167640948</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4.905686808463678</v>
+        <v>5.463453077325056</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>4.278756533887041</v>
+        <v>4.813386983565572</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>4.844786978968671</v>
+        <v>5.377592801089612</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4.128081371141114</v>
+        <v>4.663054642238755</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.566963099905443</v>
+        <v>3.11020632040843</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.761942617619425</v>
+        <v>2.278030653135893</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>1.687740925878295</v>
+        <v>2.179817877090265</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>0.5303030303030312</v>
+        <v>0.9892970783916724</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>1.418283703544539</v>
+        <v>1.907314476885645</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>1.75139920410291</v>
+        <v>2.212386576103597</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>2.551232190866664</v>
+        <v>3.010790409088798</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>3.322019606674097</v>
+        <v>3.809318459987189</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>3.655385847467194</v>
+        <v>4.117786367365582</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>3.579539886058093</v>
+        <v>4.042623845410297</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>2.978102189781019</v>
+        <v>3.556331323389408</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>2.464313732178184</v>
+        <v>3.102221526180237</v>
       </c>
     </row>
     <row r="34">
@@ -3385,76 +3385,76 @@
         <v>685</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.8117076310935829</v>
+        <v>0.7639426149550914</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.498828642962742</v>
+        <v>1.393948188010349</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.980517623128826</v>
+        <v>2.912976713855997</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.143476012445213</v>
+        <v>3.196486923806894</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>3.82958335011692</v>
+        <v>4.088811995386394</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.308520339134013</v>
+        <v>4.683701805764038</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.288396472761903</v>
+        <v>5.78643001250942</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.864199626548974</v>
+        <v>5.335524167640948</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.905686808463678</v>
+        <v>5.463453077325056</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>4.278756533887041</v>
+        <v>4.813386983565572</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>4.844786978968671</v>
+        <v>5.377592801089612</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.128081371141114</v>
+        <v>4.663054642238755</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>2.566963099905443</v>
+        <v>3.11020632040843</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.761942617619425</v>
+        <v>2.278030653135893</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>1.687740925878295</v>
+        <v>2.179817877090265</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0.5303030303030312</v>
+        <v>0.9892970783916724</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>1.418283703544539</v>
+        <v>1.907314476885645</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>1.75139920410291</v>
+        <v>2.212386576103597</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>2.551232190866664</v>
+        <v>3.010790409088798</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>3.322019606674097</v>
+        <v>3.809318459987189</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>3.655385847467194</v>
+        <v>4.117786367365582</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>3.579539886058093</v>
+        <v>4.042623845410297</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>2.978102189781019</v>
+        <v>3.556331323389408</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>2.464313732178184</v>
+        <v>3.102221526180237</v>
       </c>
     </row>
     <row r="35">
@@ -3716,79 +3716,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.25989473247958</v>
+        <v>-1.012864823348693</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.933957245115117</v>
+        <v>-2.44924784952876</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-3.181500103669912</v>
+        <v>-2.662275284753662</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.489692218350747</v>
+        <v>-3.998725102609505</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.230244595659926</v>
+        <v>-3.679045147470745</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-3.299230790514933</v>
+        <v>-2.778063922425048</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-3.327131855357663</v>
+        <v>-2.829098315610146</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-2.184001663605173</v>
+        <v>-1.79473304473305</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.806482273135622</v>
+        <v>-2.410851754096562</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.900059216824879</v>
+        <v>-2.611665154077798</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-1.944626894015279</v>
+        <v>-1.744192044235369</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-1.390035482840645</v>
+        <v>-1.276726379659053</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.82750436025546</v>
+        <v>-1.79638040187173</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.511203751954135</v>
+        <v>-1.59818589187627</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-1.417467350286579</v>
+        <v>-1.536292654713698</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.5223285486443459</v>
+        <v>-0.6773695882749919</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-2.460756963817303</v>
+        <v>-2.71577380952381</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-3.016725487187351</v>
+        <v>-3.443896009923506</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-4.154217564909644</v>
+        <v>-4.568719497063455</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-4.41849957449049</v>
+        <v>-4.949371147242566</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-4.058790103358781</v>
+        <v>-4.475148981956622</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-4.585763884316748</v>
+        <v>-5.064602540743934</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-4.311289171834694</v>
+        <v>-4.739779364049312</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-4.086369545358728</v>
+        <v>-4.521533288173906</v>
       </c>
     </row>
     <row r="8">
@@ -3798,79 +3798,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.25989473247958</v>
+        <v>-1.012864823348693</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.933957245115117</v>
+        <v>-2.44924784952876</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.181500103669912</v>
+        <v>-2.662275284753662</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-4.489692218350747</v>
+        <v>-3.998725102609505</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-4.230244595659926</v>
+        <v>-3.679045147470745</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.299230790514933</v>
+        <v>-2.778063922425048</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.327131855357663</v>
+        <v>-2.829098315610146</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-2.184001663605173</v>
+        <v>-1.79473304473305</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-2.806482273135622</v>
+        <v>-2.410851754096562</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.900059216824879</v>
+        <v>-2.611665154077798</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.944626894015279</v>
+        <v>-1.744192044235369</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.390035482840645</v>
+        <v>-1.276726379659053</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.82750436025546</v>
+        <v>-1.79638040187173</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.511203751954135</v>
+        <v>-1.59818589187627</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-1.417467350286579</v>
+        <v>-1.536292654713698</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.5223285486443459</v>
+        <v>-0.6773695882749919</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-2.460756963817303</v>
+        <v>-2.71577380952381</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-3.016725487187351</v>
+        <v>-3.443896009923506</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-4.154217564909644</v>
+        <v>-4.568719497063455</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-4.41849957449049</v>
+        <v>-4.949371147242566</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-4.058790103358781</v>
+        <v>-4.475148981956622</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-4.585763884316748</v>
+        <v>-5.064602540743934</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-4.311289171834694</v>
+        <v>-4.739779364049312</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-4.086369545358728</v>
+        <v>-4.521533288173906</v>
       </c>
     </row>
     <row r="9">
@@ -3880,79 +3880,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.25989473247958</v>
+        <v>-1.012864823348693</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.933957245115117</v>
+        <v>-2.44924784952876</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.181500103669912</v>
+        <v>-2.662275284753662</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.489692218350747</v>
+        <v>-3.998725102609505</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-4.230244595659926</v>
+        <v>-3.679045147470745</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-3.299230790514933</v>
+        <v>-2.778063922425048</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.327131855357663</v>
+        <v>-2.829098315610146</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.184001663605173</v>
+        <v>-1.79473304473305</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.806482273135622</v>
+        <v>-2.410851754096562</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.900059216824879</v>
+        <v>-2.611665154077798</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.944626894015279</v>
+        <v>-1.744192044235369</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.390035482840645</v>
+        <v>-1.276726379659053</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.82750436025546</v>
+        <v>-1.79638040187173</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.511203751954135</v>
+        <v>-1.59818589187627</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-1.417467350286579</v>
+        <v>-1.536292654713698</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.5223285486443459</v>
+        <v>-0.6773695882749919</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-2.460756963817303</v>
+        <v>-2.71577380952381</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-3.016725487187351</v>
+        <v>-3.443896009923506</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-4.154217564909644</v>
+        <v>-4.568719497063455</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-4.41849957449049</v>
+        <v>-4.949371147242566</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-4.058790103358781</v>
+        <v>-4.475148981956622</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-4.585763884316748</v>
+        <v>-5.064602540743934</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-4.311289171834694</v>
+        <v>-4.739779364049312</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-4.086369545358728</v>
+        <v>-4.521533288173906</v>
       </c>
     </row>
     <row r="10">
@@ -3962,79 +3962,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.25989473247958</v>
+        <v>-1.012864823348693</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.933957245115117</v>
+        <v>-2.44924784952876</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.181500103669912</v>
+        <v>-2.662275284753662</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-4.489692218350747</v>
+        <v>-3.998725102609505</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.230244595659926</v>
+        <v>-3.679045147470745</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-3.299230790514933</v>
+        <v>-2.778063922425048</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.327131855357663</v>
+        <v>-2.829098315610146</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.184001663605173</v>
+        <v>-1.79473304473305</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.806482273135622</v>
+        <v>-2.410851754096562</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.900059216824879</v>
+        <v>-2.611665154077798</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.944626894015279</v>
+        <v>-1.744192044235369</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.390035482840645</v>
+        <v>-1.276726379659053</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.82750436025546</v>
+        <v>-1.79638040187173</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.511203751954135</v>
+        <v>-1.59818589187627</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-1.417467350286579</v>
+        <v>-1.536292654713698</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.5223285486443459</v>
+        <v>-0.6773695882749919</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-2.460756963817303</v>
+        <v>-2.71577380952381</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-3.016725487187351</v>
+        <v>-3.443896009923506</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-4.154217564909644</v>
+        <v>-4.568719497063455</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-4.41849957449049</v>
+        <v>-4.949371147242566</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-4.058790103358781</v>
+        <v>-4.475148981956622</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-4.585763884316748</v>
+        <v>-5.064602540743934</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-4.311289171834694</v>
+        <v>-4.739779364049312</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-4.086369545358728</v>
+        <v>-4.521533288173906</v>
       </c>
     </row>
     <row r="11">
@@ -4044,79 +4044,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.25989473247958</v>
+        <v>-1.012864823348693</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.933957245115117</v>
+        <v>-2.44924784952876</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-3.181500103669912</v>
+        <v>-2.662275284753662</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-4.489692218350747</v>
+        <v>-3.998725102609505</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-4.230244595659926</v>
+        <v>-3.679045147470745</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.299230790514933</v>
+        <v>-2.778063922425048</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.327131855357663</v>
+        <v>-2.829098315610146</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.184001663605173</v>
+        <v>-1.79473304473305</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.806482273135622</v>
+        <v>-2.410851754096562</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.900059216824879</v>
+        <v>-2.611665154077798</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.944626894015279</v>
+        <v>-1.744192044235369</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.390035482840645</v>
+        <v>-1.276726379659053</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.82750436025546</v>
+        <v>-1.79638040187173</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.511203751954135</v>
+        <v>-1.59818589187627</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-1.417467350286579</v>
+        <v>-1.536292654713698</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.5223285486443459</v>
+        <v>-0.6773695882749919</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-2.460756963817303</v>
+        <v>-2.71577380952381</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-3.016725487187351</v>
+        <v>-3.443896009923506</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-4.154217564909644</v>
+        <v>-4.568719497063455</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-4.41849957449049</v>
+        <v>-4.949371147242566</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-4.058790103358781</v>
+        <v>-4.475148981956622</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-4.585763884316748</v>
+        <v>-5.064602540743934</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-4.311289171834694</v>
+        <v>-4.739779364049312</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-4.086369545358728</v>
+        <v>-4.521533288173906</v>
       </c>
     </row>
     <row r="12">
@@ -4126,79 +4126,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.25989473247958</v>
+        <v>-1.012864823348693</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.933957245115117</v>
+        <v>-2.44924784952876</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.181500103669912</v>
+        <v>-2.662275284753662</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.489692218350747</v>
+        <v>-3.998725102609505</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-4.230244595659926</v>
+        <v>-3.679045147470745</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.299230790514933</v>
+        <v>-2.778063922425048</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.327131855357663</v>
+        <v>-2.829098315610146</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.184001663605173</v>
+        <v>-1.79473304473305</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.806482273135622</v>
+        <v>-2.410851754096562</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.900059216824879</v>
+        <v>-2.611665154077798</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.944626894015279</v>
+        <v>-1.744192044235369</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.390035482840645</v>
+        <v>-1.276726379659053</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.82750436025546</v>
+        <v>-1.79638040187173</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.511203751954135</v>
+        <v>-1.59818589187627</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1.417467350286579</v>
+        <v>-1.536292654713698</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.5223285486443459</v>
+        <v>-0.6773695882749919</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.460756963817303</v>
+        <v>-2.71577380952381</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-3.016725487187351</v>
+        <v>-3.443896009923506</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-4.154217564909644</v>
+        <v>-4.568719497063455</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-4.41849957449049</v>
+        <v>-4.949371147242566</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-4.058790103358781</v>
+        <v>-4.475148981956622</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-4.585763884316748</v>
+        <v>-5.064602540743934</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-4.311289171834694</v>
+        <v>-4.739779364049312</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-4.086369545358728</v>
+        <v>-4.521533288173906</v>
       </c>
     </row>
     <row r="13">
@@ -4208,79 +4208,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.25989473247958</v>
+        <v>-1.012864823348693</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.933957245115117</v>
+        <v>-2.44924784952876</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.181500103669912</v>
+        <v>-2.662275284753662</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-4.489692218350747</v>
+        <v>-3.998725102609505</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.230244595659926</v>
+        <v>-3.679045147470745</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-3.299230790514933</v>
+        <v>-2.778063922425048</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-3.327131855357663</v>
+        <v>-2.829098315610146</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.184001663605173</v>
+        <v>-1.79473304473305</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.806482273135622</v>
+        <v>-2.410851754096562</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.900059216824879</v>
+        <v>-2.611665154077798</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.944626894015279</v>
+        <v>-1.744192044235369</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.390035482840645</v>
+        <v>-1.276726379659053</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.82750436025546</v>
+        <v>-1.79638040187173</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.511203751954135</v>
+        <v>-1.59818589187627</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-1.417467350286579</v>
+        <v>-1.536292654713698</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.5223285486443459</v>
+        <v>-0.6773695882749919</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-2.460756963817303</v>
+        <v>-2.71577380952381</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-3.016725487187351</v>
+        <v>-3.443896009923506</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-4.154217564909644</v>
+        <v>-4.568719497063455</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-4.41849957449049</v>
+        <v>-4.949371147242566</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-4.058790103358781</v>
+        <v>-4.475148981956622</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-4.585763884316748</v>
+        <v>-5.064602540743934</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-4.311289171834694</v>
+        <v>-4.739779364049312</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-4.086369545358728</v>
+        <v>-4.521533288173906</v>
       </c>
     </row>
     <row r="14">
@@ -4290,79 +4290,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.4508829557258736</v>
+        <v>-0.2474977882825158</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.1850647539284083</v>
+        <v>0.5094607055265072</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.6524015474427927</v>
+        <v>0.9739643113713115</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.7699547438824226</v>
+        <v>1.02626125296424</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.4031768893970735</v>
+        <v>0.5358033993978495</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.7029959994816437</v>
+        <v>0.8360034810406347</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.8359993798578031</v>
+        <v>0.9005203226761083</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.103813417331281</v>
+        <v>1.025399306201585</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2501523619083343</v>
+        <v>0.07882964855046026</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.09594826348753571</v>
+        <v>-0.1441559440900804</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.382228225648042</v>
+        <v>-0.6598865455315988</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.6195031189647793</v>
+        <v>-1.008101737825235</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.8334517393047918</v>
+        <v>-1.335028239230169</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.012308177272132</v>
+        <v>-1.583262300663279</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.019221373550238</v>
+        <v>-1.579175399209355</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.9313467526202714</v>
+        <v>-1.478421716443336</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-2.078288491623795</v>
+        <v>-2.617813771237145</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-2.183129195444977</v>
+        <v>-2.78195019711562</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-2.473750115533669</v>
+        <v>-3.030129582305307</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-2.721057706433953</v>
+        <v>-3.278850420966435</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-2.684732673242245</v>
+        <v>-3.158361467814899</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-2.615860834361904</v>
+        <v>-3.120968152738591</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-2.413745022024571</v>
+        <v>-2.836713582646311</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.548911573366517</v>
+        <v>-2.020222939329933</v>
       </c>
     </row>
     <row r="15">
@@ -4372,79 +4372,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.4508829557258736</v>
+        <v>-0.2474977882825158</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1850647539284083</v>
+        <v>0.5094607055265072</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.6524015474427927</v>
+        <v>0.9739643113713115</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.7699547438824226</v>
+        <v>1.02626125296424</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.4031768893970735</v>
+        <v>0.5358033993978495</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.7029959994816437</v>
+        <v>0.8360034810406347</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.8359993798578031</v>
+        <v>0.9005203226761083</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.103813417331281</v>
+        <v>1.025399306201585</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.2501523619083343</v>
+        <v>0.07882964855046026</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.09594826348753571</v>
+        <v>-0.1441559440900804</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.382228225648042</v>
+        <v>-0.6598865455315988</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.6195031189647793</v>
+        <v>-1.008101737825235</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.8334517393047918</v>
+        <v>-1.335028239230169</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.012308177272132</v>
+        <v>-1.583262300663279</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.019221373550238</v>
+        <v>-1.579175399209355</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.9313467526202714</v>
+        <v>-1.478421716443336</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-2.078288491623795</v>
+        <v>-2.617813771237145</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.183129195444977</v>
+        <v>-2.78195019711562</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-2.473750115533669</v>
+        <v>-3.030129582305307</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-2.721057706433953</v>
+        <v>-3.278850420966435</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-2.684732673242245</v>
+        <v>-3.158361467814899</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-2.615860834361904</v>
+        <v>-3.120968152738591</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-2.413745022024571</v>
+        <v>-2.836713582646311</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-1.548911573366517</v>
+        <v>-2.020222939329933</v>
       </c>
     </row>
     <row r="16">
@@ -4454,79 +4454,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.4508829557258736</v>
+        <v>-0.2474977882825158</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.1850647539284083</v>
+        <v>0.5094607055265072</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.6524015474427927</v>
+        <v>0.9739643113713115</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.7699547438824226</v>
+        <v>1.02626125296424</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.4031768893970735</v>
+        <v>0.5358033993978495</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.7029959994816437</v>
+        <v>0.8360034810406347</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.8359993798578031</v>
+        <v>0.9005203226761083</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.103813417331281</v>
+        <v>1.025399306201585</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.2501523619083343</v>
+        <v>0.07882964855046026</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.09594826348753571</v>
+        <v>-0.1441559440900804</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.382228225648042</v>
+        <v>-0.6598865455315988</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.6195031189647793</v>
+        <v>-1.008101737825235</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.8334517393047918</v>
+        <v>-1.335028239230169</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.012308177272132</v>
+        <v>-1.583262300663279</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-1.019221373550238</v>
+        <v>-1.579175399209355</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.9313467526202714</v>
+        <v>-1.478421716443336</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-2.078288491623795</v>
+        <v>-2.617813771237145</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.183129195444977</v>
+        <v>-2.78195019711562</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-2.473750115533669</v>
+        <v>-3.030129582305307</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-2.721057706433953</v>
+        <v>-3.278850420966435</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-2.684732673242245</v>
+        <v>-3.158361467814899</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-2.615860834361904</v>
+        <v>-3.120968152738591</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-2.413745022024571</v>
+        <v>-2.836713582646311</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.548911573366517</v>
+        <v>-2.020222939329933</v>
       </c>
     </row>
     <row r="17">
@@ -4536,79 +4536,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4508829557258736</v>
+        <v>-0.2474977882825158</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.1850647539284083</v>
+        <v>0.5094607055265072</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.6524015474427927</v>
+        <v>0.9739643113713115</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.7699547438824226</v>
+        <v>1.02626125296424</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.4031768893970735</v>
+        <v>0.5358033993978495</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.7029959994816437</v>
+        <v>0.8360034810406347</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.8359993798578031</v>
+        <v>0.9005203226761083</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.103813417331281</v>
+        <v>1.025399306201585</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.2501523619083343</v>
+        <v>0.07882964855046026</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.09594826348753571</v>
+        <v>-0.1441559440900804</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.382228225648042</v>
+        <v>-0.6598865455315988</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.6195031189647793</v>
+        <v>-1.008101737825235</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.8334517393047918</v>
+        <v>-1.335028239230169</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.012308177272132</v>
+        <v>-1.583262300663279</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.019221373550238</v>
+        <v>-1.579175399209355</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.9313467526202714</v>
+        <v>-1.478421716443336</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-2.078288491623795</v>
+        <v>-2.617813771237145</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-2.183129195444977</v>
+        <v>-2.78195019711562</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-2.473750115533669</v>
+        <v>-3.030129582305307</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-2.721057706433953</v>
+        <v>-3.278850420966435</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-2.684732673242245</v>
+        <v>-3.158361467814899</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-2.615860834361904</v>
+        <v>-3.120968152738591</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-2.413745022024571</v>
+        <v>-2.836713582646311</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.548911573366517</v>
+        <v>-2.020222939329933</v>
       </c>
     </row>
     <row r="18">
@@ -4618,79 +4618,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.4508829557258736</v>
+        <v>-0.2474977882825158</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.1850647539284083</v>
+        <v>0.5094607055265072</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.6524015474427927</v>
+        <v>0.9739643113713115</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.7699547438824226</v>
+        <v>1.02626125296424</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.4031768893970735</v>
+        <v>0.5358033993978495</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.7029959994816437</v>
+        <v>0.8360034810406347</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.8359993798578031</v>
+        <v>0.9005203226761083</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.103813417331281</v>
+        <v>1.025399306201585</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.2501523619083343</v>
+        <v>0.07882964855046026</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.09594826348753571</v>
+        <v>-0.1441559440900804</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.382228225648042</v>
+        <v>-0.6598865455315988</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.6195031189647793</v>
+        <v>-1.008101737825235</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.8334517393047918</v>
+        <v>-1.335028239230169</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.012308177272132</v>
+        <v>-1.583262300663279</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.019221373550238</v>
+        <v>-1.579175399209355</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.9313467526202714</v>
+        <v>-1.478421716443336</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-2.078288491623795</v>
+        <v>-2.617813771237145</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-2.183129195444977</v>
+        <v>-2.78195019711562</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-2.473750115533669</v>
+        <v>-3.030129582305307</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-2.721057706433953</v>
+        <v>-3.278850420966435</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-2.684732673242245</v>
+        <v>-3.158361467814899</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-2.615860834361904</v>
+        <v>-3.120968152738591</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-2.413745022024571</v>
+        <v>-2.836713582646311</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.548911573366517</v>
+        <v>-2.020222939329933</v>
       </c>
     </row>
     <row r="19">
@@ -4700,79 +4700,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.4508829557258736</v>
+        <v>-0.2474977882825158</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.1850647539284083</v>
+        <v>0.5094607055265072</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.6524015474427927</v>
+        <v>0.9739643113713115</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.7699547438824226</v>
+        <v>1.02626125296424</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.4031768893970735</v>
+        <v>0.5358033993978495</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.7029959994816437</v>
+        <v>0.8360034810406347</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.8359993798578031</v>
+        <v>0.9005203226761083</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.103813417331281</v>
+        <v>1.025399306201585</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.2501523619083343</v>
+        <v>0.07882964855046026</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.09594826348753571</v>
+        <v>-0.1441559440900804</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.382228225648042</v>
+        <v>-0.6598865455315988</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.6195031189647793</v>
+        <v>-1.008101737825235</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.8334517393047918</v>
+        <v>-1.335028239230169</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.012308177272132</v>
+        <v>-1.583262300663279</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-1.019221373550238</v>
+        <v>-1.579175399209355</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.9313467526202714</v>
+        <v>-1.478421716443336</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-2.078288491623795</v>
+        <v>-2.617813771237145</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.183129195444977</v>
+        <v>-2.78195019711562</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-2.473750115533669</v>
+        <v>-3.030129582305307</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-2.721057706433953</v>
+        <v>-3.278850420966435</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-2.684732673242245</v>
+        <v>-3.158361467814899</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-2.615860834361904</v>
+        <v>-3.120968152738591</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-2.413745022024571</v>
+        <v>-2.836713582646311</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.548911573366517</v>
+        <v>-2.020222939329933</v>
       </c>
     </row>
     <row r="20">
@@ -4782,79 +4782,79 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.4508829557258736</v>
+        <v>-0.2474977882825158</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.1850647539284083</v>
+        <v>0.5094607055265072</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.6524015474427927</v>
+        <v>0.9739643113713115</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.7699547438824226</v>
+        <v>1.02626125296424</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.4031768893970735</v>
+        <v>0.5358033993978495</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.7029959994816437</v>
+        <v>0.8360034810406347</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.8359993798578031</v>
+        <v>0.9005203226761083</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.103813417331281</v>
+        <v>1.025399306201585</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.2501523619083343</v>
+        <v>0.07882964855046026</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.09594826348753571</v>
+        <v>-0.1441559440900804</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.382228225648042</v>
+        <v>-0.6598865455315988</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.6195031189647793</v>
+        <v>-1.008101737825235</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.8334517393047918</v>
+        <v>-1.335028239230169</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.012308177272132</v>
+        <v>-1.583262300663279</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.019221373550238</v>
+        <v>-1.579175399209355</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.9313467526202714</v>
+        <v>-1.478421716443336</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-2.078288491623795</v>
+        <v>-2.617813771237145</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-2.183129195444977</v>
+        <v>-2.78195019711562</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-2.473750115533669</v>
+        <v>-3.030129582305307</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-2.721057706433953</v>
+        <v>-3.278850420966435</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-2.684732673242245</v>
+        <v>-3.158361467814899</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-2.615860834361904</v>
+        <v>-3.120968152738591</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-2.413745022024571</v>
+        <v>-2.836713582646311</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.548911573366517</v>
+        <v>-2.020222939329933</v>
       </c>
     </row>
     <row r="21">
@@ -4864,79 +4864,79 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2078</v>
+        <v>2089</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.01142973043292272</v>
+        <v>0.06611021395968208</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.1571997862593051</v>
+        <v>0.1051036631560933</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.3467213546942247</v>
+        <v>-0.3898563456680577</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.06661201065792</v>
+        <v>-0.0325909281419996</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.8643013284008703</v>
+        <v>-1.020399780492049</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.129418394517756</v>
+        <v>-1.243333221027676</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.587599835653229</v>
+        <v>-1.800998329176828</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.264249339766657</v>
+        <v>-1.557344740242605</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.819089419570268</v>
+        <v>-2.116061784876933</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.654132191628896</v>
+        <v>-1.982674256720294</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.120762147500635</v>
+        <v>-2.445196756300987</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.228766381433601</v>
+        <v>-2.600500772805169</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.980250766604165</v>
+        <v>-2.403523259014584</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.17384064211322</v>
+        <v>-2.624964516618213</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-2.159230455791814</v>
+        <v>-2.56533391850234</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.564843533848823</v>
+        <v>-1.929157857230649</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.227352693892129</v>
+        <v>-2.578323791348602</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-2.043870476041029</v>
+        <v>-2.350092736824294</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-2.260463477625116</v>
+        <v>-2.538258315456133</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-2.506102050165502</v>
+        <v>-2.774462722334135</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-2.327840913950851</v>
+        <v>-2.550299214133631</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-1.991417441286089</v>
+        <v>-2.215688630372249</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.881477268338578</v>
+        <v>-2.136051591429165</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.352031293569475</v>
+        <v>-1.600688747655951</v>
       </c>
     </row>
     <row r="22">
@@ -4946,79 +4946,79 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2078</v>
+        <v>2089</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01142973043292272</v>
+        <v>0.06611021395968208</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.1571997862593051</v>
+        <v>0.1051036631560933</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.3467213546942247</v>
+        <v>-0.3898563456680577</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.06661201065792</v>
+        <v>-0.0325909281419996</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.8643013284008703</v>
+        <v>-1.020399780492049</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.129418394517756</v>
+        <v>-1.243333221027676</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.587599835653229</v>
+        <v>-1.800998329176828</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.264249339766657</v>
+        <v>-1.557344740242605</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.819089419570268</v>
+        <v>-2.116061784876933</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.654132191628896</v>
+        <v>-1.982674256720294</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.120762147500635</v>
+        <v>-2.445196756300987</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.228766381433601</v>
+        <v>-2.600500772805169</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.980250766604165</v>
+        <v>-2.403523259014584</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.17384064211322</v>
+        <v>-2.624964516618213</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-2.159230455791814</v>
+        <v>-2.56533391850234</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.564843533848823</v>
+        <v>-1.929157857230649</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-2.227352693892129</v>
+        <v>-2.578323791348602</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-2.043870476041029</v>
+        <v>-2.350092736824294</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-2.260463477625116</v>
+        <v>-2.538258315456133</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-2.506102050165502</v>
+        <v>-2.774462722334135</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-2.327840913950851</v>
+        <v>-2.550299214133631</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.991417441286089</v>
+        <v>-2.215688630372249</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.881477268338578</v>
+        <v>-2.136051591429165</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.352031293569475</v>
+        <v>-1.600688747655951</v>
       </c>
     </row>
     <row r="23">
@@ -5028,79 +5028,79 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2078</v>
+        <v>2089</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.01142973043292272</v>
+        <v>0.06611021395968208</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1571997862593051</v>
+        <v>0.1051036631560933</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3467213546942247</v>
+        <v>-0.3898563456680577</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.06661201065792</v>
+        <v>-0.0325909281419996</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.8643013284008703</v>
+        <v>-1.020399780492049</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.129418394517756</v>
+        <v>-1.243333221027676</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.587599835653229</v>
+        <v>-1.800998329176828</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.264249339766657</v>
+        <v>-1.557344740242605</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.819089419570268</v>
+        <v>-2.116061784876933</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.654132191628896</v>
+        <v>-1.982674256720294</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.120762147500635</v>
+        <v>-2.445196756300987</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.228766381433601</v>
+        <v>-2.600500772805169</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.980250766604165</v>
+        <v>-2.403523259014584</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.17384064211322</v>
+        <v>-2.624964516618213</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-2.159230455791814</v>
+        <v>-2.56533391850234</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.564843533848823</v>
+        <v>-1.929157857230649</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-2.227352693892129</v>
+        <v>-2.578323791348602</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-2.043870476041029</v>
+        <v>-2.350092736824294</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-2.260463477625116</v>
+        <v>-2.538258315456133</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.506102050165502</v>
+        <v>-2.774462722334135</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.327840913950851</v>
+        <v>-2.550299214133631</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.991417441286089</v>
+        <v>-2.215688630372249</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.881477268338578</v>
+        <v>-2.136051591429165</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.352031293569475</v>
+        <v>-1.600688747655951</v>
       </c>
     </row>
     <row r="24">
@@ -5110,79 +5110,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2078</v>
+        <v>2089</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.01142973043292272</v>
+        <v>0.06611021395968208</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.1571997862593051</v>
+        <v>0.1051036631560933</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.3467213546942247</v>
+        <v>-0.3898563456680577</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.06661201065792</v>
+        <v>-0.0325909281419996</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.8643013284008703</v>
+        <v>-1.020399780492049</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.129418394517756</v>
+        <v>-1.243333221027676</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.587599835653229</v>
+        <v>-1.800998329176828</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.264249339766657</v>
+        <v>-1.557344740242605</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.819089419570268</v>
+        <v>-2.116061784876933</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.654132191628896</v>
+        <v>-1.982674256720294</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.120762147500635</v>
+        <v>-2.445196756300987</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.228766381433601</v>
+        <v>-2.600500772805169</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.980250766604165</v>
+        <v>-2.403523259014584</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.17384064211322</v>
+        <v>-2.624964516618213</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-2.159230455791814</v>
+        <v>-2.56533391850234</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.564843533848823</v>
+        <v>-1.929157857230649</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-2.227352693892129</v>
+        <v>-2.578323791348602</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-2.043870476041029</v>
+        <v>-2.350092736824294</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-2.260463477625116</v>
+        <v>-2.538258315456133</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-2.506102050165502</v>
+        <v>-2.774462722334135</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-2.327840913950851</v>
+        <v>-2.550299214133631</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.991417441286089</v>
+        <v>-2.215688630372249</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.881477268338578</v>
+        <v>-2.136051591429165</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.352031293569475</v>
+        <v>-1.600688747655951</v>
       </c>
     </row>
     <row r="25">
@@ -5192,79 +5192,79 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2078</v>
+        <v>2089</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.01142973043292272</v>
+        <v>0.06611021395968208</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.1571997862593051</v>
+        <v>0.1051036631560933</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.3467213546942247</v>
+        <v>-0.3898563456680577</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.06661201065792</v>
+        <v>-0.0325909281419996</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.8643013284008703</v>
+        <v>-1.020399780492049</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.129418394517756</v>
+        <v>-1.243333221027676</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.587599835653229</v>
+        <v>-1.800998329176828</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.264249339766657</v>
+        <v>-1.557344740242605</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.819089419570268</v>
+        <v>-2.116061784876933</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.654132191628896</v>
+        <v>-1.982674256720294</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.120762147500635</v>
+        <v>-2.445196756300987</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.228766381433601</v>
+        <v>-2.600500772805169</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.980250766604165</v>
+        <v>-2.403523259014584</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.17384064211322</v>
+        <v>-2.624964516618213</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-2.159230455791814</v>
+        <v>-2.56533391850234</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.564843533848823</v>
+        <v>-1.929157857230649</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-2.227352693892129</v>
+        <v>-2.578323791348602</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-2.043870476041029</v>
+        <v>-2.350092736824294</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-2.260463477625116</v>
+        <v>-2.538258315456133</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-2.506102050165502</v>
+        <v>-2.774462722334135</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-2.327840913950851</v>
+        <v>-2.550299214133631</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.991417441286089</v>
+        <v>-2.215688630372249</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.881477268338578</v>
+        <v>-2.136051591429165</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.352031293569475</v>
+        <v>-1.600688747655951</v>
       </c>
     </row>
     <row r="26">
@@ -5274,79 +5274,79 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2078</v>
+        <v>2089</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.01142973043292272</v>
+        <v>0.06611021395968208</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.1571997862593051</v>
+        <v>0.1051036631560933</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.3467213546942247</v>
+        <v>-0.3898563456680577</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.06661201065792</v>
+        <v>-0.0325909281419996</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.8643013284008703</v>
+        <v>-1.020399780492049</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.129418394517756</v>
+        <v>-1.243333221027676</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.587599835653229</v>
+        <v>-1.800998329176828</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.264249339766657</v>
+        <v>-1.557344740242605</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.819089419570268</v>
+        <v>-2.116061784876933</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.654132191628896</v>
+        <v>-1.982674256720294</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.120762147500635</v>
+        <v>-2.445196756300987</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.228766381433601</v>
+        <v>-2.600500772805169</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.980250766604165</v>
+        <v>-2.403523259014584</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.17384064211322</v>
+        <v>-2.624964516618213</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-2.159230455791814</v>
+        <v>-2.56533391850234</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.564843533848823</v>
+        <v>-1.929157857230649</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-2.227352693892129</v>
+        <v>-2.578323791348602</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-2.043870476041029</v>
+        <v>-2.350092736824294</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-2.260463477625116</v>
+        <v>-2.538258315456133</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-2.506102050165502</v>
+        <v>-2.774462722334135</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-2.327840913950851</v>
+        <v>-2.550299214133631</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.991417441286089</v>
+        <v>-2.215688630372249</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.881477268338578</v>
+        <v>-2.136051591429165</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.352031293569475</v>
+        <v>-1.600688747655951</v>
       </c>
     </row>
     <row r="27">
@@ -5356,79 +5356,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2078</v>
+        <v>2089</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.01142973043292272</v>
+        <v>0.06611021395968208</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1571997862593051</v>
+        <v>0.1051036631560933</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.3467213546942247</v>
+        <v>-0.3898563456680577</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.06661201065792</v>
+        <v>-0.0325909281419996</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.8643013284008703</v>
+        <v>-1.020399780492049</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.129418394517756</v>
+        <v>-1.243333221027676</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.587599835653229</v>
+        <v>-1.800998329176828</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.264249339766657</v>
+        <v>-1.557344740242605</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.819089419570268</v>
+        <v>-2.116061784876933</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.654132191628896</v>
+        <v>-1.982674256720294</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.120762147500635</v>
+        <v>-2.445196756300987</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.228766381433601</v>
+        <v>-2.600500772805169</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.980250766604165</v>
+        <v>-2.403523259014584</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.17384064211322</v>
+        <v>-2.624964516618213</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-2.159230455791814</v>
+        <v>-2.56533391850234</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.564843533848823</v>
+        <v>-1.929157857230649</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-2.227352693892129</v>
+        <v>-2.578323791348602</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-2.043870476041029</v>
+        <v>-2.350092736824294</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-2.260463477625116</v>
+        <v>-2.538258315456133</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-2.506102050165502</v>
+        <v>-2.774462722334135</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-2.327840913950851</v>
+        <v>-2.550299214133631</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.991417441286089</v>
+        <v>-2.215688630372249</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.881477268338578</v>
+        <v>-2.136051591429165</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.352031293569475</v>
+        <v>-1.600688747655951</v>
       </c>
     </row>
     <row r="28">
@@ -5438,79 +5438,79 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2739</v>
+        <v>2764</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2013105457274094</v>
+        <v>-0.1877648694812422</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.3718571606046766</v>
+        <v>-0.3427331330894106</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.7397299173345075</v>
+        <v>-0.7164772168730096</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.7804570744925527</v>
+        <v>-0.7864919334797875</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.9511474237962645</v>
+        <v>-1.006408989162651</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.070488368627792</v>
+        <v>-1.153247928450178</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.314423651611726</v>
+        <v>-1.425280315918357</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.209428945258097</v>
+        <v>-1.314688508933116</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.220187169134931</v>
+        <v>-1.346694983075814</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.06463793160647</v>
+        <v>-1.186886279244931</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.205915363587764</v>
+        <v>-1.326485800772915</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.027893761988977</v>
+        <v>-1.150645688016404</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.6394071721582648</v>
+        <v>-0.7677446232359557</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.4390435405854163</v>
+        <v>-0.5625273963223094</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.4207068901843627</v>
+        <v>-0.5384692556101101</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.1322379234647144</v>
+        <v>-0.2444691553745599</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.3537961897043047</v>
+        <v>-0.4714941958378489</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.4370522604045419</v>
+        <v>-0.5471064276646089</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.6368782983759615</v>
+        <v>-0.7448145287922756</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.8295965842405337</v>
+        <v>-0.9426962229375775</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.9131799071900204</v>
+        <v>-1.019401395607311</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.8945584903136776</v>
+        <v>-1.00115594147001</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.7445255474452495</v>
+        <v>-0.8810441072411379</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.6163033612785895</v>
+        <v>-0.7688211814158663</v>
       </c>
     </row>
     <row r="29">
@@ -5520,79 +5520,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2739</v>
+        <v>2764</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.2013105457274094</v>
+        <v>-0.1877648694812422</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.3718571606046766</v>
+        <v>-0.3427331330894106</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.7397299173345075</v>
+        <v>-0.7164772168730096</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.7804570744925527</v>
+        <v>-0.7864919334797875</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.9511474237962645</v>
+        <v>-1.006408989162651</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.070488368627792</v>
+        <v>-1.153247928450178</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.314423651611726</v>
+        <v>-1.425280315918357</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.209428945258097</v>
+        <v>-1.314688508933116</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.220187169134931</v>
+        <v>-1.346694983075814</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.06463793160647</v>
+        <v>-1.186886279244931</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.205915363587764</v>
+        <v>-1.326485800772915</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.027893761988977</v>
+        <v>-1.150645688016404</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.6394071721582648</v>
+        <v>-0.7677446232359557</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.4390435405854163</v>
+        <v>-0.5625273963223094</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.4207068901843627</v>
+        <v>-0.5384692556101101</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.1322379234647144</v>
+        <v>-0.2444691553745599</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.3537961897043047</v>
+        <v>-0.4714941958378489</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.4370522604045419</v>
+        <v>-0.5471064276646089</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.6368782983759615</v>
+        <v>-0.7448145287922756</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.8295965842405337</v>
+        <v>-0.9426962229375775</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.9131799071900204</v>
+        <v>-1.019401395607311</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.8945584903136776</v>
+        <v>-1.00115594147001</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.7445255474452495</v>
+        <v>-0.8810441072411379</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.6163033612785895</v>
+        <v>-0.7688211814158663</v>
       </c>
     </row>
     <row r="30">
@@ -5602,79 +5602,79 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2739</v>
+        <v>2764</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.2013105457274094</v>
+        <v>-0.1877648694812422</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3718571606046766</v>
+        <v>-0.3427331330894106</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7397299173345075</v>
+        <v>-0.7164772168730096</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.7804570744925527</v>
+        <v>-0.7864919334797875</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.9511474237962645</v>
+        <v>-1.006408989162651</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.070488368627792</v>
+        <v>-1.153247928450178</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.314423651611726</v>
+        <v>-1.425280315918357</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.209428945258097</v>
+        <v>-1.314688508933116</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.220187169134931</v>
+        <v>-1.346694983075814</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.06463793160647</v>
+        <v>-1.186886279244931</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.205915363587764</v>
+        <v>-1.326485800772915</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.027893761988977</v>
+        <v>-1.150645688016404</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.6394071721582648</v>
+        <v>-0.7677446232359557</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.4390435405854163</v>
+        <v>-0.5625273963223094</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.4207068901843627</v>
+        <v>-0.5384692556101101</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.1322379234647144</v>
+        <v>-0.2444691553745599</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.3537961897043047</v>
+        <v>-0.4714941958378489</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.4370522604045419</v>
+        <v>-0.5471064276646089</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.6368782983759615</v>
+        <v>-0.7448145287922756</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.8295965842405337</v>
+        <v>-0.9426962229375775</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.9131799071900204</v>
+        <v>-1.019401395607311</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.8945584903136776</v>
+        <v>-1.00115594147001</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.7445255474452495</v>
+        <v>-0.8810441072411379</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.6163033612785895</v>
+        <v>-0.7688211814158663</v>
       </c>
     </row>
     <row r="31">
@@ -5684,79 +5684,79 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2739</v>
+        <v>2764</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.2013105457274094</v>
+        <v>-0.1877648694812422</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3718571606046766</v>
+        <v>-0.3427331330894106</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.7397299173345075</v>
+        <v>-0.7164772168730096</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.7804570744925527</v>
+        <v>-0.7864919334797875</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.9511474237962645</v>
+        <v>-1.006408989162651</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.070488368627792</v>
+        <v>-1.153247928450178</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.314423651611726</v>
+        <v>-1.425280315918357</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.209428945258097</v>
+        <v>-1.314688508933116</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.220187169134931</v>
+        <v>-1.346694983075814</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.06463793160647</v>
+        <v>-1.186886279244931</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.205915363587764</v>
+        <v>-1.326485800772915</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.027893761988977</v>
+        <v>-1.150645688016404</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.6394071721582648</v>
+        <v>-0.7677446232359557</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.4390435405854163</v>
+        <v>-0.5625273963223094</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.4207068901843627</v>
+        <v>-0.5384692556101101</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.1322379234647144</v>
+        <v>-0.2444691553745599</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.3537961897043047</v>
+        <v>-0.4714941958378489</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.4370522604045419</v>
+        <v>-0.5471064276646089</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.6368782983759615</v>
+        <v>-0.7448145287922756</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.8295965842405337</v>
+        <v>-0.9426962229375775</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.9131799071900204</v>
+        <v>-1.019401395607311</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.8945584903136776</v>
+        <v>-1.00115594147001</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.7445255474452495</v>
+        <v>-0.8810441072411379</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.6163033612785895</v>
+        <v>-0.7688211814158663</v>
       </c>
     </row>
     <row r="32">
@@ -5766,79 +5766,79 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2739</v>
+        <v>2764</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.2013105457274094</v>
+        <v>-0.1877648694812422</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.3718571606046766</v>
+        <v>-0.3427331330894106</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.7397299173345075</v>
+        <v>-0.7164772168730096</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.7804570744925527</v>
+        <v>-0.7864919334797875</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.9511474237962645</v>
+        <v>-1.006408989162651</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.070488368627792</v>
+        <v>-1.153247928450178</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.314423651611726</v>
+        <v>-1.425280315918357</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.209428945258097</v>
+        <v>-1.314688508933116</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.220187169134931</v>
+        <v>-1.346694983075814</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.06463793160647</v>
+        <v>-1.186886279244931</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.205915363587764</v>
+        <v>-1.326485800772915</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.027893761988977</v>
+        <v>-1.150645688016404</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.6394071721582648</v>
+        <v>-0.7677446232359557</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.4390435405854163</v>
+        <v>-0.5625273963223094</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.4207068901843627</v>
+        <v>-0.5384692556101101</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.1322379234647144</v>
+        <v>-0.2444691553745599</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.3537961897043047</v>
+        <v>-0.4714941958378489</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.4370522604045419</v>
+        <v>-0.5471064276646089</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.6368782983759615</v>
+        <v>-0.7448145287922756</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.8295965842405337</v>
+        <v>-0.9426962229375775</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.9131799071900204</v>
+        <v>-1.019401395607311</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.8945584903136776</v>
+        <v>-1.00115594147001</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.7445255474452495</v>
+        <v>-0.8810441072411379</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.6163033612785895</v>
+        <v>-0.7688211814158663</v>
       </c>
     </row>
     <row r="33">
@@ -5848,79 +5848,79 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2739</v>
+        <v>2764</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.2013105457274094</v>
+        <v>-0.1877648694812422</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.3718571606046766</v>
+        <v>-0.3427331330894106</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.7397299173345075</v>
+        <v>-0.7164772168730096</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.7804570744925527</v>
+        <v>-0.7864919334797875</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.9511474237962645</v>
+        <v>-1.006408989162651</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.070488368627792</v>
+        <v>-1.153247928450178</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.314423651611726</v>
+        <v>-1.425280315918357</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.209428945258097</v>
+        <v>-1.314688508933116</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-1.220187169134931</v>
+        <v>-1.346694983075814</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-1.06463793160647</v>
+        <v>-1.186886279244931</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.205915363587764</v>
+        <v>-1.326485800772915</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.027893761988977</v>
+        <v>-1.150645688016404</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.6394071721582648</v>
+        <v>-0.7677446232359557</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.4390435405854163</v>
+        <v>-0.5625273963223094</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.4207068901843627</v>
+        <v>-0.5384692556101101</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.1322379234647144</v>
+        <v>-0.2444691553745599</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.3537961897043047</v>
+        <v>-0.4714941958378489</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.4370522604045419</v>
+        <v>-0.5471064276646089</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.6368782983759615</v>
+        <v>-0.7448145287922756</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.8295965842405337</v>
+        <v>-0.9426962229375775</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.9131799071900204</v>
+        <v>-1.019401395607311</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.8945584903136776</v>
+        <v>-1.00115594147001</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.7445255474452495</v>
+        <v>-0.8810441072411379</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.6163033612785895</v>
+        <v>-0.7688211814158663</v>
       </c>
     </row>
     <row r="34">
@@ -5930,79 +5930,79 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2739</v>
+        <v>2764</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2013105457274094</v>
+        <v>-0.1877648694812422</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.3718571606046766</v>
+        <v>-0.3427331330894106</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.7397299173345075</v>
+        <v>-0.7164772168730096</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.7804570744925527</v>
+        <v>-0.7864919334797875</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.9511474237962645</v>
+        <v>-1.006408989162651</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.070488368627792</v>
+        <v>-1.153247928450178</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.314423651611726</v>
+        <v>-1.425280315918357</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.209428945258097</v>
+        <v>-1.314688508933116</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-1.220187169134931</v>
+        <v>-1.346694983075814</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.06463793160647</v>
+        <v>-1.186886279244931</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-1.205915363587764</v>
+        <v>-1.326485800772915</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-1.027893761988977</v>
+        <v>-1.150645688016404</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.6394071721582648</v>
+        <v>-0.7677446232359557</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.4390435405854163</v>
+        <v>-0.5625273963223094</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.4207068901843627</v>
+        <v>-0.5384692556101101</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.1322379234647144</v>
+        <v>-0.2444691553745599</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.3537961897043047</v>
+        <v>-0.4714941958378489</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.4370522604045419</v>
+        <v>-0.5471064276646089</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.6368782983759615</v>
+        <v>-0.7448145287922756</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.8295965842405337</v>
+        <v>-0.9426962229375775</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.9131799071900204</v>
+        <v>-1.019401395607311</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.8945584903136776</v>
+        <v>-1.00115594147001</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.7445255474452495</v>
+        <v>-0.8810441072411379</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.6163033612785895</v>
+        <v>-0.7688211814158663</v>
       </c>
     </row>
     <row r="35">
@@ -6012,79 +6012,79 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2739</v>
+        <v>2764</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.2013105457274094</v>
+        <v>-0.1877648694812422</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.3718571606046766</v>
+        <v>-0.3427331330894106</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.7397299173345075</v>
+        <v>-0.7164772168730096</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.7804570744925527</v>
+        <v>-0.7864919334797875</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.9511474237962645</v>
+        <v>-1.006408989162651</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-1.070488368627792</v>
+        <v>-1.153247928450178</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-1.314423651611726</v>
+        <v>-1.425280315918357</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-1.209428945258097</v>
+        <v>-1.314688508933116</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-1.220187169134931</v>
+        <v>-1.346694983075814</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-1.06463793160647</v>
+        <v>-1.186886279244931</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-1.205915363587764</v>
+        <v>-1.326485800772915</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-1.027893761988977</v>
+        <v>-1.150645688016404</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.6394071721582648</v>
+        <v>-0.7677446232359557</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.4390435405854163</v>
+        <v>-0.5625273963223094</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.4207068901843627</v>
+        <v>-0.5384692556101101</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.1322379234647144</v>
+        <v>-0.2444691553745599</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.3537961897043047</v>
+        <v>-0.4714941958378489</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.4370522604045419</v>
+        <v>-0.5471064276646089</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.6368782983759615</v>
+        <v>-0.7448145287922756</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.8295965842405337</v>
+        <v>-0.9426962229375775</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.9131799071900204</v>
+        <v>-1.019401395607311</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.8945584903136776</v>
+        <v>-1.00115594147001</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.7445255474452495</v>
+        <v>-0.8810441072411379</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.6163033612785895</v>
+        <v>-0.7688211814158663</v>
       </c>
     </row>
   </sheetData>
